--- a/database/event/8034/event_8034_evp_summary.xlsx
+++ b/database/event/8034/event_8034_evp_summary.xlsx
@@ -499,7 +499,7 @@
         <v>10.9162</v>
       </c>
       <c r="C2" t="n">
-        <v>0</v>
+        <v>7.0982</v>
       </c>
       <c r="D2" t="n">
         <v>3.9885</v>
@@ -545,7 +545,7 @@
         <v>10.4199</v>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>6.7754</v>
       </c>
       <c r="D3" t="n">
         <v>3.788</v>
@@ -591,7 +591,7 @@
         <v>7.074</v>
       </c>
       <c r="C4" t="n">
-        <v>0</v>
+        <v>4.5998</v>
       </c>
       <c r="D4" t="n">
         <v>2.4364</v>
@@ -637,7 +637,7 @@
         <v>5.7014</v>
       </c>
       <c r="C5" t="n">
-        <v>0</v>
+        <v>3.7073</v>
       </c>
       <c r="D5" t="n">
         <v>1.8819</v>
@@ -683,7 +683,7 @@
         <v>5.6975</v>
       </c>
       <c r="C6" t="n">
-        <v>0</v>
+        <v>3.7047</v>
       </c>
       <c r="D6" t="n">
         <v>1.8803</v>
@@ -729,7 +729,7 @@
         <v>4.9691</v>
       </c>
       <c r="C7" t="n">
-        <v>0</v>
+        <v>3.2311</v>
       </c>
       <c r="D7" t="n">
         <v>1.586</v>
@@ -775,7 +775,7 @@
         <v>4.5383</v>
       </c>
       <c r="C8" t="n">
-        <v>0</v>
+        <v>2.951</v>
       </c>
       <c r="D8" t="n">
         <v>1.412</v>
@@ -821,7 +821,7 @@
         <v>4.5256</v>
       </c>
       <c r="C9" t="n">
-        <v>0</v>
+        <v>2.9427</v>
       </c>
       <c r="D9" t="n">
         <v>1.4069</v>
@@ -867,7 +867,7 @@
         <v>3.9558</v>
       </c>
       <c r="C10" t="n">
-        <v>0</v>
+        <v>2.5722</v>
       </c>
       <c r="D10" t="n">
         <v>1.1767</v>
@@ -913,7 +913,7 @@
         <v>3.8757</v>
       </c>
       <c r="C11" t="n">
-        <v>0</v>
+        <v>2.5201</v>
       </c>
       <c r="D11" t="n">
         <v>1.1443</v>
@@ -959,7 +959,7 @@
         <v>3.7821</v>
       </c>
       <c r="C12" t="n">
-        <v>0</v>
+        <v>2.4593</v>
       </c>
       <c r="D12" t="n">
         <v>1.1065</v>
@@ -1005,7 +1005,7 @@
         <v>3.4703</v>
       </c>
       <c r="C13" t="n">
-        <v>0</v>
+        <v>2.2565</v>
       </c>
       <c r="D13" t="n">
         <v>0.9806</v>
@@ -1051,7 +1051,7 @@
         <v>3.2944</v>
       </c>
       <c r="C14" t="n">
-        <v>0</v>
+        <v>2.1422</v>
       </c>
       <c r="D14" t="n">
         <v>0.9095</v>
@@ -1097,7 +1097,7 @@
         <v>2.994</v>
       </c>
       <c r="C15" t="n">
-        <v>0</v>
+        <v>1.9468</v>
       </c>
       <c r="D15" t="n">
         <v>0.7881</v>
@@ -1143,7 +1143,7 @@
         <v>2.9482</v>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>1.917</v>
       </c>
       <c r="D16" t="n">
         <v>0.7696</v>
@@ -1189,7 +1189,7 @@
         <v>2.8986</v>
       </c>
       <c r="C17" t="n">
-        <v>0</v>
+        <v>1.8848</v>
       </c>
       <c r="D17" t="n">
         <v>0.7496</v>
@@ -1235,7 +1235,7 @@
         <v>2.882</v>
       </c>
       <c r="C18" t="n">
-        <v>0</v>
+        <v>1.874</v>
       </c>
       <c r="D18" t="n">
         <v>0.7429</v>
@@ -1281,7 +1281,7 @@
         <v>2.8019</v>
       </c>
       <c r="C19" t="n">
-        <v>0</v>
+        <v>1.8219</v>
       </c>
       <c r="D19" t="n">
         <v>0.7105</v>
@@ -1327,7 +1327,7 @@
         <v>2.7893</v>
       </c>
       <c r="C20" t="n">
-        <v>0</v>
+        <v>1.8137</v>
       </c>
       <c r="D20" t="n">
         <v>0.7055</v>
@@ -1373,7 +1373,7 @@
         <v>2.7473</v>
       </c>
       <c r="C21" t="n">
-        <v>0</v>
+        <v>1.7864</v>
       </c>
       <c r="D21" t="n">
         <v>0.6885</v>
@@ -1419,7 +1419,7 @@
         <v>2.6832</v>
       </c>
       <c r="C22" t="n">
-        <v>0</v>
+        <v>1.7447</v>
       </c>
       <c r="D22" t="n">
         <v>0.6626</v>
@@ -1465,7 +1465,7 @@
         <v>2.291</v>
       </c>
       <c r="C23" t="n">
-        <v>0</v>
+        <v>1.4897</v>
       </c>
       <c r="D23" t="n">
         <v>0.5042</v>
@@ -1511,7 +1511,7 @@
         <v>2.0439</v>
       </c>
       <c r="C24" t="n">
-        <v>0</v>
+        <v>1.329</v>
       </c>
       <c r="D24" t="n">
         <v>0.4043</v>
@@ -1557,7 +1557,7 @@
         <v>1.9794</v>
       </c>
       <c r="C25" t="n">
-        <v>0</v>
+        <v>1.2871</v>
       </c>
       <c r="D25" t="n">
         <v>0.3783</v>
@@ -1603,7 +1603,7 @@
         <v>1.7341</v>
       </c>
       <c r="C26" t="n">
-        <v>0</v>
+        <v>1.1276</v>
       </c>
       <c r="D26" t="n">
         <v>0.2792</v>
@@ -1649,7 +1649,7 @@
         <v>1.7015</v>
       </c>
       <c r="C27" t="n">
-        <v>0</v>
+        <v>1.1064</v>
       </c>
       <c r="D27" t="n">
         <v>0.266</v>
@@ -1695,7 +1695,7 @@
         <v>1.6964</v>
       </c>
       <c r="C28" t="n">
-        <v>0</v>
+        <v>1.1031</v>
       </c>
       <c r="D28" t="n">
         <v>0.2639</v>
@@ -1741,7 +1741,7 @@
         <v>1.4662</v>
       </c>
       <c r="C29" t="n">
-        <v>0</v>
+        <v>0.9534</v>
       </c>
       <c r="D29" t="n">
         <v>0.171</v>
@@ -1787,7 +1787,7 @@
         <v>1.3473</v>
       </c>
       <c r="C30" t="n">
-        <v>0</v>
+        <v>0.8761</v>
       </c>
       <c r="D30" t="n">
         <v>0.1229</v>
@@ -1833,7 +1833,7 @@
         <v>1.314</v>
       </c>
       <c r="C31" t="n">
-        <v>0</v>
+        <v>0.8544</v>
       </c>
       <c r="D31" t="n">
         <v>0.1095</v>
@@ -1879,7 +1879,7 @@
         <v>1.2185</v>
       </c>
       <c r="C32" t="n">
-        <v>0</v>
+        <v>0.7923</v>
       </c>
       <c r="D32" t="n">
         <v>0.0709</v>
@@ -1925,7 +1925,7 @@
         <v>1.177</v>
       </c>
       <c r="C33" t="n">
-        <v>0</v>
+        <v>0.7653</v>
       </c>
       <c r="D33" t="n">
         <v>0.0541</v>
@@ -1971,7 +1971,7 @@
         <v>0.9573</v>
       </c>
       <c r="C34" t="n">
-        <v>0</v>
+        <v>0.6225000000000001</v>
       </c>
       <c r="D34" t="n">
         <v>-0.0346</v>
@@ -2017,7 +2017,7 @@
         <v>0.9463</v>
       </c>
       <c r="C35" t="n">
-        <v>0</v>
+        <v>0.6153</v>
       </c>
       <c r="D35" t="n">
         <v>-0.0391</v>
@@ -2063,7 +2063,7 @@
         <v>0.8845</v>
       </c>
       <c r="C36" t="n">
-        <v>0</v>
+        <v>0.5750999999999999</v>
       </c>
       <c r="D36" t="n">
         <v>-0.064</v>
@@ -2109,7 +2109,7 @@
         <v>0.8375</v>
       </c>
       <c r="C37" t="n">
-        <v>0</v>
+        <v>0.5446</v>
       </c>
       <c r="D37" t="n">
         <v>-0.083</v>
@@ -2155,7 +2155,7 @@
         <v>0.7481</v>
       </c>
       <c r="C38" t="n">
-        <v>0</v>
+        <v>0.4864</v>
       </c>
       <c r="D38" t="n">
         <v>-0.1191</v>
@@ -2201,7 +2201,7 @@
         <v>0.701</v>
       </c>
       <c r="C39" t="n">
-        <v>0</v>
+        <v>0.4558</v>
       </c>
       <c r="D39" t="n">
         <v>-0.1382</v>
@@ -2247,7 +2247,7 @@
         <v>0.6912</v>
       </c>
       <c r="C40" t="n">
-        <v>0</v>
+        <v>0.4494</v>
       </c>
       <c r="D40" t="n">
         <v>-0.1421</v>
@@ -2293,7 +2293,7 @@
         <v>0.6882</v>
       </c>
       <c r="C41" t="n">
-        <v>0</v>
+        <v>0.4475</v>
       </c>
       <c r="D41" t="n">
         <v>-0.1433</v>
@@ -2339,7 +2339,7 @@
         <v>0.6838</v>
       </c>
       <c r="C42" t="n">
-        <v>0</v>
+        <v>0.4446</v>
       </c>
       <c r="D42" t="n">
         <v>-0.1451</v>
@@ -2385,7 +2385,7 @@
         <v>0.6127</v>
       </c>
       <c r="C43" t="n">
-        <v>0</v>
+        <v>0.3984</v>
       </c>
       <c r="D43" t="n">
         <v>-0.1738</v>
@@ -2431,7 +2431,7 @@
         <v>0.4793</v>
       </c>
       <c r="C44" t="n">
-        <v>0</v>
+        <v>0.3117</v>
       </c>
       <c r="D44" t="n">
         <v>-0.2277</v>
@@ -2477,7 +2477,7 @@
         <v>0.4571</v>
       </c>
       <c r="C45" t="n">
-        <v>0</v>
+        <v>0.2972</v>
       </c>
       <c r="D45" t="n">
         <v>-0.2367</v>
@@ -2523,7 +2523,7 @@
         <v>0.4327</v>
       </c>
       <c r="C46" t="n">
-        <v>0</v>
+        <v>0.2814</v>
       </c>
       <c r="D46" t="n">
         <v>-0.2466</v>
@@ -2569,7 +2569,7 @@
         <v>0.3297</v>
       </c>
       <c r="C47" t="n">
-        <v>0</v>
+        <v>0.2144</v>
       </c>
       <c r="D47" t="n">
         <v>-0.2882</v>
@@ -2615,7 +2615,7 @@
         <v>0.1112</v>
       </c>
       <c r="C48" t="n">
-        <v>0</v>
+        <v>0.0723</v>
       </c>
       <c r="D48" t="n">
         <v>-0.3764</v>
@@ -2661,7 +2661,7 @@
         <v>0.08550000000000001</v>
       </c>
       <c r="C49" t="n">
-        <v>0</v>
+        <v>0.0556</v>
       </c>
       <c r="D49" t="n">
         <v>-0.3868</v>
@@ -2707,7 +2707,7 @@
         <v>0.0347</v>
       </c>
       <c r="C50" t="n">
-        <v>0</v>
+        <v>0.0226</v>
       </c>
       <c r="D50" t="n">
         <v>-0.4073</v>
@@ -2753,7 +2753,7 @@
         <v>0.0189</v>
       </c>
       <c r="C51" t="n">
-        <v>0</v>
+        <v>0.0123</v>
       </c>
       <c r="D51" t="n">
         <v>-0.4137</v>
@@ -2799,7 +2799,7 @@
         <v>0.0147</v>
       </c>
       <c r="C52" t="n">
-        <v>0</v>
+        <v>0.009599999999999999</v>
       </c>
       <c r="D52" t="n">
         <v>-0.4154</v>
@@ -2845,7 +2845,7 @@
         <v>-0.004</v>
       </c>
       <c r="C53" t="n">
-        <v>-0</v>
+        <v>-0.0026</v>
       </c>
       <c r="D53" t="n">
         <v>-0.423</v>
@@ -2891,7 +2891,7 @@
         <v>-0.0046</v>
       </c>
       <c r="C54" t="n">
-        <v>-0</v>
+        <v>-0.003</v>
       </c>
       <c r="D54" t="n">
         <v>-0.4232</v>
@@ -2937,7 +2937,7 @@
         <v>-0.0425</v>
       </c>
       <c r="C55" t="n">
-        <v>-0</v>
+        <v>-0.0276</v>
       </c>
       <c r="D55" t="n">
         <v>-0.4385</v>
@@ -2983,7 +2983,7 @@
         <v>-0.0723</v>
       </c>
       <c r="C56" t="n">
-        <v>-0</v>
+        <v>-0.047</v>
       </c>
       <c r="D56" t="n">
         <v>-0.4506</v>
@@ -3029,7 +3029,7 @@
         <v>-0.1632</v>
       </c>
       <c r="C57" t="n">
-        <v>-0</v>
+        <v>-0.1061</v>
       </c>
       <c r="D57" t="n">
         <v>-0.4873</v>
@@ -3075,7 +3075,7 @@
         <v>-0.2611</v>
       </c>
       <c r="C58" t="n">
-        <v>-0</v>
+        <v>-0.1698</v>
       </c>
       <c r="D58" t="n">
         <v>-0.5268</v>
@@ -3121,7 +3121,7 @@
         <v>-0.318</v>
       </c>
       <c r="C59" t="n">
-        <v>-0</v>
+        <v>-0.2068</v>
       </c>
       <c r="D59" t="n">
         <v>-0.5498</v>
@@ -3167,7 +3167,7 @@
         <v>-0.3748</v>
       </c>
       <c r="C60" t="n">
-        <v>-0</v>
+        <v>-0.2437</v>
       </c>
       <c r="D60" t="n">
         <v>-0.5728</v>
@@ -3213,7 +3213,7 @@
         <v>-0.6744</v>
       </c>
       <c r="C61" t="n">
-        <v>-0</v>
+        <v>-0.4385</v>
       </c>
       <c r="D61" t="n">
         <v>-0.6938</v>
@@ -3259,7 +3259,7 @@
         <v>-0.7255</v>
       </c>
       <c r="C62" t="n">
-        <v>-0</v>
+        <v>-0.4717</v>
       </c>
       <c r="D62" t="n">
         <v>-0.7144</v>
@@ -3305,7 +3305,7 @@
         <v>-0.7313</v>
       </c>
       <c r="C63" t="n">
-        <v>-0</v>
+        <v>-0.4755</v>
       </c>
       <c r="D63" t="n">
         <v>-0.7168</v>
@@ -3351,7 +3351,7 @@
         <v>-0.8459</v>
       </c>
       <c r="C64" t="n">
-        <v>-0</v>
+        <v>-0.55</v>
       </c>
       <c r="D64" t="n">
         <v>-0.7631</v>
@@ -3397,7 +3397,7 @@
         <v>-0.8686</v>
       </c>
       <c r="C65" t="n">
-        <v>-0</v>
+        <v>-0.5648</v>
       </c>
       <c r="D65" t="n">
         <v>-0.7723</v>
@@ -3443,7 +3443,7 @@
         <v>-0.8851</v>
       </c>
       <c r="C66" t="n">
-        <v>-0</v>
+        <v>-0.5755</v>
       </c>
       <c r="D66" t="n">
         <v>-0.7789</v>
@@ -3489,7 +3489,7 @@
         <v>-0.9142</v>
       </c>
       <c r="C67" t="n">
-        <v>-0</v>
+        <v>-0.5944</v>
       </c>
       <c r="D67" t="n">
         <v>-0.7907</v>
@@ -3535,7 +3535,7 @@
         <v>-0.9201</v>
       </c>
       <c r="C68" t="n">
-        <v>-0</v>
+        <v>-0.5983000000000001</v>
       </c>
       <c r="D68" t="n">
         <v>-0.7931</v>
@@ -3581,7 +3581,7 @@
         <v>-1.0186</v>
       </c>
       <c r="C69" t="n">
-        <v>-0</v>
+        <v>-0.6623</v>
       </c>
       <c r="D69" t="n">
         <v>-0.8329</v>
@@ -3627,7 +3627,7 @@
         <v>-1.0443</v>
       </c>
       <c r="C70" t="n">
-        <v>-0</v>
+        <v>-0.679</v>
       </c>
       <c r="D70" t="n">
         <v>-0.8431999999999999</v>
@@ -3673,7 +3673,7 @@
         <v>-1.0481</v>
       </c>
       <c r="C71" t="n">
-        <v>-0</v>
+        <v>-0.6815</v>
       </c>
       <c r="D71" t="n">
         <v>-0.8448</v>
@@ -3719,7 +3719,7 @@
         <v>-1.061</v>
       </c>
       <c r="C72" t="n">
-        <v>-0</v>
+        <v>-0.6899</v>
       </c>
       <c r="D72" t="n">
         <v>-0.85</v>
@@ -3765,7 +3765,7 @@
         <v>-1.1541</v>
       </c>
       <c r="C73" t="n">
-        <v>-0</v>
+        <v>-0.7504</v>
       </c>
       <c r="D73" t="n">
         <v>-0.8875999999999999</v>
@@ -3811,7 +3811,7 @@
         <v>-1.1753</v>
       </c>
       <c r="C74" t="n">
-        <v>-0</v>
+        <v>-0.7642</v>
       </c>
       <c r="D74" t="n">
         <v>-0.8962</v>
@@ -3857,7 +3857,7 @@
         <v>-1.2132</v>
       </c>
       <c r="C75" t="n">
-        <v>-0</v>
+        <v>-0.7889</v>
       </c>
       <c r="D75" t="n">
         <v>-0.9115</v>
@@ -3903,7 +3903,7 @@
         <v>-1.4458</v>
       </c>
       <c r="C76" t="n">
-        <v>-0</v>
+        <v>-0.9401</v>
       </c>
       <c r="D76" t="n">
         <v>-1.0054</v>
@@ -3949,7 +3949,7 @@
         <v>-1.6855</v>
       </c>
       <c r="C77" t="n">
-        <v>-0</v>
+        <v>-1.096</v>
       </c>
       <c r="D77" t="n">
         <v>-1.1023</v>
@@ -3995,7 +3995,7 @@
         <v>-1.8121</v>
       </c>
       <c r="C78" t="n">
-        <v>-0</v>
+        <v>-1.1783</v>
       </c>
       <c r="D78" t="n">
         <v>-1.1534</v>
@@ -4041,7 +4041,7 @@
         <v>-1.8421</v>
       </c>
       <c r="C79" t="n">
-        <v>-0</v>
+        <v>-1.1978</v>
       </c>
       <c r="D79" t="n">
         <v>-1.1655</v>
@@ -4087,7 +4087,7 @@
         <v>-1.9432</v>
       </c>
       <c r="C80" t="n">
-        <v>-0</v>
+        <v>-1.2635</v>
       </c>
       <c r="D80" t="n">
         <v>-1.2064</v>
@@ -4133,7 +4133,7 @@
         <v>-2.1733</v>
       </c>
       <c r="C81" t="n">
-        <v>-0</v>
+        <v>-1.4132</v>
       </c>
       <c r="D81" t="n">
         <v>-1.2993</v>
@@ -4179,7 +4179,7 @@
         <v>-3.4854</v>
       </c>
       <c r="C82" t="n">
-        <v>-0</v>
+        <v>-2.2663</v>
       </c>
       <c r="D82" t="n">
         <v>-1.8294</v>

--- a/database/event/8034/event_8034_evp_summary.xlsx
+++ b/database/event/8034/event_8034_evp_summary.xlsx
@@ -496,25 +496,25 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>10.9162</v>
+        <v>10.8046</v>
       </c>
       <c r="C2" t="n">
-        <v>7.0982</v>
+        <v>7.0256</v>
       </c>
       <c r="D2" t="n">
-        <v>3.9885</v>
+        <v>3.8606</v>
       </c>
       <c r="E2" t="n">
-        <v>10.9162</v>
+        <v>10.8046</v>
       </c>
       <c r="F2" t="n">
-        <v>5.7906</v>
+        <v>5.679</v>
       </c>
       <c r="G2" t="n">
         <v>5.1256</v>
       </c>
       <c r="H2" t="n">
-        <v>6.7766</v>
+        <v>6.6016</v>
       </c>
       <c r="I2" t="n">
         <v>7.0005</v>
@@ -548,7 +548,7 @@
         <v>6.7754</v>
       </c>
       <c r="D3" t="n">
-        <v>3.788</v>
+        <v>3.7074</v>
       </c>
       <c r="E3" t="n">
         <v>10.4199</v>
@@ -594,7 +594,7 @@
         <v>4.5998</v>
       </c>
       <c r="D4" t="n">
-        <v>2.4364</v>
+        <v>2.3744</v>
       </c>
       <c r="E4" t="n">
         <v>7.074</v>
@@ -640,7 +640,7 @@
         <v>3.7073</v>
       </c>
       <c r="D5" t="n">
-        <v>1.8819</v>
+        <v>1.8275</v>
       </c>
       <c r="E5" t="n">
         <v>5.7014</v>
@@ -680,25 +680,25 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5.6975</v>
+        <v>5.6409</v>
       </c>
       <c r="C6" t="n">
-        <v>3.7047</v>
+        <v>3.6679</v>
       </c>
       <c r="D6" t="n">
-        <v>1.8803</v>
+        <v>1.8034</v>
       </c>
       <c r="E6" t="n">
-        <v>5.6975</v>
+        <v>5.6409</v>
       </c>
       <c r="F6" t="n">
-        <v>2.1887</v>
+        <v>2.1322</v>
       </c>
       <c r="G6" t="n">
         <v>3.5088</v>
       </c>
       <c r="H6" t="n">
-        <v>2.1887</v>
+        <v>2.1322</v>
       </c>
       <c r="I6" t="n">
         <v>2.261</v>
@@ -732,7 +732,7 @@
         <v>3.2311</v>
       </c>
       <c r="D7" t="n">
-        <v>1.586</v>
+        <v>1.5358</v>
       </c>
       <c r="E7" t="n">
         <v>4.9691</v>
@@ -778,7 +778,7 @@
         <v>2.951</v>
       </c>
       <c r="D8" t="n">
-        <v>1.412</v>
+        <v>1.3641</v>
       </c>
       <c r="E8" t="n">
         <v>4.5383</v>
@@ -824,7 +824,7 @@
         <v>2.9427</v>
       </c>
       <c r="D9" t="n">
-        <v>1.4069</v>
+        <v>1.3591</v>
       </c>
       <c r="E9" t="n">
         <v>4.5256</v>
@@ -870,7 +870,7 @@
         <v>2.5722</v>
       </c>
       <c r="D10" t="n">
-        <v>1.1767</v>
+        <v>1.1321</v>
       </c>
       <c r="E10" t="n">
         <v>3.9558</v>
@@ -916,7 +916,7 @@
         <v>2.5201</v>
       </c>
       <c r="D11" t="n">
-        <v>1.1443</v>
+        <v>1.1002</v>
       </c>
       <c r="E11" t="n">
         <v>3.8757</v>
@@ -956,25 +956,25 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3.7821</v>
+        <v>3.6944</v>
       </c>
       <c r="C12" t="n">
-        <v>2.4593</v>
+        <v>2.4022</v>
       </c>
       <c r="D12" t="n">
-        <v>1.1065</v>
+        <v>1.0279</v>
       </c>
       <c r="E12" t="n">
-        <v>3.7821</v>
+        <v>3.6944</v>
       </c>
       <c r="F12" t="n">
-        <v>3.3962</v>
+        <v>3.3085</v>
       </c>
       <c r="G12" t="n">
         <v>0.3859</v>
       </c>
       <c r="H12" t="n">
-        <v>3.3962</v>
+        <v>3.3085</v>
       </c>
       <c r="I12" t="n">
         <v>3.5084</v>
@@ -1002,25 +1002,25 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>3.4703</v>
+        <v>3.3986</v>
       </c>
       <c r="C13" t="n">
-        <v>2.2565</v>
+        <v>2.2099</v>
       </c>
       <c r="D13" t="n">
-        <v>0.9806</v>
+        <v>0.9101</v>
       </c>
       <c r="E13" t="n">
-        <v>3.4703</v>
+        <v>3.3986</v>
       </c>
       <c r="F13" t="n">
-        <v>2.7742</v>
+        <v>2.7025</v>
       </c>
       <c r="G13" t="n">
         <v>0.6961000000000001</v>
       </c>
       <c r="H13" t="n">
-        <v>2.7742</v>
+        <v>2.7025</v>
       </c>
       <c r="I13" t="n">
         <v>2.8658</v>
@@ -1054,7 +1054,7 @@
         <v>2.1422</v>
       </c>
       <c r="D14" t="n">
-        <v>0.9095</v>
+        <v>0.8686</v>
       </c>
       <c r="E14" t="n">
         <v>3.2944</v>
@@ -1094,25 +1094,25 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2.994</v>
+        <v>2.9541</v>
       </c>
       <c r="C15" t="n">
-        <v>1.9468</v>
+        <v>1.9209</v>
       </c>
       <c r="D15" t="n">
-        <v>0.7881</v>
+        <v>0.733</v>
       </c>
       <c r="E15" t="n">
-        <v>2.994</v>
+        <v>2.9541</v>
       </c>
       <c r="F15" t="n">
-        <v>1.5459</v>
+        <v>1.506</v>
       </c>
       <c r="G15" t="n">
         <v>1.4481</v>
       </c>
       <c r="H15" t="n">
-        <v>1.5459</v>
+        <v>1.506</v>
       </c>
       <c r="I15" t="n">
         <v>1.597</v>
@@ -1140,25 +1140,25 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2.9482</v>
+        <v>2.8936</v>
       </c>
       <c r="C16" t="n">
-        <v>1.917</v>
+        <v>1.8815</v>
       </c>
       <c r="D16" t="n">
-        <v>0.7696</v>
+        <v>0.7089</v>
       </c>
       <c r="E16" t="n">
-        <v>2.9482</v>
+        <v>2.8936</v>
       </c>
       <c r="F16" t="n">
-        <v>2.9482</v>
+        <v>2.8936</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>2.9482</v>
+        <v>2.8936</v>
       </c>
       <c r="I16" t="n">
         <v>3.0174</v>
@@ -1182,93 +1182,93 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>frozen</t>
+          <t>NertZ</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2.8986</v>
+        <v>2.8499</v>
       </c>
       <c r="C17" t="n">
-        <v>1.8848</v>
+        <v>1.8531</v>
       </c>
       <c r="D17" t="n">
-        <v>0.7496</v>
+        <v>0.6915</v>
       </c>
       <c r="E17" t="n">
-        <v>2.8986</v>
+        <v>2.8499</v>
       </c>
       <c r="F17" t="n">
-        <v>2.8986</v>
+        <v>2.8499</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>2.8986</v>
+        <v>2.8499</v>
       </c>
       <c r="I17" t="n">
-        <v>2.9667</v>
+        <v>2.9224</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>276</v>
+        <v>152</v>
       </c>
       <c r="L17" t="n">
         <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>2.9667</v>
+        <v>2.9224</v>
       </c>
       <c r="N17" t="n">
-        <v>276</v>
+        <v>152</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>NertZ</t>
+          <t>frozen</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2.882</v>
+        <v>2.8449</v>
       </c>
       <c r="C18" t="n">
-        <v>1.874</v>
+        <v>1.8499</v>
       </c>
       <c r="D18" t="n">
-        <v>0.7429</v>
+        <v>0.6895</v>
       </c>
       <c r="E18" t="n">
-        <v>2.882</v>
+        <v>2.8449</v>
       </c>
       <c r="F18" t="n">
-        <v>2.882</v>
+        <v>2.8449</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>2.882</v>
+        <v>2.8449</v>
       </c>
       <c r="I18" t="n">
-        <v>2.9224</v>
+        <v>2.9667</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>152</v>
+        <v>276</v>
       </c>
       <c r="L18" t="n">
         <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>2.9224</v>
+        <v>2.9667</v>
       </c>
       <c r="N18" t="n">
-        <v>152</v>
+        <v>276</v>
       </c>
     </row>
     <row r="19">
@@ -1278,25 +1278,25 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>2.8019</v>
+        <v>2.7707</v>
       </c>
       <c r="C19" t="n">
-        <v>1.8219</v>
+        <v>1.8016</v>
       </c>
       <c r="D19" t="n">
-        <v>0.7105</v>
+        <v>0.6599</v>
       </c>
       <c r="E19" t="n">
-        <v>2.8019</v>
+        <v>2.7707</v>
       </c>
       <c r="F19" t="n">
-        <v>2.1013</v>
+        <v>2.0701</v>
       </c>
       <c r="G19" t="n">
         <v>0.7006</v>
       </c>
       <c r="H19" t="n">
-        <v>2.1013</v>
+        <v>2.0701</v>
       </c>
       <c r="I19" t="n">
         <v>2.1407</v>
@@ -1320,93 +1320,93 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>woxic</t>
+          <t>bLitz</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>2.7893</v>
+        <v>2.746</v>
       </c>
       <c r="C20" t="n">
-        <v>1.8137</v>
+        <v>1.7856</v>
       </c>
       <c r="D20" t="n">
-        <v>0.7055</v>
+        <v>0.6501</v>
       </c>
       <c r="E20" t="n">
-        <v>2.7893</v>
+        <v>2.746</v>
       </c>
       <c r="F20" t="n">
-        <v>3.2711</v>
+        <v>0.0853</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.4818</v>
+        <v>2.6607</v>
       </c>
       <c r="H20" t="n">
-        <v>3.2711</v>
+        <v>0.0853</v>
       </c>
       <c r="I20" t="n">
-        <v>3.3792</v>
+        <v>0.0882</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.4818</v>
+        <v>2.6607</v>
       </c>
       <c r="K20" t="n">
-        <v>245</v>
+        <v>147</v>
       </c>
       <c r="L20" t="n">
-        <v>60</v>
+        <v>102</v>
       </c>
       <c r="M20" t="n">
-        <v>2.8974</v>
+        <v>2.7489</v>
       </c>
       <c r="N20" t="n">
-        <v>305</v>
+        <v>249</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>bLitz</t>
+          <t>woxic</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>2.7473</v>
+        <v>2.7049</v>
       </c>
       <c r="C21" t="n">
-        <v>1.7864</v>
+        <v>1.7588</v>
       </c>
       <c r="D21" t="n">
-        <v>0.6885</v>
+        <v>0.6337</v>
       </c>
       <c r="E21" t="n">
-        <v>2.7473</v>
+        <v>2.7049</v>
       </c>
       <c r="F21" t="n">
-        <v>0.0866</v>
+        <v>3.1867</v>
       </c>
       <c r="G21" t="n">
-        <v>2.6607</v>
+        <v>-0.4818</v>
       </c>
       <c r="H21" t="n">
-        <v>0.0866</v>
+        <v>3.1867</v>
       </c>
       <c r="I21" t="n">
-        <v>0.0882</v>
+        <v>3.3792</v>
       </c>
       <c r="J21" t="n">
-        <v>2.6607</v>
+        <v>-0.4818</v>
       </c>
       <c r="K21" t="n">
-        <v>147</v>
+        <v>245</v>
       </c>
       <c r="L21" t="n">
-        <v>102</v>
+        <v>60</v>
       </c>
       <c r="M21" t="n">
-        <v>2.7489</v>
+        <v>2.8974</v>
       </c>
       <c r="N21" t="n">
-        <v>249</v>
+        <v>305</v>
       </c>
     </row>
     <row r="22">
@@ -1416,25 +1416,25 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>2.6832</v>
+        <v>2.6109</v>
       </c>
       <c r="C22" t="n">
-        <v>1.7447</v>
+        <v>1.6977</v>
       </c>
       <c r="D22" t="n">
-        <v>0.6626</v>
+        <v>0.5963000000000001</v>
       </c>
       <c r="E22" t="n">
-        <v>2.6832</v>
+        <v>2.6109</v>
       </c>
       <c r="F22" t="n">
-        <v>2.7998</v>
+        <v>2.7275</v>
       </c>
       <c r="G22" t="n">
         <v>-0.1166</v>
       </c>
       <c r="H22" t="n">
-        <v>2.7998</v>
+        <v>2.7275</v>
       </c>
       <c r="I22" t="n">
         <v>2.8923</v>
@@ -1462,25 +1462,25 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>2.291</v>
+        <v>2.2569</v>
       </c>
       <c r="C23" t="n">
-        <v>1.4897</v>
+        <v>1.4675</v>
       </c>
       <c r="D23" t="n">
-        <v>0.5042</v>
+        <v>0.4552</v>
       </c>
       <c r="E23" t="n">
-        <v>2.291</v>
+        <v>2.2569</v>
       </c>
       <c r="F23" t="n">
-        <v>2.3025</v>
+        <v>2.2684</v>
       </c>
       <c r="G23" t="n">
         <v>-0.0115</v>
       </c>
       <c r="H23" t="n">
-        <v>2.3025</v>
+        <v>2.2684</v>
       </c>
       <c r="I23" t="n">
         <v>2.3457</v>
@@ -1508,25 +1508,25 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>2.0439</v>
+        <v>2.0061</v>
       </c>
       <c r="C24" t="n">
-        <v>1.329</v>
+        <v>1.3044</v>
       </c>
       <c r="D24" t="n">
-        <v>0.4043</v>
+        <v>0.3553</v>
       </c>
       <c r="E24" t="n">
-        <v>2.0439</v>
+        <v>2.0061</v>
       </c>
       <c r="F24" t="n">
-        <v>2.0439</v>
+        <v>2.0061</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>2.0439</v>
+        <v>2.0061</v>
       </c>
       <c r="I24" t="n">
         <v>2.0919</v>
@@ -1554,25 +1554,25 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>1.9794</v>
+        <v>1.9573</v>
       </c>
       <c r="C25" t="n">
-        <v>1.2871</v>
+        <v>1.2727</v>
       </c>
       <c r="D25" t="n">
-        <v>0.3783</v>
+        <v>0.3359</v>
       </c>
       <c r="E25" t="n">
-        <v>1.9794</v>
+        <v>1.9573</v>
       </c>
       <c r="F25" t="n">
-        <v>1.9794</v>
+        <v>1.9573</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>1.9794</v>
+        <v>1.9573</v>
       </c>
       <c r="I25" t="n">
         <v>2.0072</v>
@@ -1600,25 +1600,25 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>1.7341</v>
+        <v>1.7147</v>
       </c>
       <c r="C26" t="n">
-        <v>1.1276</v>
+        <v>1.115</v>
       </c>
       <c r="D26" t="n">
-        <v>0.2792</v>
+        <v>0.2392</v>
       </c>
       <c r="E26" t="n">
-        <v>1.7341</v>
+        <v>1.7147</v>
       </c>
       <c r="F26" t="n">
-        <v>1.7341</v>
+        <v>1.7147</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>1.7341</v>
+        <v>1.7147</v>
       </c>
       <c r="I26" t="n">
         <v>1.7584</v>
@@ -1646,25 +1646,25 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>1.7015</v>
+        <v>1.6826</v>
       </c>
       <c r="C27" t="n">
-        <v>1.1064</v>
+        <v>1.0941</v>
       </c>
       <c r="D27" t="n">
-        <v>0.266</v>
+        <v>0.2264</v>
       </c>
       <c r="E27" t="n">
-        <v>1.7015</v>
+        <v>1.6826</v>
       </c>
       <c r="F27" t="n">
-        <v>1.7015</v>
+        <v>1.6826</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>1.7015</v>
+        <v>1.6826</v>
       </c>
       <c r="I27" t="n">
         <v>1.7254</v>
@@ -1692,25 +1692,25 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>1.6964</v>
+        <v>1.6774</v>
       </c>
       <c r="C28" t="n">
-        <v>1.1031</v>
+        <v>1.0907</v>
       </c>
       <c r="D28" t="n">
-        <v>0.2639</v>
+        <v>0.2244</v>
       </c>
       <c r="E28" t="n">
-        <v>1.6964</v>
+        <v>1.6774</v>
       </c>
       <c r="F28" t="n">
-        <v>1.6964</v>
+        <v>1.6774</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>1.6964</v>
+        <v>1.6774</v>
       </c>
       <c r="I28" t="n">
         <v>1.7201</v>
@@ -1738,25 +1738,25 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>1.4662</v>
+        <v>1.4107</v>
       </c>
       <c r="C29" t="n">
-        <v>0.9534</v>
+        <v>0.9173</v>
       </c>
       <c r="D29" t="n">
-        <v>0.171</v>
+        <v>0.1181</v>
       </c>
       <c r="E29" t="n">
-        <v>1.4662</v>
+        <v>1.4107</v>
       </c>
       <c r="F29" t="n">
-        <v>2.1488</v>
+        <v>2.0933</v>
       </c>
       <c r="G29" t="n">
         <v>-0.6826</v>
       </c>
       <c r="H29" t="n">
-        <v>2.1488</v>
+        <v>2.0933</v>
       </c>
       <c r="I29" t="n">
         <v>2.2198</v>
@@ -1784,25 +1784,25 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>1.3473</v>
+        <v>1.3224</v>
       </c>
       <c r="C30" t="n">
-        <v>0.8761</v>
+        <v>0.8599</v>
       </c>
       <c r="D30" t="n">
-        <v>0.1229</v>
+        <v>0.0829</v>
       </c>
       <c r="E30" t="n">
-        <v>1.3473</v>
+        <v>1.3224</v>
       </c>
       <c r="F30" t="n">
-        <v>1.3473</v>
+        <v>1.3224</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>1.3473</v>
+        <v>1.3224</v>
       </c>
       <c r="I30" t="n">
         <v>1.379</v>
@@ -1836,7 +1836,7 @@
         <v>0.8544</v>
       </c>
       <c r="D31" t="n">
-        <v>0.1095</v>
+        <v>0.0796</v>
       </c>
       <c r="E31" t="n">
         <v>1.314</v>
@@ -1876,25 +1876,25 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>1.2185</v>
+        <v>1.214</v>
       </c>
       <c r="C32" t="n">
-        <v>0.7923</v>
+        <v>0.7894</v>
       </c>
       <c r="D32" t="n">
-        <v>0.0709</v>
+        <v>0.0397</v>
       </c>
       <c r="E32" t="n">
-        <v>1.2185</v>
+        <v>1.214</v>
       </c>
       <c r="F32" t="n">
-        <v>1.2185</v>
+        <v>1.214</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>1.2185</v>
+        <v>1.214</v>
       </c>
       <c r="I32" t="n">
         <v>1.2242</v>
@@ -1922,25 +1922,25 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>1.177</v>
+        <v>1.1639</v>
       </c>
       <c r="C33" t="n">
-        <v>0.7653</v>
+        <v>0.7568</v>
       </c>
       <c r="D33" t="n">
-        <v>0.0541</v>
+        <v>0.0198</v>
       </c>
       <c r="E33" t="n">
-        <v>1.177</v>
+        <v>1.1639</v>
       </c>
       <c r="F33" t="n">
-        <v>1.177</v>
+        <v>1.1639</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>1.177</v>
+        <v>1.1639</v>
       </c>
       <c r="I33" t="n">
         <v>1.1935</v>
@@ -1968,25 +1968,25 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.9573</v>
+        <v>0.9431</v>
       </c>
       <c r="C34" t="n">
-        <v>0.6225000000000001</v>
+        <v>0.6132</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.0346</v>
+        <v>-0.0682</v>
       </c>
       <c r="E34" t="n">
-        <v>0.9573</v>
+        <v>0.9431</v>
       </c>
       <c r="F34" t="n">
-        <v>0.9573</v>
+        <v>0.9431</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>0.9573</v>
+        <v>0.9431</v>
       </c>
       <c r="I34" t="n">
         <v>0.9752999999999999</v>
@@ -2014,25 +2014,25 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.9463</v>
+        <v>0.9358</v>
       </c>
       <c r="C35" t="n">
-        <v>0.6153</v>
+        <v>0.6085</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.0391</v>
+        <v>-0.0711</v>
       </c>
       <c r="E35" t="n">
-        <v>0.9463</v>
+        <v>0.9358</v>
       </c>
       <c r="F35" t="n">
-        <v>0.9463</v>
+        <v>0.9358</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>0.9463</v>
+        <v>0.9358</v>
       </c>
       <c r="I35" t="n">
         <v>0.9596</v>
@@ -2060,25 +2060,25 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.8845</v>
+        <v>0.8623</v>
       </c>
       <c r="C36" t="n">
-        <v>0.5750999999999999</v>
+        <v>0.5607</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.064</v>
+        <v>-0.1004</v>
       </c>
       <c r="E36" t="n">
-        <v>0.8845</v>
+        <v>0.8623</v>
       </c>
       <c r="F36" t="n">
-        <v>0.8589</v>
+        <v>0.8367</v>
       </c>
       <c r="G36" t="n">
         <v>0.0256</v>
       </c>
       <c r="H36" t="n">
-        <v>0.8589</v>
+        <v>0.8367</v>
       </c>
       <c r="I36" t="n">
         <v>0.8873</v>
@@ -2106,25 +2106,25 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.8375</v>
+        <v>0.8344</v>
       </c>
       <c r="C37" t="n">
-        <v>0.5446</v>
+        <v>0.5426</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.083</v>
+        <v>-0.1115</v>
       </c>
       <c r="E37" t="n">
-        <v>0.8375</v>
+        <v>0.8344</v>
       </c>
       <c r="F37" t="n">
-        <v>0.8375</v>
+        <v>0.8344</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>0.8375</v>
+        <v>0.8344</v>
       </c>
       <c r="I37" t="n">
         <v>0.8414</v>
@@ -2152,25 +2152,25 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.7481</v>
+        <v>0.7222</v>
       </c>
       <c r="C38" t="n">
-        <v>0.4864</v>
+        <v>0.4696</v>
       </c>
       <c r="D38" t="n">
-        <v>-0.1191</v>
+        <v>-0.1562</v>
       </c>
       <c r="E38" t="n">
-        <v>0.7481</v>
+        <v>0.7222</v>
       </c>
       <c r="F38" t="n">
-        <v>1.7481</v>
+        <v>1.7222</v>
       </c>
       <c r="G38" t="n">
         <v>-1</v>
       </c>
       <c r="H38" t="n">
-        <v>1.7481</v>
+        <v>1.7222</v>
       </c>
       <c r="I38" t="n">
         <v>1.7809</v>
@@ -2198,25 +2198,25 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.701</v>
+        <v>0.6879999999999999</v>
       </c>
       <c r="C39" t="n">
-        <v>0.4558</v>
+        <v>0.4474</v>
       </c>
       <c r="D39" t="n">
-        <v>-0.1382</v>
+        <v>-0.1698</v>
       </c>
       <c r="E39" t="n">
-        <v>0.701</v>
+        <v>0.6879999999999999</v>
       </c>
       <c r="F39" t="n">
-        <v>0.701</v>
+        <v>0.6879999999999999</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>0.701</v>
+        <v>0.6879999999999999</v>
       </c>
       <c r="I39" t="n">
         <v>0.7175</v>
@@ -2244,25 +2244,25 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.6912</v>
+        <v>0.6798999999999999</v>
       </c>
       <c r="C40" t="n">
-        <v>0.4494</v>
+        <v>0.4421</v>
       </c>
       <c r="D40" t="n">
-        <v>-0.1421</v>
+        <v>-0.173</v>
       </c>
       <c r="E40" t="n">
-        <v>0.6912</v>
+        <v>0.6798999999999999</v>
       </c>
       <c r="F40" t="n">
-        <v>0.7588</v>
+        <v>0.7475000000000001</v>
       </c>
       <c r="G40" t="n">
         <v>-0.06759999999999999</v>
       </c>
       <c r="H40" t="n">
-        <v>0.7588</v>
+        <v>0.7475000000000001</v>
       </c>
       <c r="I40" t="n">
         <v>0.773</v>
@@ -2286,93 +2286,93 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>broky</t>
+          <t>m0NESY</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.6882</v>
+        <v>0.6762</v>
       </c>
       <c r="C41" t="n">
-        <v>0.4475</v>
+        <v>0.4397</v>
       </c>
       <c r="D41" t="n">
-        <v>-0.1433</v>
+        <v>-0.1745</v>
       </c>
       <c r="E41" t="n">
-        <v>0.6882</v>
+        <v>0.6762</v>
       </c>
       <c r="F41" t="n">
-        <v>0.6882</v>
+        <v>0.6762</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>0.6882</v>
+        <v>0.6762</v>
       </c>
       <c r="I41" t="n">
-        <v>0.7044</v>
+        <v>0.6934</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
       </c>
       <c r="K41" t="n">
-        <v>276</v>
+        <v>191</v>
       </c>
       <c r="L41" t="n">
         <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>0.7044</v>
+        <v>0.6934</v>
       </c>
       <c r="N41" t="n">
-        <v>276</v>
+        <v>191</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>m0NESY</t>
+          <t>broky</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.6838</v>
+        <v>0.6755</v>
       </c>
       <c r="C42" t="n">
-        <v>0.4446</v>
+        <v>0.4392</v>
       </c>
       <c r="D42" t="n">
-        <v>-0.1451</v>
+        <v>-0.1748</v>
       </c>
       <c r="E42" t="n">
-        <v>0.6838</v>
+        <v>0.6755</v>
       </c>
       <c r="F42" t="n">
-        <v>0.6838</v>
+        <v>0.6755</v>
       </c>
       <c r="G42" t="n">
         <v>0</v>
       </c>
       <c r="H42" t="n">
-        <v>0.6838</v>
+        <v>0.6755</v>
       </c>
       <c r="I42" t="n">
-        <v>0.6934</v>
+        <v>0.7044</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
       </c>
       <c r="K42" t="n">
-        <v>191</v>
+        <v>276</v>
       </c>
       <c r="L42" t="n">
         <v>0</v>
       </c>
       <c r="M42" t="n">
-        <v>0.6934</v>
+        <v>0.7044</v>
       </c>
       <c r="N42" t="n">
-        <v>191</v>
+        <v>276</v>
       </c>
     </row>
     <row r="43">
@@ -2382,25 +2382,25 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.6127</v>
+        <v>0.6105</v>
       </c>
       <c r="C43" t="n">
-        <v>0.3984</v>
+        <v>0.397</v>
       </c>
       <c r="D43" t="n">
-        <v>-0.1738</v>
+        <v>-0.2007</v>
       </c>
       <c r="E43" t="n">
-        <v>0.6127</v>
+        <v>0.6105</v>
       </c>
       <c r="F43" t="n">
-        <v>0.6127</v>
+        <v>0.6105</v>
       </c>
       <c r="G43" t="n">
         <v>0</v>
       </c>
       <c r="H43" t="n">
-        <v>0.6127</v>
+        <v>0.6105</v>
       </c>
       <c r="I43" t="n">
         <v>0.6156</v>
@@ -2428,25 +2428,25 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.4793</v>
+        <v>0.4758</v>
       </c>
       <c r="C44" t="n">
-        <v>0.3117</v>
+        <v>0.3094</v>
       </c>
       <c r="D44" t="n">
-        <v>-0.2277</v>
+        <v>-0.2544</v>
       </c>
       <c r="E44" t="n">
-        <v>0.4793</v>
+        <v>0.4758</v>
       </c>
       <c r="F44" t="n">
-        <v>0.4793</v>
+        <v>0.4758</v>
       </c>
       <c r="G44" t="n">
         <v>0</v>
       </c>
       <c r="H44" t="n">
-        <v>0.4793</v>
+        <v>0.4758</v>
       </c>
       <c r="I44" t="n">
         <v>0.4838</v>
@@ -2474,25 +2474,25 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.4571</v>
+        <v>0.4554</v>
       </c>
       <c r="C45" t="n">
-        <v>0.2972</v>
+        <v>0.2961</v>
       </c>
       <c r="D45" t="n">
-        <v>-0.2367</v>
+        <v>-0.2625</v>
       </c>
       <c r="E45" t="n">
-        <v>0.4571</v>
+        <v>0.4554</v>
       </c>
       <c r="F45" t="n">
-        <v>0.4571</v>
+        <v>0.4554</v>
       </c>
       <c r="G45" t="n">
         <v>0</v>
       </c>
       <c r="H45" t="n">
-        <v>0.4571</v>
+        <v>0.4554</v>
       </c>
       <c r="I45" t="n">
         <v>0.4592</v>
@@ -2520,25 +2520,25 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.4327</v>
+        <v>0.4406</v>
       </c>
       <c r="C46" t="n">
-        <v>0.2814</v>
+        <v>0.2865</v>
       </c>
       <c r="D46" t="n">
-        <v>-0.2466</v>
+        <v>-0.2684</v>
       </c>
       <c r="E46" t="n">
-        <v>0.4327</v>
+        <v>0.4406</v>
       </c>
       <c r="F46" t="n">
-        <v>-0.5318000000000001</v>
+        <v>-0.5239</v>
       </c>
       <c r="G46" t="n">
         <v>0.9645</v>
       </c>
       <c r="H46" t="n">
-        <v>-0.5318000000000001</v>
+        <v>-0.5239</v>
       </c>
       <c r="I46" t="n">
         <v>-0.5417999999999999</v>
@@ -2566,25 +2566,25 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.3297</v>
+        <v>0.326</v>
       </c>
       <c r="C47" t="n">
-        <v>0.2144</v>
+        <v>0.212</v>
       </c>
       <c r="D47" t="n">
-        <v>-0.2882</v>
+        <v>-0.314</v>
       </c>
       <c r="E47" t="n">
-        <v>0.3297</v>
+        <v>0.326</v>
       </c>
       <c r="F47" t="n">
-        <v>0.3297</v>
+        <v>0.326</v>
       </c>
       <c r="G47" t="n">
         <v>0</v>
       </c>
       <c r="H47" t="n">
-        <v>0.3297</v>
+        <v>0.326</v>
       </c>
       <c r="I47" t="n">
         <v>0.3343</v>
@@ -2612,25 +2612,25 @@
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.1112</v>
+        <v>0.1108</v>
       </c>
       <c r="C48" t="n">
-        <v>0.0723</v>
+        <v>0.07199999999999999</v>
       </c>
       <c r="D48" t="n">
-        <v>-0.3764</v>
+        <v>-0.3998</v>
       </c>
       <c r="E48" t="n">
-        <v>0.1112</v>
+        <v>0.1108</v>
       </c>
       <c r="F48" t="n">
-        <v>0.1112</v>
+        <v>0.1108</v>
       </c>
       <c r="G48" t="n">
         <v>0</v>
       </c>
       <c r="H48" t="n">
-        <v>0.1112</v>
+        <v>0.1108</v>
       </c>
       <c r="I48" t="n">
         <v>0.1117</v>
@@ -2658,25 +2658,25 @@
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0.08550000000000001</v>
+        <v>0.08450000000000001</v>
       </c>
       <c r="C49" t="n">
-        <v>0.0556</v>
+        <v>0.0549</v>
       </c>
       <c r="D49" t="n">
-        <v>-0.3868</v>
+        <v>-0.4102</v>
       </c>
       <c r="E49" t="n">
-        <v>0.08550000000000001</v>
+        <v>0.08450000000000001</v>
       </c>
       <c r="F49" t="n">
-        <v>0.08550000000000001</v>
+        <v>0.08450000000000001</v>
       </c>
       <c r="G49" t="n">
         <v>0</v>
       </c>
       <c r="H49" t="n">
-        <v>0.08550000000000001</v>
+        <v>0.08450000000000001</v>
       </c>
       <c r="I49" t="n">
         <v>0.0867</v>
@@ -2704,25 +2704,25 @@
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0.0347</v>
+        <v>0.034</v>
       </c>
       <c r="C50" t="n">
-        <v>0.0226</v>
+        <v>0.0221</v>
       </c>
       <c r="D50" t="n">
-        <v>-0.4073</v>
+        <v>-0.4304</v>
       </c>
       <c r="E50" t="n">
-        <v>0.0347</v>
+        <v>0.034</v>
       </c>
       <c r="F50" t="n">
-        <v>0.0347</v>
+        <v>0.034</v>
       </c>
       <c r="G50" t="n">
         <v>0</v>
       </c>
       <c r="H50" t="n">
-        <v>0.0347</v>
+        <v>0.034</v>
       </c>
       <c r="I50" t="n">
         <v>0.0355</v>
@@ -2746,93 +2746,93 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>mzinho</t>
+          <t>JDC</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>0.0189</v>
+        <v>0.0147</v>
       </c>
       <c r="C51" t="n">
-        <v>0.0123</v>
+        <v>0.009599999999999999</v>
       </c>
       <c r="D51" t="n">
-        <v>-0.4137</v>
+        <v>-0.4381</v>
       </c>
       <c r="E51" t="n">
-        <v>0.0189</v>
+        <v>0.0147</v>
       </c>
       <c r="F51" t="n">
-        <v>1.1217</v>
+        <v>0.0147</v>
       </c>
       <c r="G51" t="n">
-        <v>-1.1028</v>
+        <v>0</v>
       </c>
       <c r="H51" t="n">
-        <v>1.1217</v>
+        <v>0.0147</v>
       </c>
       <c r="I51" t="n">
-        <v>1.1427</v>
+        <v>0.0148</v>
       </c>
       <c r="J51" t="n">
-        <v>-1.1028</v>
+        <v>0</v>
       </c>
       <c r="K51" t="n">
-        <v>147</v>
+        <v>108</v>
       </c>
       <c r="L51" t="n">
-        <v>102</v>
+        <v>0</v>
       </c>
       <c r="M51" t="n">
-        <v>0.03990000000000005</v>
+        <v>0.0148</v>
       </c>
       <c r="N51" t="n">
-        <v>249</v>
+        <v>108</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>JDC</t>
+          <t>mzinho</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>0.0147</v>
+        <v>0.0022</v>
       </c>
       <c r="C52" t="n">
-        <v>0.009599999999999999</v>
+        <v>0.0014</v>
       </c>
       <c r="D52" t="n">
-        <v>-0.4154</v>
+        <v>-0.443</v>
       </c>
       <c r="E52" t="n">
-        <v>0.0147</v>
+        <v>0.0022</v>
       </c>
       <c r="F52" t="n">
-        <v>0.0147</v>
+        <v>1.105</v>
       </c>
       <c r="G52" t="n">
-        <v>0</v>
+        <v>-1.1028</v>
       </c>
       <c r="H52" t="n">
-        <v>0.0147</v>
+        <v>1.105</v>
       </c>
       <c r="I52" t="n">
-        <v>0.0148</v>
+        <v>1.1427</v>
       </c>
       <c r="J52" t="n">
-        <v>0</v>
+        <v>-1.1028</v>
       </c>
       <c r="K52" t="n">
-        <v>108</v>
+        <v>147</v>
       </c>
       <c r="L52" t="n">
-        <v>0</v>
+        <v>102</v>
       </c>
       <c r="M52" t="n">
-        <v>0.0148</v>
+        <v>0.03990000000000005</v>
       </c>
       <c r="N52" t="n">
-        <v>108</v>
+        <v>249</v>
       </c>
     </row>
     <row r="53">
@@ -2848,7 +2848,7 @@
         <v>-0.0026</v>
       </c>
       <c r="D53" t="n">
-        <v>-0.423</v>
+        <v>-0.4455</v>
       </c>
       <c r="E53" t="n">
         <v>-0.004</v>
@@ -2894,7 +2894,7 @@
         <v>-0.003</v>
       </c>
       <c r="D54" t="n">
-        <v>-0.4232</v>
+        <v>-0.4457</v>
       </c>
       <c r="E54" t="n">
         <v>-0.0046</v>
@@ -2934,25 +2934,25 @@
         </is>
       </c>
       <c r="B55" t="n">
-        <v>-0.0425</v>
+        <v>-0.0423</v>
       </c>
       <c r="C55" t="n">
-        <v>-0.0276</v>
+        <v>-0.0275</v>
       </c>
       <c r="D55" t="n">
-        <v>-0.4385</v>
+        <v>-0.4608</v>
       </c>
       <c r="E55" t="n">
-        <v>-0.0425</v>
+        <v>-0.0423</v>
       </c>
       <c r="F55" t="n">
-        <v>-0.0425</v>
+        <v>-0.0423</v>
       </c>
       <c r="G55" t="n">
         <v>0</v>
       </c>
       <c r="H55" t="n">
-        <v>-0.0425</v>
+        <v>-0.0423</v>
       </c>
       <c r="I55" t="n">
         <v>-0.0427</v>
@@ -2980,25 +2980,25 @@
         </is>
       </c>
       <c r="B56" t="n">
-        <v>-0.0723</v>
+        <v>-0.07199999999999999</v>
       </c>
       <c r="C56" t="n">
-        <v>-0.047</v>
+        <v>-0.0468</v>
       </c>
       <c r="D56" t="n">
-        <v>-0.4506</v>
+        <v>-0.4726</v>
       </c>
       <c r="E56" t="n">
-        <v>-0.0723</v>
+        <v>-0.07199999999999999</v>
       </c>
       <c r="F56" t="n">
-        <v>-0.0723</v>
+        <v>-0.07199999999999999</v>
       </c>
       <c r="G56" t="n">
         <v>0</v>
       </c>
       <c r="H56" t="n">
-        <v>-0.0723</v>
+        <v>-0.07199999999999999</v>
       </c>
       <c r="I56" t="n">
         <v>-0.0726</v>
@@ -3032,7 +3032,7 @@
         <v>-0.1061</v>
       </c>
       <c r="D57" t="n">
-        <v>-0.4873</v>
+        <v>-0.5089</v>
       </c>
       <c r="E57" t="n">
         <v>-0.1632</v>
@@ -3078,7 +3078,7 @@
         <v>-0.1698</v>
       </c>
       <c r="D58" t="n">
-        <v>-0.5268</v>
+        <v>-0.5479000000000001</v>
       </c>
       <c r="E58" t="n">
         <v>-0.2611</v>
@@ -3118,25 +3118,25 @@
         </is>
       </c>
       <c r="B59" t="n">
-        <v>-0.318</v>
+        <v>-0.3157</v>
       </c>
       <c r="C59" t="n">
-        <v>-0.2068</v>
+        <v>-0.2053</v>
       </c>
       <c r="D59" t="n">
-        <v>-0.5498</v>
+        <v>-0.5697</v>
       </c>
       <c r="E59" t="n">
-        <v>-0.318</v>
+        <v>-0.3157</v>
       </c>
       <c r="F59" t="n">
-        <v>-0.318</v>
+        <v>-0.3157</v>
       </c>
       <c r="G59" t="n">
         <v>0</v>
       </c>
       <c r="H59" t="n">
-        <v>-0.318</v>
+        <v>-0.3157</v>
       </c>
       <c r="I59" t="n">
         <v>-0.321</v>
@@ -3164,25 +3164,25 @@
         </is>
       </c>
       <c r="B60" t="n">
-        <v>-0.3748</v>
+        <v>-0.3734</v>
       </c>
       <c r="C60" t="n">
-        <v>-0.2437</v>
+        <v>-0.2428</v>
       </c>
       <c r="D60" t="n">
-        <v>-0.5728</v>
+        <v>-0.5927</v>
       </c>
       <c r="E60" t="n">
-        <v>-0.3748</v>
+        <v>-0.3734</v>
       </c>
       <c r="F60" t="n">
-        <v>-0.3748</v>
+        <v>-0.3734</v>
       </c>
       <c r="G60" t="n">
         <v>0</v>
       </c>
       <c r="H60" t="n">
-        <v>-0.3748</v>
+        <v>-0.3734</v>
       </c>
       <c r="I60" t="n">
         <v>-0.3765</v>
@@ -3210,25 +3210,25 @@
         </is>
       </c>
       <c r="B61" t="n">
-        <v>-0.6744</v>
+        <v>-0.6694</v>
       </c>
       <c r="C61" t="n">
-        <v>-0.4385</v>
+        <v>-0.4353</v>
       </c>
       <c r="D61" t="n">
-        <v>-0.6938</v>
+        <v>-0.7106</v>
       </c>
       <c r="E61" t="n">
-        <v>-0.6744</v>
+        <v>-0.6694</v>
       </c>
       <c r="F61" t="n">
-        <v>-0.6744</v>
+        <v>-0.6694</v>
       </c>
       <c r="G61" t="n">
         <v>0</v>
       </c>
       <c r="H61" t="n">
-        <v>-0.6744</v>
+        <v>-0.6694</v>
       </c>
       <c r="I61" t="n">
         <v>-0.6807</v>
@@ -3262,7 +3262,7 @@
         <v>-0.4717</v>
       </c>
       <c r="D62" t="n">
-        <v>-0.7144</v>
+        <v>-0.7329</v>
       </c>
       <c r="E62" t="n">
         <v>-0.7255</v>
@@ -3302,25 +3302,25 @@
         </is>
       </c>
       <c r="B63" t="n">
-        <v>-0.7313</v>
+        <v>-0.7286</v>
       </c>
       <c r="C63" t="n">
-        <v>-0.4755</v>
+        <v>-0.4738</v>
       </c>
       <c r="D63" t="n">
-        <v>-0.7168</v>
+        <v>-0.7342</v>
       </c>
       <c r="E63" t="n">
-        <v>-0.7313</v>
+        <v>-0.7286</v>
       </c>
       <c r="F63" t="n">
-        <v>-0.7313</v>
+        <v>-0.7286</v>
       </c>
       <c r="G63" t="n">
         <v>0</v>
       </c>
       <c r="H63" t="n">
-        <v>-0.7313</v>
+        <v>-0.7286</v>
       </c>
       <c r="I63" t="n">
         <v>-0.7347</v>
@@ -3354,7 +3354,7 @@
         <v>-0.55</v>
       </c>
       <c r="D64" t="n">
-        <v>-0.7631</v>
+        <v>-0.7809</v>
       </c>
       <c r="E64" t="n">
         <v>-0.8459</v>
@@ -3394,25 +3394,25 @@
         </is>
       </c>
       <c r="B65" t="n">
-        <v>-0.8686</v>
+        <v>-0.8653</v>
       </c>
       <c r="C65" t="n">
-        <v>-0.5648</v>
+        <v>-0.5627</v>
       </c>
       <c r="D65" t="n">
-        <v>-0.7723</v>
+        <v>-0.7886</v>
       </c>
       <c r="E65" t="n">
-        <v>-0.8686</v>
+        <v>-0.8653</v>
       </c>
       <c r="F65" t="n">
-        <v>-0.8686</v>
+        <v>-0.8653</v>
       </c>
       <c r="G65" t="n">
         <v>0</v>
       </c>
       <c r="H65" t="n">
-        <v>-0.8686</v>
+        <v>-0.8653</v>
       </c>
       <c r="I65" t="n">
         <v>-0.8726</v>
@@ -3440,25 +3440,25 @@
         </is>
       </c>
       <c r="B66" t="n">
-        <v>-0.8851</v>
+        <v>-0.8784999999999999</v>
       </c>
       <c r="C66" t="n">
-        <v>-0.5755</v>
+        <v>-0.5712</v>
       </c>
       <c r="D66" t="n">
-        <v>-0.7789</v>
+        <v>-0.7939000000000001</v>
       </c>
       <c r="E66" t="n">
-        <v>-0.8851</v>
+        <v>-0.8784999999999999</v>
       </c>
       <c r="F66" t="n">
-        <v>-0.8851</v>
+        <v>-0.8784999999999999</v>
       </c>
       <c r="G66" t="n">
         <v>0</v>
       </c>
       <c r="H66" t="n">
-        <v>-0.8851</v>
+        <v>-0.8784999999999999</v>
       </c>
       <c r="I66" t="n">
         <v>-0.8934</v>
@@ -3486,25 +3486,25 @@
         </is>
       </c>
       <c r="B67" t="n">
-        <v>-0.9142</v>
+        <v>-0.904</v>
       </c>
       <c r="C67" t="n">
-        <v>-0.5944</v>
+        <v>-0.5878</v>
       </c>
       <c r="D67" t="n">
-        <v>-0.7907</v>
+        <v>-0.8041</v>
       </c>
       <c r="E67" t="n">
-        <v>-0.9142</v>
+        <v>-0.904</v>
       </c>
       <c r="F67" t="n">
-        <v>-0.9142</v>
+        <v>-0.904</v>
       </c>
       <c r="G67" t="n">
         <v>0</v>
       </c>
       <c r="H67" t="n">
-        <v>-0.9142</v>
+        <v>-0.904</v>
       </c>
       <c r="I67" t="n">
         <v>-0.927</v>
@@ -3532,25 +3532,25 @@
         </is>
       </c>
       <c r="B68" t="n">
-        <v>-0.9201</v>
+        <v>-0.9098000000000001</v>
       </c>
       <c r="C68" t="n">
-        <v>-0.5983000000000001</v>
+        <v>-0.5916</v>
       </c>
       <c r="D68" t="n">
-        <v>-0.7931</v>
+        <v>-0.8064</v>
       </c>
       <c r="E68" t="n">
-        <v>-0.9201</v>
+        <v>-0.9098000000000001</v>
       </c>
       <c r="F68" t="n">
-        <v>-0.9201</v>
+        <v>-0.9098000000000001</v>
       </c>
       <c r="G68" t="n">
         <v>0</v>
       </c>
       <c r="H68" t="n">
-        <v>-0.9201</v>
+        <v>-0.9098000000000001</v>
       </c>
       <c r="I68" t="n">
         <v>-0.9330000000000001</v>
@@ -3584,7 +3584,7 @@
         <v>-0.6623</v>
       </c>
       <c r="D69" t="n">
-        <v>-0.8329</v>
+        <v>-0.8497</v>
       </c>
       <c r="E69" t="n">
         <v>-1.0186</v>
@@ -3624,25 +3624,25 @@
         </is>
       </c>
       <c r="B70" t="n">
-        <v>-1.0443</v>
+        <v>-1.0321</v>
       </c>
       <c r="C70" t="n">
-        <v>-0.679</v>
+        <v>-0.6711</v>
       </c>
       <c r="D70" t="n">
-        <v>-0.8431999999999999</v>
+        <v>-0.8551</v>
       </c>
       <c r="E70" t="n">
-        <v>-1.0443</v>
+        <v>-1.0321</v>
       </c>
       <c r="F70" t="n">
-        <v>-0.8219</v>
+        <v>-0.8097</v>
       </c>
       <c r="G70" t="n">
         <v>-0.2224</v>
       </c>
       <c r="H70" t="n">
-        <v>-0.8219</v>
+        <v>-0.8097</v>
       </c>
       <c r="I70" t="n">
         <v>-0.8373</v>
@@ -3676,7 +3676,7 @@
         <v>-0.6815</v>
       </c>
       <c r="D71" t="n">
-        <v>-0.8448</v>
+        <v>-0.8615</v>
       </c>
       <c r="E71" t="n">
         <v>-1.0481</v>
@@ -3716,25 +3716,25 @@
         </is>
       </c>
       <c r="B72" t="n">
-        <v>-1.061</v>
+        <v>-1.0492</v>
       </c>
       <c r="C72" t="n">
-        <v>-0.6899</v>
+        <v>-0.6822</v>
       </c>
       <c r="D72" t="n">
-        <v>-0.85</v>
+        <v>-0.8619</v>
       </c>
       <c r="E72" t="n">
-        <v>-1.061</v>
+        <v>-1.0492</v>
       </c>
       <c r="F72" t="n">
-        <v>-1.061</v>
+        <v>-1.0492</v>
       </c>
       <c r="G72" t="n">
         <v>0</v>
       </c>
       <c r="H72" t="n">
-        <v>-1.061</v>
+        <v>-1.0492</v>
       </c>
       <c r="I72" t="n">
         <v>-1.0759</v>
@@ -3762,25 +3762,25 @@
         </is>
       </c>
       <c r="B73" t="n">
-        <v>-1.1541</v>
+        <v>-1.1327</v>
       </c>
       <c r="C73" t="n">
-        <v>-0.7504</v>
+        <v>-0.7365</v>
       </c>
       <c r="D73" t="n">
-        <v>-0.8875999999999999</v>
+        <v>-0.8952</v>
       </c>
       <c r="E73" t="n">
-        <v>-1.1541</v>
+        <v>-1.1327</v>
       </c>
       <c r="F73" t="n">
-        <v>-1.1541</v>
+        <v>-1.1327</v>
       </c>
       <c r="G73" t="n">
         <v>0</v>
       </c>
       <c r="H73" t="n">
-        <v>-1.1541</v>
+        <v>-1.1327</v>
       </c>
       <c r="I73" t="n">
         <v>-1.1812</v>
@@ -3808,25 +3808,25 @@
         </is>
       </c>
       <c r="B74" t="n">
-        <v>-1.1753</v>
+        <v>-1.1709</v>
       </c>
       <c r="C74" t="n">
-        <v>-0.7642</v>
+        <v>-0.7614</v>
       </c>
       <c r="D74" t="n">
-        <v>-0.8962</v>
+        <v>-0.9104</v>
       </c>
       <c r="E74" t="n">
-        <v>-1.1753</v>
+        <v>-1.1709</v>
       </c>
       <c r="F74" t="n">
-        <v>-1.1753</v>
+        <v>-1.1709</v>
       </c>
       <c r="G74" t="n">
         <v>0</v>
       </c>
       <c r="H74" t="n">
-        <v>-1.1753</v>
+        <v>-1.1709</v>
       </c>
       <c r="I74" t="n">
         <v>-1.1808</v>
@@ -3854,25 +3854,25 @@
         </is>
       </c>
       <c r="B75" t="n">
-        <v>-1.2132</v>
+        <v>-1.1907</v>
       </c>
       <c r="C75" t="n">
-        <v>-0.7889</v>
+        <v>-0.7742</v>
       </c>
       <c r="D75" t="n">
-        <v>-0.9115</v>
+        <v>-0.9183</v>
       </c>
       <c r="E75" t="n">
-        <v>-1.2132</v>
+        <v>-1.1907</v>
       </c>
       <c r="F75" t="n">
-        <v>-1.2132</v>
+        <v>-1.1907</v>
       </c>
       <c r="G75" t="n">
         <v>0</v>
       </c>
       <c r="H75" t="n">
-        <v>-1.2132</v>
+        <v>-1.1907</v>
       </c>
       <c r="I75" t="n">
         <v>-1.2417</v>
@@ -3900,25 +3900,25 @@
         </is>
       </c>
       <c r="B76" t="n">
-        <v>-1.4458</v>
+        <v>-1.4404</v>
       </c>
       <c r="C76" t="n">
-        <v>-0.9401</v>
+        <v>-0.9366</v>
       </c>
       <c r="D76" t="n">
-        <v>-1.0054</v>
+        <v>-1.0178</v>
       </c>
       <c r="E76" t="n">
-        <v>-1.4458</v>
+        <v>-1.4404</v>
       </c>
       <c r="F76" t="n">
-        <v>-1.4458</v>
+        <v>-1.4404</v>
       </c>
       <c r="G76" t="n">
         <v>0</v>
       </c>
       <c r="H76" t="n">
-        <v>-1.4458</v>
+        <v>-1.4404</v>
       </c>
       <c r="I76" t="n">
         <v>-1.4525</v>
@@ -3946,25 +3946,25 @@
         </is>
       </c>
       <c r="B77" t="n">
-        <v>-1.6855</v>
+        <v>-1.6792</v>
       </c>
       <c r="C77" t="n">
-        <v>-1.096</v>
+        <v>-1.0919</v>
       </c>
       <c r="D77" t="n">
-        <v>-1.1023</v>
+        <v>-1.1129</v>
       </c>
       <c r="E77" t="n">
-        <v>-1.6855</v>
+        <v>-1.6792</v>
       </c>
       <c r="F77" t="n">
-        <v>-1.6855</v>
+        <v>-1.6792</v>
       </c>
       <c r="G77" t="n">
         <v>0</v>
       </c>
       <c r="H77" t="n">
-        <v>-1.6855</v>
+        <v>-1.6792</v>
       </c>
       <c r="I77" t="n">
         <v>-1.6933</v>
@@ -3992,25 +3992,25 @@
         </is>
       </c>
       <c r="B78" t="n">
-        <v>-1.8121</v>
+        <v>-1.7919</v>
       </c>
       <c r="C78" t="n">
-        <v>-1.1783</v>
+        <v>-1.1652</v>
       </c>
       <c r="D78" t="n">
-        <v>-1.1534</v>
+        <v>-1.1578</v>
       </c>
       <c r="E78" t="n">
-        <v>-1.8121</v>
+        <v>-1.7919</v>
       </c>
       <c r="F78" t="n">
-        <v>-1.8121</v>
+        <v>-1.7919</v>
       </c>
       <c r="G78" t="n">
         <v>0</v>
       </c>
       <c r="H78" t="n">
-        <v>-1.8121</v>
+        <v>-1.7919</v>
       </c>
       <c r="I78" t="n">
         <v>-1.8375</v>
@@ -4038,25 +4038,25 @@
         </is>
       </c>
       <c r="B79" t="n">
-        <v>-1.8421</v>
+        <v>-1.8197</v>
       </c>
       <c r="C79" t="n">
-        <v>-1.1978</v>
+        <v>-1.1832</v>
       </c>
       <c r="D79" t="n">
-        <v>-1.1655</v>
+        <v>-1.1689</v>
       </c>
       <c r="E79" t="n">
-        <v>-1.8421</v>
+        <v>-1.8197</v>
       </c>
       <c r="F79" t="n">
-        <v>-0.8665</v>
+        <v>-0.8441</v>
       </c>
       <c r="G79" t="n">
         <v>-0.9756</v>
       </c>
       <c r="H79" t="n">
-        <v>-0.8665</v>
+        <v>-0.8441</v>
       </c>
       <c r="I79" t="n">
         <v>-0.8951</v>
@@ -4084,25 +4084,25 @@
         </is>
       </c>
       <c r="B80" t="n">
-        <v>-1.9432</v>
+        <v>-1.9072</v>
       </c>
       <c r="C80" t="n">
-        <v>-1.2635</v>
+        <v>-1.2401</v>
       </c>
       <c r="D80" t="n">
-        <v>-1.2064</v>
+        <v>-1.2037</v>
       </c>
       <c r="E80" t="n">
-        <v>-1.9432</v>
+        <v>-1.9072</v>
       </c>
       <c r="F80" t="n">
-        <v>-1.9432</v>
+        <v>-1.9072</v>
       </c>
       <c r="G80" t="n">
         <v>0</v>
       </c>
       <c r="H80" t="n">
-        <v>-1.9432</v>
+        <v>-1.9072</v>
       </c>
       <c r="I80" t="n">
         <v>-1.9888</v>
@@ -4130,25 +4130,25 @@
         </is>
       </c>
       <c r="B81" t="n">
-        <v>-2.1733</v>
+        <v>-2.1571</v>
       </c>
       <c r="C81" t="n">
-        <v>-1.4132</v>
+        <v>-1.4026</v>
       </c>
       <c r="D81" t="n">
-        <v>-1.2993</v>
+        <v>-1.3033</v>
       </c>
       <c r="E81" t="n">
-        <v>-2.1733</v>
+        <v>-2.1571</v>
       </c>
       <c r="F81" t="n">
-        <v>-2.1733</v>
+        <v>-2.1571</v>
       </c>
       <c r="G81" t="n">
         <v>0</v>
       </c>
       <c r="H81" t="n">
-        <v>-2.1733</v>
+        <v>-2.1571</v>
       </c>
       <c r="I81" t="n">
         <v>-2.1936</v>
@@ -4176,25 +4176,25 @@
         </is>
       </c>
       <c r="B82" t="n">
-        <v>-3.4854</v>
+        <v>-3.4485</v>
       </c>
       <c r="C82" t="n">
-        <v>-2.2663</v>
+        <v>-2.2424</v>
       </c>
       <c r="D82" t="n">
-        <v>-1.8294</v>
+        <v>-1.8178</v>
       </c>
       <c r="E82" t="n">
-        <v>-3.4854</v>
+        <v>-3.4485</v>
       </c>
       <c r="F82" t="n">
-        <v>-2.4854</v>
+        <v>-2.4485</v>
       </c>
       <c r="G82" t="n">
         <v>-1</v>
       </c>
       <c r="H82" t="n">
-        <v>-2.4854</v>
+        <v>-2.4485</v>
       </c>
       <c r="I82" t="n">
         <v>-2.532</v>

--- a/database/event/8034/event_8034_evp_summary.xlsx
+++ b/database/event/8034/event_8034_evp_summary.xlsx
@@ -496,31 +496,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>9.9156</v>
+        <v>10.4111</v>
       </c>
       <c r="C2" t="n">
-        <v>6.4475</v>
+        <v>6.7697</v>
       </c>
       <c r="D2" t="n">
-        <v>3.8896</v>
+        <v>4.0366</v>
       </c>
       <c r="E2" t="n">
-        <v>9.9156</v>
+        <v>10.4111</v>
       </c>
       <c r="F2" t="n">
-        <v>5.0739</v>
+        <v>5.0696</v>
       </c>
       <c r="G2" t="n">
-        <v>4.8417</v>
+        <v>4.8177</v>
       </c>
       <c r="H2" t="n">
-        <v>8.3802</v>
+        <v>8.370799999999999</v>
       </c>
       <c r="I2" t="n">
-        <v>10.0139</v>
+        <v>10.0026</v>
       </c>
       <c r="J2" t="n">
-        <v>4.8417</v>
+        <v>4.8177</v>
       </c>
       <c r="K2" t="n">
         <v>214</v>
@@ -529,7 +529,7 @@
         <v>149</v>
       </c>
       <c r="M2" t="n">
-        <v>14.8556</v>
+        <v>14.8203</v>
       </c>
       <c r="N2" t="n">
         <v>363</v>
@@ -542,31 +542,31 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>9.076499999999999</v>
+        <v>9.4556</v>
       </c>
       <c r="C3" t="n">
-        <v>5.9019</v>
+        <v>6.1484</v>
       </c>
       <c r="D3" t="n">
-        <v>3.5076</v>
+        <v>3.6098</v>
       </c>
       <c r="E3" t="n">
-        <v>9.076499999999999</v>
+        <v>9.4556</v>
       </c>
       <c r="F3" t="n">
-        <v>3.8626</v>
+        <v>3.851</v>
       </c>
       <c r="G3" t="n">
-        <v>5.2138</v>
+        <v>5.2129</v>
       </c>
       <c r="H3" t="n">
-        <v>7.8501</v>
+        <v>7.8118</v>
       </c>
       <c r="I3" t="n">
-        <v>4.239</v>
+        <v>4.2183</v>
       </c>
       <c r="J3" t="n">
-        <v>5.2138</v>
+        <v>5.2129</v>
       </c>
       <c r="K3" t="n">
         <v>170</v>
@@ -575,7 +575,7 @@
         <v>103</v>
       </c>
       <c r="M3" t="n">
-        <v>9.4528</v>
+        <v>9.4312</v>
       </c>
       <c r="N3" t="n">
         <v>273</v>
@@ -588,31 +588,31 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>6.5092</v>
+        <v>6.555</v>
       </c>
       <c r="C4" t="n">
-        <v>4.2325</v>
+        <v>4.2623</v>
       </c>
       <c r="D4" t="n">
-        <v>2.3389</v>
+        <v>2.3142</v>
       </c>
       <c r="E4" t="n">
-        <v>6.5092</v>
+        <v>6.555</v>
       </c>
       <c r="F4" t="n">
-        <v>3.1014</v>
+        <v>3.1142</v>
       </c>
       <c r="G4" t="n">
-        <v>3.4078</v>
+        <v>3.4077</v>
       </c>
       <c r="H4" t="n">
-        <v>5.3386</v>
+        <v>5.3806</v>
       </c>
       <c r="I4" t="n">
-        <v>2.8828</v>
+        <v>2.9055</v>
       </c>
       <c r="J4" t="n">
-        <v>3.4078</v>
+        <v>3.4077</v>
       </c>
       <c r="K4" t="n">
         <v>170</v>
@@ -621,7 +621,7 @@
         <v>103</v>
       </c>
       <c r="M4" t="n">
-        <v>6.2906</v>
+        <v>6.3132</v>
       </c>
       <c r="N4" t="n">
         <v>273</v>
@@ -630,93 +630,93 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>magixx</t>
+          <t>b1t</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5.8291</v>
+        <v>5.8228</v>
       </c>
       <c r="C5" t="n">
-        <v>3.7903</v>
+        <v>3.7862</v>
       </c>
       <c r="D5" t="n">
-        <v>2.0293</v>
+        <v>1.9871</v>
       </c>
       <c r="E5" t="n">
-        <v>5.8291</v>
+        <v>5.8228</v>
       </c>
       <c r="F5" t="n">
-        <v>2.4266</v>
+        <v>4.5807</v>
       </c>
       <c r="G5" t="n">
-        <v>3.4025</v>
+        <v>0.97</v>
       </c>
       <c r="H5" t="n">
-        <v>2.5862</v>
+        <v>11.1717</v>
       </c>
       <c r="I5" t="n">
-        <v>3.0903</v>
+        <v>6.0326</v>
       </c>
       <c r="J5" t="n">
-        <v>3.4025</v>
+        <v>0.97</v>
       </c>
       <c r="K5" t="n">
-        <v>214</v>
+        <v>147</v>
       </c>
       <c r="L5" t="n">
-        <v>149</v>
+        <v>51</v>
       </c>
       <c r="M5" t="n">
-        <v>6.4928</v>
+        <v>7.0026</v>
       </c>
       <c r="N5" t="n">
-        <v>363</v>
+        <v>198</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>b1t</t>
+          <t>magixx</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5.551</v>
+        <v>5.6975</v>
       </c>
       <c r="C6" t="n">
-        <v>3.6095</v>
+        <v>3.7047</v>
       </c>
       <c r="D6" t="n">
-        <v>1.9027</v>
+        <v>1.9311</v>
       </c>
       <c r="E6" t="n">
-        <v>5.551</v>
+        <v>5.6975</v>
       </c>
       <c r="F6" t="n">
-        <v>4.5807</v>
+        <v>2.4305</v>
       </c>
       <c r="G6" t="n">
-        <v>0.9703000000000001</v>
+        <v>3.3941</v>
       </c>
       <c r="H6" t="n">
-        <v>11.2037</v>
+        <v>2.5947</v>
       </c>
       <c r="I6" t="n">
-        <v>6.0499</v>
+        <v>3.1005</v>
       </c>
       <c r="J6" t="n">
-        <v>0.9703000000000001</v>
+        <v>3.3941</v>
       </c>
       <c r="K6" t="n">
-        <v>147</v>
+        <v>214</v>
       </c>
       <c r="L6" t="n">
-        <v>51</v>
+        <v>149</v>
       </c>
       <c r="M6" t="n">
-        <v>7.0202</v>
+        <v>6.4946</v>
       </c>
       <c r="N6" t="n">
-        <v>198</v>
+        <v>363</v>
       </c>
     </row>
     <row r="7">
@@ -726,31 +726,31 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4.7298</v>
+        <v>4.8351</v>
       </c>
       <c r="C7" t="n">
-        <v>3.0755</v>
+        <v>3.144</v>
       </c>
       <c r="D7" t="n">
-        <v>1.5289</v>
+        <v>1.5459</v>
       </c>
       <c r="E7" t="n">
-        <v>4.7298</v>
+        <v>4.8351</v>
       </c>
       <c r="F7" t="n">
         <v>4.0897</v>
       </c>
       <c r="G7" t="n">
-        <v>0.6401</v>
+        <v>0.6939</v>
       </c>
       <c r="H7" t="n">
-        <v>8.599399999999999</v>
+        <v>8.5992</v>
       </c>
       <c r="I7" t="n">
-        <v>4.6436</v>
+        <v>4.6435</v>
       </c>
       <c r="J7" t="n">
-        <v>0.6401</v>
+        <v>0.6939</v>
       </c>
       <c r="K7" t="n">
         <v>170</v>
@@ -759,7 +759,7 @@
         <v>103</v>
       </c>
       <c r="M7" t="n">
-        <v>5.283700000000001</v>
+        <v>5.337400000000001</v>
       </c>
       <c r="N7" t="n">
         <v>273</v>
@@ -772,31 +772,31 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4.7072</v>
+        <v>4.6435</v>
       </c>
       <c r="C8" t="n">
-        <v>3.0608</v>
+        <v>3.0194</v>
       </c>
       <c r="D8" t="n">
-        <v>1.5186</v>
+        <v>1.4603</v>
       </c>
       <c r="E8" t="n">
-        <v>4.7072</v>
+        <v>4.6435</v>
       </c>
       <c r="F8" t="n">
-        <v>2.56</v>
+        <v>2.5601</v>
       </c>
       <c r="G8" t="n">
-        <v>2.1472</v>
+        <v>2.1251</v>
       </c>
       <c r="H8" t="n">
-        <v>3.5521</v>
+        <v>3.5525</v>
       </c>
       <c r="I8" t="n">
-        <v>1.9181</v>
+        <v>1.9183</v>
       </c>
       <c r="J8" t="n">
-        <v>2.1472</v>
+        <v>2.1251</v>
       </c>
       <c r="K8" t="n">
         <v>170</v>
@@ -805,7 +805,7 @@
         <v>103</v>
       </c>
       <c r="M8" t="n">
-        <v>4.065300000000001</v>
+        <v>4.0434</v>
       </c>
       <c r="N8" t="n">
         <v>273</v>
@@ -818,31 +818,31 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>4.4832</v>
+        <v>4.6217</v>
       </c>
       <c r="C9" t="n">
-        <v>2.9152</v>
+        <v>3.0052</v>
       </c>
       <c r="D9" t="n">
-        <v>1.4166</v>
+        <v>1.4506</v>
       </c>
       <c r="E9" t="n">
-        <v>4.4832</v>
+        <v>4.6217</v>
       </c>
       <c r="F9" t="n">
         <v>4.5807</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.0975</v>
+        <v>-0.0979</v>
       </c>
       <c r="H9" t="n">
-        <v>11.3055</v>
+        <v>11.3068</v>
       </c>
       <c r="I9" t="n">
-        <v>6.1049</v>
+        <v>6.1056</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.0975</v>
+        <v>-0.0979</v>
       </c>
       <c r="K9" t="n">
         <v>147</v>
@@ -851,7 +851,7 @@
         <v>51</v>
       </c>
       <c r="M9" t="n">
-        <v>6.0074</v>
+        <v>6.0077</v>
       </c>
       <c r="N9" t="n">
         <v>198</v>
@@ -864,31 +864,31 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>4.4385</v>
+        <v>4.6054</v>
       </c>
       <c r="C10" t="n">
-        <v>2.8861</v>
+        <v>2.9946</v>
       </c>
       <c r="D10" t="n">
-        <v>1.3963</v>
+        <v>1.4433</v>
       </c>
       <c r="E10" t="n">
-        <v>4.4385</v>
+        <v>4.6054</v>
       </c>
       <c r="F10" t="n">
-        <v>4.2329</v>
+        <v>4.2261</v>
       </c>
       <c r="G10" t="n">
-        <v>0.2056</v>
+        <v>0.2052</v>
       </c>
       <c r="H10" t="n">
-        <v>9.0716</v>
+        <v>9.0494</v>
       </c>
       <c r="I10" t="n">
-        <v>4.8986</v>
+        <v>4.8866</v>
       </c>
       <c r="J10" t="n">
-        <v>0.2056</v>
+        <v>0.2052</v>
       </c>
       <c r="K10" t="n">
         <v>147</v>
@@ -897,7 +897,7 @@
         <v>51</v>
       </c>
       <c r="M10" t="n">
-        <v>5.104200000000001</v>
+        <v>5.091799999999999</v>
       </c>
       <c r="N10" t="n">
         <v>198</v>
@@ -906,185 +906,185 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>zont1x</t>
+          <t>PR</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3.6283</v>
+        <v>3.7466</v>
       </c>
       <c r="C11" t="n">
-        <v>2.3593</v>
+        <v>2.4362</v>
       </c>
       <c r="D11" t="n">
-        <v>1.0275</v>
+        <v>1.0597</v>
       </c>
       <c r="E11" t="n">
-        <v>3.6283</v>
+        <v>3.7466</v>
       </c>
       <c r="F11" t="n">
-        <v>2.661</v>
+        <v>3.1416</v>
       </c>
       <c r="G11" t="n">
-        <v>0.9673</v>
+        <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>3.0991</v>
+        <v>4.1511</v>
       </c>
       <c r="I11" t="n">
-        <v>3.7032</v>
+        <v>4.7142</v>
       </c>
       <c r="J11" t="n">
-        <v>0.9673</v>
+        <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>214</v>
+        <v>187</v>
       </c>
       <c r="L11" t="n">
-        <v>149</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>4.6705</v>
+        <v>4.7142</v>
       </c>
       <c r="N11" t="n">
-        <v>363</v>
+        <v>187</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>mezii</t>
+          <t>zont1x</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3.5459</v>
+        <v>3.6091</v>
       </c>
       <c r="C12" t="n">
-        <v>2.3057</v>
+        <v>2.3468</v>
       </c>
       <c r="D12" t="n">
-        <v>0.99</v>
+        <v>0.9983</v>
       </c>
       <c r="E12" t="n">
-        <v>3.5459</v>
+        <v>3.6091</v>
       </c>
       <c r="F12" t="n">
-        <v>2.9387</v>
+        <v>2.6608</v>
       </c>
       <c r="G12" t="n">
-        <v>0.6072</v>
+        <v>0.9683</v>
       </c>
       <c r="H12" t="n">
-        <v>4.8016</v>
+        <v>3.0988</v>
       </c>
       <c r="I12" t="n">
-        <v>2.5928</v>
+        <v>3.7029</v>
       </c>
       <c r="J12" t="n">
-        <v>0.6072</v>
+        <v>0.9683</v>
       </c>
       <c r="K12" t="n">
-        <v>170</v>
+        <v>214</v>
       </c>
       <c r="L12" t="n">
-        <v>103</v>
+        <v>149</v>
       </c>
       <c r="M12" t="n">
-        <v>3.2</v>
+        <v>4.6712</v>
       </c>
       <c r="N12" t="n">
-        <v>273</v>
+        <v>363</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>w0nderful</t>
+          <t>mezii</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>3.4531</v>
+        <v>3.4908</v>
       </c>
       <c r="C13" t="n">
-        <v>2.2453</v>
+        <v>2.2699</v>
       </c>
       <c r="D13" t="n">
-        <v>0.9477</v>
+        <v>0.9454</v>
       </c>
       <c r="E13" t="n">
-        <v>3.4531</v>
+        <v>3.4908</v>
       </c>
       <c r="F13" t="n">
-        <v>3.5732</v>
+        <v>2.9458</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.1201</v>
+        <v>0.6334</v>
       </c>
       <c r="H13" t="n">
-        <v>6.8951</v>
+        <v>4.8253</v>
       </c>
       <c r="I13" t="n">
-        <v>3.7233</v>
+        <v>2.6056</v>
       </c>
       <c r="J13" t="n">
-        <v>-0.1201</v>
+        <v>0.6334</v>
       </c>
       <c r="K13" t="n">
-        <v>147</v>
+        <v>170</v>
       </c>
       <c r="L13" t="n">
-        <v>51</v>
+        <v>103</v>
       </c>
       <c r="M13" t="n">
-        <v>3.6032</v>
+        <v>3.239</v>
       </c>
       <c r="N13" t="n">
-        <v>198</v>
+        <v>273</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>bLitz</t>
+          <t>w0nderful</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>3.2324</v>
+        <v>3.4804</v>
       </c>
       <c r="C14" t="n">
-        <v>2.1018</v>
+        <v>2.2631</v>
       </c>
       <c r="D14" t="n">
-        <v>0.8473000000000001</v>
+        <v>0.9408</v>
       </c>
       <c r="E14" t="n">
-        <v>3.2324</v>
+        <v>3.4804</v>
       </c>
       <c r="F14" t="n">
-        <v>0.9333</v>
+        <v>3.5735</v>
       </c>
       <c r="G14" t="n">
-        <v>2.2991</v>
+        <v>-0.1202</v>
       </c>
       <c r="H14" t="n">
-        <v>0.9333</v>
+        <v>6.8962</v>
       </c>
       <c r="I14" t="n">
-        <v>1.0333</v>
+        <v>3.7239</v>
       </c>
       <c r="J14" t="n">
-        <v>2.2991</v>
+        <v>-0.1202</v>
       </c>
       <c r="K14" t="n">
         <v>147</v>
       </c>
       <c r="L14" t="n">
-        <v>102</v>
+        <v>51</v>
       </c>
       <c r="M14" t="n">
-        <v>3.3324</v>
+        <v>3.6037</v>
       </c>
       <c r="N14" t="n">
-        <v>249</v>
+        <v>198</v>
       </c>
     </row>
     <row r="15">
@@ -1094,28 +1094,28 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>3.1872</v>
+        <v>3.437</v>
       </c>
       <c r="C15" t="n">
-        <v>2.0724</v>
+        <v>2.2349</v>
       </c>
       <c r="D15" t="n">
-        <v>0.8267</v>
+        <v>0.9214</v>
       </c>
       <c r="E15" t="n">
-        <v>3.1872</v>
+        <v>3.437</v>
       </c>
       <c r="F15" t="n">
-        <v>3.1872</v>
+        <v>3.1799</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>4.2509</v>
+        <v>4.2349</v>
       </c>
       <c r="I15" t="n">
-        <v>4.5881</v>
+        <v>4.5708</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1127,7 +1127,7 @@
         <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>4.5881</v>
+        <v>4.5708</v>
       </c>
       <c r="N15" t="n">
         <v>152</v>
@@ -1136,47 +1136,47 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>PR</t>
+          <t>bLitz</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>3.1414</v>
+        <v>3.3896</v>
       </c>
       <c r="C16" t="n">
-        <v>2.0427</v>
+        <v>2.2041</v>
       </c>
       <c r="D16" t="n">
-        <v>0.8058</v>
+        <v>0.9002</v>
       </c>
       <c r="E16" t="n">
-        <v>3.1414</v>
+        <v>3.3896</v>
       </c>
       <c r="F16" t="n">
-        <v>3.1414</v>
+        <v>0.9330000000000001</v>
       </c>
       <c r="G16" t="n">
-        <v>0</v>
+        <v>2.2992</v>
       </c>
       <c r="H16" t="n">
-        <v>4.1506</v>
+        <v>0.9330000000000001</v>
       </c>
       <c r="I16" t="n">
-        <v>4.7137</v>
+        <v>1.0329</v>
       </c>
       <c r="J16" t="n">
-        <v>0</v>
+        <v>2.2992</v>
       </c>
       <c r="K16" t="n">
-        <v>187</v>
+        <v>147</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>102</v>
       </c>
       <c r="M16" t="n">
-        <v>4.7137</v>
+        <v>3.3321</v>
       </c>
       <c r="N16" t="n">
-        <v>187</v>
+        <v>249</v>
       </c>
     </row>
     <row r="17">
@@ -1186,28 +1186,28 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>3.1091</v>
+        <v>3.3609</v>
       </c>
       <c r="C17" t="n">
-        <v>2.0217</v>
+        <v>2.1854</v>
       </c>
       <c r="D17" t="n">
-        <v>0.7911</v>
+        <v>0.8874</v>
       </c>
       <c r="E17" t="n">
-        <v>3.1091</v>
+        <v>3.3609</v>
       </c>
       <c r="F17" t="n">
-        <v>2.7253</v>
+        <v>2.7254</v>
       </c>
       <c r="G17" t="n">
         <v>0.3838</v>
       </c>
       <c r="H17" t="n">
-        <v>3.2399</v>
+        <v>3.2401</v>
       </c>
       <c r="I17" t="n">
-        <v>3.8715</v>
+        <v>3.8717</v>
       </c>
       <c r="J17" t="n">
         <v>0.3838</v>
@@ -1219,7 +1219,7 @@
         <v>60</v>
       </c>
       <c r="M17" t="n">
-        <v>4.2553</v>
+        <v>4.255500000000001</v>
       </c>
       <c r="N17" t="n">
         <v>305</v>
@@ -1232,31 +1232,31 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2.8547</v>
+        <v>2.8872</v>
       </c>
       <c r="C18" t="n">
-        <v>1.8562</v>
+        <v>1.8774</v>
       </c>
       <c r="D18" t="n">
-        <v>0.6753</v>
+        <v>0.6758</v>
       </c>
       <c r="E18" t="n">
-        <v>2.8547</v>
+        <v>2.8872</v>
       </c>
       <c r="F18" t="n">
-        <v>1.6691</v>
+        <v>1.695</v>
       </c>
       <c r="G18" t="n">
-        <v>1.1856</v>
+        <v>1.1866</v>
       </c>
       <c r="H18" t="n">
-        <v>1.6691</v>
+        <v>1.695</v>
       </c>
       <c r="I18" t="n">
-        <v>1.9945</v>
+        <v>2.0254</v>
       </c>
       <c r="J18" t="n">
-        <v>1.1856</v>
+        <v>1.1866</v>
       </c>
       <c r="K18" t="n">
         <v>214</v>
@@ -1265,7 +1265,7 @@
         <v>149</v>
       </c>
       <c r="M18" t="n">
-        <v>3.1801</v>
+        <v>3.212</v>
       </c>
       <c r="N18" t="n">
         <v>363</v>
@@ -1278,28 +1278,28 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>2.6879</v>
+        <v>2.7978</v>
       </c>
       <c r="C19" t="n">
-        <v>1.7478</v>
+        <v>1.8192</v>
       </c>
       <c r="D19" t="n">
-        <v>0.5994</v>
+        <v>0.6359</v>
       </c>
       <c r="E19" t="n">
-        <v>2.6879</v>
+        <v>2.7978</v>
       </c>
       <c r="F19" t="n">
-        <v>2.6879</v>
+        <v>2.6876</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>3.1581</v>
+        <v>3.1574</v>
       </c>
       <c r="I19" t="n">
-        <v>3.5865</v>
+        <v>3.5857</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -1311,7 +1311,7 @@
         <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>3.5865</v>
+        <v>3.5857</v>
       </c>
       <c r="N19" t="n">
         <v>276</v>
@@ -1324,28 +1324,28 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>2.6152</v>
+        <v>2.7687</v>
       </c>
       <c r="C20" t="n">
-        <v>1.7005</v>
+        <v>1.8003</v>
       </c>
       <c r="D20" t="n">
-        <v>0.5663</v>
+        <v>0.6229</v>
       </c>
       <c r="E20" t="n">
-        <v>2.6152</v>
+        <v>2.7687</v>
       </c>
       <c r="F20" t="n">
-        <v>2.6152</v>
+        <v>2.6154</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>2.999</v>
+        <v>2.9993</v>
       </c>
       <c r="I20" t="n">
-        <v>3.2369</v>
+        <v>3.2372</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -1357,7 +1357,7 @@
         <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>3.2369</v>
+        <v>3.2372</v>
       </c>
       <c r="N20" t="n">
         <v>169</v>
@@ -1366,219 +1366,219 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Wicadia</t>
+          <t>910</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>2.5016</v>
+        <v>2.6769</v>
       </c>
       <c r="C21" t="n">
-        <v>1.6266</v>
+        <v>1.7406</v>
       </c>
       <c r="D21" t="n">
-        <v>0.5145999999999999</v>
+        <v>0.5819</v>
       </c>
       <c r="E21" t="n">
-        <v>2.5016</v>
+        <v>2.6769</v>
       </c>
       <c r="F21" t="n">
-        <v>2.4408</v>
+        <v>1.7657</v>
       </c>
       <c r="G21" t="n">
-        <v>0.0608</v>
+        <v>0.7009</v>
       </c>
       <c r="H21" t="n">
-        <v>2.6173</v>
+        <v>1.7657</v>
       </c>
       <c r="I21" t="n">
-        <v>3.1275</v>
+        <v>1.9549</v>
       </c>
       <c r="J21" t="n">
-        <v>0.0608</v>
+        <v>0.7009</v>
       </c>
       <c r="K21" t="n">
-        <v>245</v>
+        <v>147</v>
       </c>
       <c r="L21" t="n">
-        <v>60</v>
+        <v>102</v>
       </c>
       <c r="M21" t="n">
-        <v>3.1883</v>
+        <v>2.6558</v>
       </c>
       <c r="N21" t="n">
-        <v>305</v>
+        <v>249</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>fame</t>
+          <t>frozen</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>2.4984</v>
+        <v>2.6072</v>
       </c>
       <c r="C22" t="n">
-        <v>1.6246</v>
+        <v>1.6953</v>
       </c>
       <c r="D22" t="n">
-        <v>0.5131</v>
+        <v>0.5508</v>
       </c>
       <c r="E22" t="n">
-        <v>2.4984</v>
+        <v>2.6072</v>
       </c>
       <c r="F22" t="n">
-        <v>2.2566</v>
+        <v>2.4174</v>
       </c>
       <c r="G22" t="n">
-        <v>0.2418</v>
+        <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>2.2566</v>
+        <v>2.5659</v>
       </c>
       <c r="I22" t="n">
-        <v>2.4983</v>
+        <v>2.914</v>
       </c>
       <c r="J22" t="n">
-        <v>0.2418</v>
+        <v>0</v>
       </c>
       <c r="K22" t="n">
-        <v>165</v>
+        <v>276</v>
       </c>
       <c r="L22" t="n">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>2.7401</v>
+        <v>2.914</v>
       </c>
       <c r="N22" t="n">
-        <v>202</v>
+        <v>276</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>910</t>
+          <t>fame</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>2.4799</v>
+        <v>2.5044</v>
       </c>
       <c r="C23" t="n">
-        <v>1.6125</v>
+        <v>1.6285</v>
       </c>
       <c r="D23" t="n">
-        <v>0.5047</v>
+        <v>0.5048</v>
       </c>
       <c r="E23" t="n">
-        <v>2.4799</v>
+        <v>2.5044</v>
       </c>
       <c r="F23" t="n">
-        <v>1.7659</v>
+        <v>2.2572</v>
       </c>
       <c r="G23" t="n">
-        <v>0.714</v>
+        <v>0.2407</v>
       </c>
       <c r="H23" t="n">
-        <v>1.7659</v>
+        <v>2.2572</v>
       </c>
       <c r="I23" t="n">
-        <v>1.9551</v>
+        <v>2.499</v>
       </c>
       <c r="J23" t="n">
-        <v>0.714</v>
+        <v>0.2407</v>
       </c>
       <c r="K23" t="n">
-        <v>147</v>
+        <v>165</v>
       </c>
       <c r="L23" t="n">
-        <v>102</v>
+        <v>37</v>
       </c>
       <c r="M23" t="n">
-        <v>2.6691</v>
+        <v>2.7397</v>
       </c>
       <c r="N23" t="n">
-        <v>249</v>
+        <v>202</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>frozen</t>
+          <t>woxic</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>2.4177</v>
+        <v>2.4776</v>
       </c>
       <c r="C24" t="n">
-        <v>1.5721</v>
+        <v>1.611</v>
       </c>
       <c r="D24" t="n">
-        <v>0.4764</v>
+        <v>0.4929</v>
       </c>
       <c r="E24" t="n">
-        <v>2.4177</v>
+        <v>2.4776</v>
       </c>
       <c r="F24" t="n">
-        <v>2.4177</v>
+        <v>2.7291</v>
       </c>
       <c r="G24" t="n">
-        <v>0</v>
+        <v>-0.3586</v>
       </c>
       <c r="H24" t="n">
-        <v>2.5666</v>
+        <v>3.2483</v>
       </c>
       <c r="I24" t="n">
-        <v>2.9148</v>
+        <v>3.8815</v>
       </c>
       <c r="J24" t="n">
-        <v>0</v>
+        <v>-0.3586</v>
       </c>
       <c r="K24" t="n">
-        <v>276</v>
+        <v>245</v>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="M24" t="n">
-        <v>2.9148</v>
+        <v>3.5229</v>
       </c>
       <c r="N24" t="n">
-        <v>276</v>
+        <v>305</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>woxic</t>
+          <t>Wicadia</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>2.3705</v>
+        <v>2.4699</v>
       </c>
       <c r="C25" t="n">
-        <v>1.5414</v>
+        <v>1.606</v>
       </c>
       <c r="D25" t="n">
-        <v>0.4549</v>
+        <v>0.4894</v>
       </c>
       <c r="E25" t="n">
-        <v>2.3705</v>
+        <v>2.4699</v>
       </c>
       <c r="F25" t="n">
-        <v>2.7291</v>
+        <v>2.4324</v>
       </c>
       <c r="G25" t="n">
-        <v>-0.3586</v>
+        <v>0.0608</v>
       </c>
       <c r="H25" t="n">
-        <v>3.2481</v>
+        <v>2.5988</v>
       </c>
       <c r="I25" t="n">
-        <v>3.8813</v>
+        <v>3.1054</v>
       </c>
       <c r="J25" t="n">
-        <v>-0.3586</v>
+        <v>0.0608</v>
       </c>
       <c r="K25" t="n">
         <v>245</v>
@@ -1587,7 +1587,7 @@
         <v>60</v>
       </c>
       <c r="M25" t="n">
-        <v>3.5227</v>
+        <v>3.1662</v>
       </c>
       <c r="N25" t="n">
         <v>305</v>
@@ -1600,28 +1600,28 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>2.3394</v>
+        <v>2.4059</v>
       </c>
       <c r="C26" t="n">
-        <v>1.5212</v>
+        <v>1.5644</v>
       </c>
       <c r="D26" t="n">
-        <v>0.4407</v>
+        <v>0.4608</v>
       </c>
       <c r="E26" t="n">
-        <v>2.3394</v>
+        <v>2.4059</v>
       </c>
       <c r="F26" t="n">
-        <v>2.3394</v>
+        <v>2.3514</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>2.3952</v>
+        <v>2.4214</v>
       </c>
       <c r="I26" t="n">
-        <v>2.5852</v>
+        <v>2.6135</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -1633,7 +1633,7 @@
         <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>2.5852</v>
+        <v>2.6135</v>
       </c>
       <c r="N26" t="n">
         <v>169</v>
@@ -1646,28 +1646,28 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>1.9735</v>
+        <v>2.2852</v>
       </c>
       <c r="C27" t="n">
-        <v>1.2832</v>
+        <v>1.4859</v>
       </c>
       <c r="D27" t="n">
-        <v>0.2742</v>
+        <v>0.4069</v>
       </c>
       <c r="E27" t="n">
-        <v>1.9735</v>
+        <v>2.2852</v>
       </c>
       <c r="F27" t="n">
-        <v>1.9735</v>
+        <v>1.9993</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>1.9735</v>
+        <v>1.9993</v>
       </c>
       <c r="I27" t="n">
-        <v>2.13</v>
+        <v>2.1579</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -1679,7 +1679,7 @@
         <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>2.13</v>
+        <v>2.1579</v>
       </c>
       <c r="N27" t="n">
         <v>152</v>
@@ -1692,28 +1692,28 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>1.7963</v>
+        <v>1.9252</v>
       </c>
       <c r="C28" t="n">
-        <v>1.168</v>
+        <v>1.2518</v>
       </c>
       <c r="D28" t="n">
-        <v>0.1935</v>
+        <v>0.2461</v>
       </c>
       <c r="E28" t="n">
-        <v>1.7963</v>
+        <v>1.9252</v>
       </c>
       <c r="F28" t="n">
-        <v>1.7963</v>
+        <v>1.7802</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>1.7963</v>
+        <v>1.7802</v>
       </c>
       <c r="I28" t="n">
-        <v>1.9388</v>
+        <v>1.9214</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -1725,7 +1725,7 @@
         <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>1.9388</v>
+        <v>1.9214</v>
       </c>
       <c r="N28" t="n">
         <v>169</v>
@@ -1734,47 +1734,47 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>MAJ3R</t>
+          <t>NiKo</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>1.7472</v>
+        <v>1.8119</v>
       </c>
       <c r="C29" t="n">
-        <v>1.1361</v>
+        <v>1.1782</v>
       </c>
       <c r="D29" t="n">
-        <v>0.1712</v>
+        <v>0.1955</v>
       </c>
       <c r="E29" t="n">
-        <v>1.7472</v>
+        <v>1.8119</v>
       </c>
       <c r="F29" t="n">
-        <v>1.6269</v>
+        <v>1.5042</v>
       </c>
       <c r="G29" t="n">
-        <v>0.1203</v>
+        <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>1.6269</v>
+        <v>1.5042</v>
       </c>
       <c r="I29" t="n">
-        <v>1.944</v>
+        <v>1.543</v>
       </c>
       <c r="J29" t="n">
-        <v>0.1203</v>
+        <v>0</v>
       </c>
       <c r="K29" t="n">
-        <v>245</v>
+        <v>104</v>
       </c>
       <c r="L29" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>2.0643</v>
+        <v>1.543</v>
       </c>
       <c r="N29" t="n">
-        <v>305</v>
+        <v>104</v>
       </c>
     </row>
     <row r="30">
@@ -1784,28 +1784,28 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>1.7063</v>
+        <v>1.6666</v>
       </c>
       <c r="C30" t="n">
-        <v>1.1095</v>
+        <v>1.0837</v>
       </c>
       <c r="D30" t="n">
-        <v>0.1525</v>
+        <v>0.1306</v>
       </c>
       <c r="E30" t="n">
-        <v>1.7063</v>
+        <v>1.6666</v>
       </c>
       <c r="F30" t="n">
-        <v>2.1416</v>
+        <v>2.1333</v>
       </c>
       <c r="G30" t="n">
         <v>-0.4353</v>
       </c>
       <c r="H30" t="n">
-        <v>2.1416</v>
+        <v>2.1333</v>
       </c>
       <c r="I30" t="n">
-        <v>2.5591</v>
+        <v>2.5492</v>
       </c>
       <c r="J30" t="n">
         <v>-0.4353</v>
@@ -1817,7 +1817,7 @@
         <v>60</v>
       </c>
       <c r="M30" t="n">
-        <v>2.1238</v>
+        <v>2.1139</v>
       </c>
       <c r="N30" t="n">
         <v>305</v>
@@ -1826,185 +1826,185 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>HeavyGod</t>
+          <t>REZ</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>1.651</v>
+        <v>1.6614</v>
       </c>
       <c r="C31" t="n">
-        <v>1.0735</v>
+        <v>1.0803</v>
       </c>
       <c r="D31" t="n">
-        <v>0.1274</v>
+        <v>0.1283</v>
       </c>
       <c r="E31" t="n">
-        <v>1.651</v>
+        <v>1.6614</v>
       </c>
       <c r="F31" t="n">
-        <v>1.651</v>
+        <v>1.582</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>1.651</v>
+        <v>1.582</v>
       </c>
       <c r="I31" t="n">
-        <v>1.7819</v>
+        <v>1.7966</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
       </c>
       <c r="K31" t="n">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="L31" t="n">
         <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>1.7819</v>
+        <v>1.7966</v>
       </c>
       <c r="N31" t="n">
-        <v>191</v>
+        <v>187</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>torzsi</t>
+          <t>MAJ3R</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>1.6076</v>
+        <v>1.6549</v>
       </c>
       <c r="C32" t="n">
-        <v>1.0453</v>
+        <v>1.0761</v>
       </c>
       <c r="D32" t="n">
-        <v>0.1076</v>
+        <v>0.1254</v>
       </c>
       <c r="E32" t="n">
-        <v>1.6076</v>
+        <v>1.6549</v>
       </c>
       <c r="F32" t="n">
-        <v>1.6076</v>
+        <v>1.6269</v>
       </c>
       <c r="G32" t="n">
-        <v>0</v>
+        <v>0.1203</v>
       </c>
       <c r="H32" t="n">
-        <v>1.6076</v>
+        <v>1.6269</v>
       </c>
       <c r="I32" t="n">
-        <v>1.6076</v>
+        <v>1.9441</v>
       </c>
       <c r="J32" t="n">
-        <v>0</v>
+        <v>0.1203</v>
       </c>
       <c r="K32" t="n">
-        <v>86</v>
+        <v>245</v>
       </c>
       <c r="L32" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="M32" t="n">
-        <v>1.6076</v>
+        <v>2.0644</v>
       </c>
       <c r="N32" t="n">
-        <v>86</v>
+        <v>305</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>REZ</t>
+          <t>HeavyGod</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>1.5898</v>
+        <v>1.5657</v>
       </c>
       <c r="C33" t="n">
-        <v>1.0338</v>
+        <v>1.0181</v>
       </c>
       <c r="D33" t="n">
-        <v>0.09950000000000001</v>
+        <v>0.08550000000000001</v>
       </c>
       <c r="E33" t="n">
-        <v>1.5898</v>
+        <v>1.5657</v>
       </c>
       <c r="F33" t="n">
-        <v>1.5898</v>
+        <v>1.6507</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>1.5898</v>
+        <v>1.6507</v>
       </c>
       <c r="I33" t="n">
-        <v>1.8055</v>
+        <v>1.7816</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
       </c>
       <c r="K33" t="n">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="L33" t="n">
         <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>1.8055</v>
+        <v>1.7816</v>
       </c>
       <c r="N33" t="n">
-        <v>187</v>
+        <v>191</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>NiKo</t>
+          <t>torzsi</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>1.505</v>
+        <v>1.483</v>
       </c>
       <c r="C34" t="n">
-        <v>0.9786</v>
+        <v>0.9643</v>
       </c>
       <c r="D34" t="n">
-        <v>0.0609</v>
+        <v>0.0486</v>
       </c>
       <c r="E34" t="n">
-        <v>1.505</v>
+        <v>1.483</v>
       </c>
       <c r="F34" t="n">
-        <v>1.505</v>
+        <v>1.6076</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>1.505</v>
+        <v>1.6076</v>
       </c>
       <c r="I34" t="n">
-        <v>1.5438</v>
+        <v>1.6076</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
       </c>
       <c r="K34" t="n">
-        <v>104</v>
+        <v>86</v>
       </c>
       <c r="L34" t="n">
         <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>1.5438</v>
+        <v>1.6076</v>
       </c>
       <c r="N34" t="n">
-        <v>104</v>
+        <v>86</v>
       </c>
     </row>
     <row r="35">
@@ -2014,28 +2014,28 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>1.1845</v>
+        <v>1.23</v>
       </c>
       <c r="C35" t="n">
-        <v>0.7702</v>
+        <v>0.7998</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.08500000000000001</v>
+        <v>-0.0644</v>
       </c>
       <c r="E35" t="n">
-        <v>1.1845</v>
+        <v>1.23</v>
       </c>
       <c r="F35" t="n">
-        <v>1.1845</v>
+        <v>1.1846</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>1.1845</v>
+        <v>1.1846</v>
       </c>
       <c r="I35" t="n">
-        <v>1.215</v>
+        <v>1.2151</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -2047,7 +2047,7 @@
         <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>1.215</v>
+        <v>1.2151</v>
       </c>
       <c r="N35" t="n">
         <v>108</v>
@@ -2056,369 +2056,369 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>malbsMd</t>
+          <t>EliGE</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>1.0739</v>
+        <v>1.1859</v>
       </c>
       <c r="C36" t="n">
-        <v>0.6983</v>
+        <v>0.7711</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.1353</v>
+        <v>-0.08409999999999999</v>
       </c>
       <c r="E36" t="n">
-        <v>1.0739</v>
+        <v>1.1859</v>
       </c>
       <c r="F36" t="n">
-        <v>1.0739</v>
+        <v>1.0663</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>1.0739</v>
+        <v>1.0663</v>
       </c>
       <c r="I36" t="n">
-        <v>1.1591</v>
+        <v>1.2109</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
       </c>
       <c r="K36" t="n">
-        <v>191</v>
+        <v>276</v>
       </c>
       <c r="L36" t="n">
         <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>1.1591</v>
+        <v>1.2109</v>
       </c>
       <c r="N36" t="n">
-        <v>191</v>
+        <v>276</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>EliGE</t>
+          <t>malbsMd</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>1.0346</v>
+        <v>1.1663</v>
       </c>
       <c r="C37" t="n">
-        <v>0.6727</v>
+        <v>0.7584</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.1532</v>
+        <v>-0.0929</v>
       </c>
       <c r="E37" t="n">
-        <v>1.0346</v>
+        <v>1.1663</v>
       </c>
       <c r="F37" t="n">
-        <v>1.0346</v>
+        <v>1.0925</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>1.0346</v>
+        <v>1.0925</v>
       </c>
       <c r="I37" t="n">
-        <v>1.175</v>
+        <v>1.1792</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
       </c>
       <c r="K37" t="n">
-        <v>276</v>
+        <v>191</v>
       </c>
       <c r="L37" t="n">
         <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>1.175</v>
+        <v>1.1792</v>
       </c>
       <c r="N37" t="n">
-        <v>276</v>
+        <v>191</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>KSCERATO</t>
+          <t>m0NESY</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.9995000000000001</v>
+        <v>1.0998</v>
       </c>
       <c r="C38" t="n">
-        <v>0.6499</v>
+        <v>0.7151</v>
       </c>
       <c r="D38" t="n">
-        <v>-0.1692</v>
+        <v>-0.1226</v>
       </c>
       <c r="E38" t="n">
-        <v>0.9995000000000001</v>
+        <v>1.0998</v>
       </c>
       <c r="F38" t="n">
-        <v>0.9995000000000001</v>
+        <v>0.9719</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>0.9995000000000001</v>
+        <v>0.9719</v>
       </c>
       <c r="I38" t="n">
-        <v>1.0253</v>
+        <v>1.049</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
       </c>
       <c r="K38" t="n">
-        <v>102</v>
+        <v>191</v>
       </c>
       <c r="L38" t="n">
         <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>1.0253</v>
+        <v>1.049</v>
       </c>
       <c r="N38" t="n">
-        <v>102</v>
+        <v>191</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>m0NESY</t>
+          <t>FL1T</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.9722</v>
+        <v>0.9739</v>
       </c>
       <c r="C39" t="n">
-        <v>0.6322</v>
+        <v>0.6333</v>
       </c>
       <c r="D39" t="n">
-        <v>-0.1816</v>
+        <v>-0.1788</v>
       </c>
       <c r="E39" t="n">
-        <v>0.9722</v>
+        <v>0.9739</v>
       </c>
       <c r="F39" t="n">
-        <v>0.9722</v>
+        <v>1.7014</v>
       </c>
       <c r="G39" t="n">
-        <v>0</v>
+        <v>-0.7864</v>
       </c>
       <c r="H39" t="n">
-        <v>0.9722</v>
+        <v>1.7014</v>
       </c>
       <c r="I39" t="n">
-        <v>1.0493</v>
+        <v>1.8837</v>
       </c>
       <c r="J39" t="n">
-        <v>0</v>
+        <v>-0.7864</v>
       </c>
       <c r="K39" t="n">
-        <v>191</v>
+        <v>165</v>
       </c>
       <c r="L39" t="n">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="M39" t="n">
-        <v>1.0493</v>
+        <v>1.0973</v>
       </c>
       <c r="N39" t="n">
-        <v>191</v>
+        <v>202</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>FL1T</t>
+          <t>skullz</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.9379</v>
+        <v>0.9198</v>
       </c>
       <c r="C40" t="n">
-        <v>0.6099</v>
+        <v>0.5981</v>
       </c>
       <c r="D40" t="n">
-        <v>-0.1973</v>
+        <v>-0.203</v>
       </c>
       <c r="E40" t="n">
-        <v>0.9379</v>
+        <v>0.9198</v>
       </c>
       <c r="F40" t="n">
-        <v>1.724</v>
+        <v>0.6478</v>
       </c>
       <c r="G40" t="n">
-        <v>-0.7861</v>
+        <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>1.724</v>
+        <v>0.6478</v>
       </c>
       <c r="I40" t="n">
-        <v>1.9087</v>
+        <v>0.6645</v>
       </c>
       <c r="J40" t="n">
-        <v>-0.7861</v>
+        <v>0</v>
       </c>
       <c r="K40" t="n">
-        <v>165</v>
+        <v>102</v>
       </c>
       <c r="L40" t="n">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>1.1226</v>
+        <v>0.6645</v>
       </c>
       <c r="N40" t="n">
-        <v>202</v>
+        <v>102</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>FL4MUS</t>
+          <t>ICY</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.9165</v>
+        <v>0.8792</v>
       </c>
       <c r="C41" t="n">
-        <v>0.5959</v>
+        <v>0.5717</v>
       </c>
       <c r="D41" t="n">
-        <v>-0.207</v>
+        <v>-0.2211</v>
       </c>
       <c r="E41" t="n">
-        <v>0.9165</v>
+        <v>0.8792</v>
       </c>
       <c r="F41" t="n">
-        <v>0.9165</v>
+        <v>0.8289</v>
       </c>
       <c r="G41" t="n">
-        <v>0</v>
+        <v>0.0159</v>
       </c>
       <c r="H41" t="n">
-        <v>0.9165</v>
+        <v>0.8289</v>
       </c>
       <c r="I41" t="n">
-        <v>1.0147</v>
+        <v>0.9177</v>
       </c>
       <c r="J41" t="n">
-        <v>0</v>
+        <v>0.0159</v>
       </c>
       <c r="K41" t="n">
         <v>165</v>
       </c>
       <c r="L41" t="n">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="M41" t="n">
-        <v>1.0147</v>
+        <v>0.9336</v>
       </c>
       <c r="N41" t="n">
-        <v>165</v>
+        <v>202</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>ICY</t>
+          <t>FL4MUS</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.8446</v>
+        <v>0.8716</v>
       </c>
       <c r="C42" t="n">
-        <v>0.5492</v>
+        <v>0.5667</v>
       </c>
       <c r="D42" t="n">
-        <v>-0.2397</v>
+        <v>-0.2245</v>
       </c>
       <c r="E42" t="n">
-        <v>0.8446</v>
+        <v>0.8716</v>
       </c>
       <c r="F42" t="n">
-        <v>0.8286</v>
+        <v>0.9169</v>
       </c>
       <c r="G42" t="n">
-        <v>0.016</v>
+        <v>0</v>
       </c>
       <c r="H42" t="n">
-        <v>0.8286</v>
+        <v>0.9169</v>
       </c>
       <c r="I42" t="n">
-        <v>0.9174</v>
+        <v>1.0151</v>
       </c>
       <c r="J42" t="n">
-        <v>0.016</v>
+        <v>0</v>
       </c>
       <c r="K42" t="n">
         <v>165</v>
       </c>
       <c r="L42" t="n">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="M42" t="n">
-        <v>0.9334</v>
+        <v>1.0151</v>
       </c>
       <c r="N42" t="n">
-        <v>202</v>
+        <v>165</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Techno</t>
+          <t>KSCERATO</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.7415</v>
+        <v>0.866</v>
       </c>
       <c r="C43" t="n">
-        <v>0.4822</v>
+        <v>0.5631</v>
       </c>
       <c r="D43" t="n">
-        <v>-0.2867</v>
+        <v>-0.227</v>
       </c>
       <c r="E43" t="n">
-        <v>0.7415</v>
+        <v>0.866</v>
       </c>
       <c r="F43" t="n">
-        <v>-0.0434</v>
+        <v>0.9995000000000001</v>
       </c>
       <c r="G43" t="n">
-        <v>0.7849</v>
+        <v>0</v>
       </c>
       <c r="H43" t="n">
-        <v>-0.0434</v>
+        <v>0.9995000000000001</v>
       </c>
       <c r="I43" t="n">
-        <v>-0.048</v>
+        <v>1.0253</v>
       </c>
       <c r="J43" t="n">
-        <v>0.7849</v>
+        <v>0</v>
       </c>
       <c r="K43" t="n">
-        <v>147</v>
+        <v>102</v>
       </c>
       <c r="L43" t="n">
+        <v>0</v>
+      </c>
+      <c r="M43" t="n">
+        <v>1.0253</v>
+      </c>
+      <c r="N43" t="n">
         <v>102</v>
-      </c>
-      <c r="M43" t="n">
-        <v>0.7369</v>
-      </c>
-      <c r="N43" t="n">
-        <v>249</v>
       </c>
     </row>
     <row r="44">
@@ -2428,28 +2428,28 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.7397</v>
+        <v>0.7684</v>
       </c>
       <c r="C44" t="n">
-        <v>0.481</v>
+        <v>0.4996</v>
       </c>
       <c r="D44" t="n">
-        <v>-0.2875</v>
+        <v>-0.2706</v>
       </c>
       <c r="E44" t="n">
-        <v>0.7397</v>
+        <v>0.7684</v>
       </c>
       <c r="F44" t="n">
-        <v>0.7397</v>
+        <v>0.7533</v>
       </c>
       <c r="G44" t="n">
         <v>0</v>
       </c>
       <c r="H44" t="n">
-        <v>0.7397</v>
+        <v>0.7533</v>
       </c>
       <c r="I44" t="n">
-        <v>0.84</v>
+        <v>0.8555</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -2461,7 +2461,7 @@
         <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>0.84</v>
+        <v>0.8555</v>
       </c>
       <c r="N44" t="n">
         <v>276</v>
@@ -2470,47 +2470,47 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>skullz</t>
+          <t>Techno</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.6478</v>
+        <v>0.7334000000000001</v>
       </c>
       <c r="C45" t="n">
-        <v>0.4212</v>
+        <v>0.4769</v>
       </c>
       <c r="D45" t="n">
-        <v>-0.3293</v>
+        <v>-0.2862</v>
       </c>
       <c r="E45" t="n">
-        <v>0.6478</v>
+        <v>0.7334000000000001</v>
       </c>
       <c r="F45" t="n">
-        <v>0.6478</v>
+        <v>-0.0438</v>
       </c>
       <c r="G45" t="n">
-        <v>0</v>
+        <v>0.7851</v>
       </c>
       <c r="H45" t="n">
-        <v>0.6478</v>
+        <v>-0.0438</v>
       </c>
       <c r="I45" t="n">
-        <v>0.6645</v>
+        <v>-0.0485</v>
       </c>
       <c r="J45" t="n">
-        <v>0</v>
+        <v>0.7851</v>
       </c>
       <c r="K45" t="n">
+        <v>147</v>
+      </c>
+      <c r="L45" t="n">
         <v>102</v>
       </c>
-      <c r="L45" t="n">
-        <v>0</v>
-      </c>
       <c r="M45" t="n">
-        <v>0.6645</v>
+        <v>0.7366</v>
       </c>
       <c r="N45" t="n">
-        <v>102</v>
+        <v>249</v>
       </c>
     </row>
     <row r="46">
@@ -2520,16 +2520,16 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.5863</v>
+        <v>0.6722</v>
       </c>
       <c r="C46" t="n">
-        <v>0.3812</v>
+        <v>0.4371</v>
       </c>
       <c r="D46" t="n">
-        <v>-0.3573</v>
+        <v>-0.3136</v>
       </c>
       <c r="E46" t="n">
-        <v>0.5863</v>
+        <v>0.6722</v>
       </c>
       <c r="F46" t="n">
         <v>0.5863</v>
@@ -2562,553 +2562,553 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Ex3rcice</t>
+          <t>huNter-</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.5276999999999999</v>
+        <v>0.5242</v>
       </c>
       <c r="C47" t="n">
-        <v>0.3431</v>
+        <v>0.3409</v>
       </c>
       <c r="D47" t="n">
-        <v>-0.384</v>
+        <v>-0.3797</v>
       </c>
       <c r="E47" t="n">
-        <v>0.5276999999999999</v>
+        <v>0.5242</v>
       </c>
       <c r="F47" t="n">
-        <v>0.5276999999999999</v>
+        <v>0.5078</v>
       </c>
       <c r="G47" t="n">
         <v>0</v>
       </c>
       <c r="H47" t="n">
-        <v>0.5276999999999999</v>
+        <v>0.5078</v>
       </c>
       <c r="I47" t="n">
-        <v>0.5696</v>
+        <v>0.5481</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
       </c>
       <c r="K47" t="n">
-        <v>169</v>
+        <v>191</v>
       </c>
       <c r="L47" t="n">
         <v>0</v>
       </c>
       <c r="M47" t="n">
-        <v>0.5696</v>
+        <v>0.5481</v>
       </c>
       <c r="N47" t="n">
-        <v>169</v>
+        <v>191</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>huNter-</t>
+          <t>degster</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.5081</v>
+        <v>0.4792</v>
       </c>
       <c r="C48" t="n">
-        <v>0.3304</v>
+        <v>0.3116</v>
       </c>
       <c r="D48" t="n">
-        <v>-0.3929</v>
+        <v>-0.3998</v>
       </c>
       <c r="E48" t="n">
-        <v>0.5081</v>
+        <v>0.4792</v>
       </c>
       <c r="F48" t="n">
-        <v>0.5081</v>
+        <v>0.1791</v>
       </c>
       <c r="G48" t="n">
         <v>0</v>
       </c>
       <c r="H48" t="n">
-        <v>0.5081</v>
+        <v>0.1791</v>
       </c>
       <c r="I48" t="n">
-        <v>0.5484</v>
+        <v>0.1837</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
       </c>
       <c r="K48" t="n">
-        <v>191</v>
+        <v>104</v>
       </c>
       <c r="L48" t="n">
         <v>0</v>
       </c>
       <c r="M48" t="n">
-        <v>0.5484</v>
+        <v>0.1837</v>
       </c>
       <c r="N48" t="n">
-        <v>191</v>
+        <v>104</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Aleksib</t>
+          <t>Ex3rcice</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0.4985</v>
+        <v>0.4397</v>
       </c>
       <c r="C49" t="n">
-        <v>0.3241</v>
+        <v>0.2859</v>
       </c>
       <c r="D49" t="n">
-        <v>-0.3973</v>
+        <v>-0.4174</v>
       </c>
       <c r="E49" t="n">
-        <v>0.4985</v>
+        <v>0.4397</v>
       </c>
       <c r="F49" t="n">
-        <v>1.0271</v>
+        <v>0.4989</v>
       </c>
       <c r="G49" t="n">
-        <v>-0.5286</v>
+        <v>0</v>
       </c>
       <c r="H49" t="n">
-        <v>1.0271</v>
+        <v>0.4989</v>
       </c>
       <c r="I49" t="n">
-        <v>0.5546</v>
+        <v>0.5385</v>
       </c>
       <c r="J49" t="n">
-        <v>-0.5286</v>
+        <v>0</v>
       </c>
       <c r="K49" t="n">
-        <v>147</v>
+        <v>169</v>
       </c>
       <c r="L49" t="n">
-        <v>51</v>
+        <v>0</v>
       </c>
       <c r="M49" t="n">
-        <v>0.02600000000000002</v>
+        <v>0.5385</v>
       </c>
       <c r="N49" t="n">
-        <v>198</v>
+        <v>169</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>sl3nd</t>
+          <t>JDC</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0.4579</v>
+        <v>0.3463</v>
       </c>
       <c r="C50" t="n">
-        <v>0.2977</v>
+        <v>0.2252</v>
       </c>
       <c r="D50" t="n">
-        <v>-0.4158</v>
+        <v>-0.4591</v>
       </c>
       <c r="E50" t="n">
-        <v>0.4579</v>
+        <v>0.3463</v>
       </c>
       <c r="F50" t="n">
-        <v>0.4579</v>
+        <v>0.2321</v>
       </c>
       <c r="G50" t="n">
         <v>0</v>
       </c>
       <c r="H50" t="n">
-        <v>0.4579</v>
+        <v>0.2321</v>
       </c>
       <c r="I50" t="n">
-        <v>0.52</v>
+        <v>0.2381</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
       </c>
       <c r="K50" t="n">
-        <v>187</v>
+        <v>108</v>
       </c>
       <c r="L50" t="n">
         <v>0</v>
       </c>
       <c r="M50" t="n">
-        <v>0.52</v>
+        <v>0.2381</v>
       </c>
       <c r="N50" t="n">
-        <v>187</v>
+        <v>108</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>tabseN</t>
+          <t>mzinho</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>0.4063</v>
+        <v>0.3413</v>
       </c>
       <c r="C51" t="n">
-        <v>0.2642</v>
+        <v>0.2219</v>
       </c>
       <c r="D51" t="n">
-        <v>-0.4392</v>
+        <v>-0.4614</v>
       </c>
       <c r="E51" t="n">
-        <v>0.4063</v>
+        <v>0.3413</v>
       </c>
       <c r="F51" t="n">
-        <v>0.4063</v>
+        <v>1.1253</v>
       </c>
       <c r="G51" t="n">
-        <v>0</v>
+        <v>-0.7319</v>
       </c>
       <c r="H51" t="n">
-        <v>0.4063</v>
+        <v>1.1253</v>
       </c>
       <c r="I51" t="n">
-        <v>0.4168</v>
+        <v>1.2458</v>
       </c>
       <c r="J51" t="n">
-        <v>0</v>
+        <v>-0.7319</v>
       </c>
       <c r="K51" t="n">
-        <v>108</v>
+        <v>147</v>
       </c>
       <c r="L51" t="n">
-        <v>0</v>
+        <v>102</v>
       </c>
       <c r="M51" t="n">
-        <v>0.4168</v>
+        <v>0.5139</v>
       </c>
       <c r="N51" t="n">
-        <v>108</v>
+        <v>249</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>mzinho</t>
+          <t>tabseN</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>0.3743</v>
+        <v>0.3163</v>
       </c>
       <c r="C52" t="n">
-        <v>0.2434</v>
+        <v>0.2057</v>
       </c>
       <c r="D52" t="n">
-        <v>-0.4538</v>
+        <v>-0.4725</v>
       </c>
       <c r="E52" t="n">
-        <v>0.3743</v>
+        <v>0.3163</v>
       </c>
       <c r="F52" t="n">
-        <v>1.1063</v>
+        <v>0.4066</v>
       </c>
       <c r="G52" t="n">
-        <v>-0.732</v>
+        <v>0</v>
       </c>
       <c r="H52" t="n">
-        <v>1.1063</v>
+        <v>0.4066</v>
       </c>
       <c r="I52" t="n">
-        <v>1.2248</v>
+        <v>0.4171</v>
       </c>
       <c r="J52" t="n">
-        <v>-0.732</v>
+        <v>0</v>
       </c>
       <c r="K52" t="n">
-        <v>147</v>
+        <v>108</v>
       </c>
       <c r="L52" t="n">
-        <v>102</v>
+        <v>0</v>
       </c>
       <c r="M52" t="n">
-        <v>0.4928000000000001</v>
+        <v>0.4171</v>
       </c>
       <c r="N52" t="n">
-        <v>249</v>
+        <v>108</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>jks</t>
+          <t>sl3nd</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>0.3524</v>
+        <v>0.3045</v>
       </c>
       <c r="C53" t="n">
-        <v>0.2291</v>
+        <v>0.198</v>
       </c>
       <c r="D53" t="n">
-        <v>-0.4638</v>
+        <v>-0.4778</v>
       </c>
       <c r="E53" t="n">
-        <v>0.3524</v>
+        <v>0.3045</v>
       </c>
       <c r="F53" t="n">
-        <v>0.3524</v>
+        <v>0.4501</v>
       </c>
       <c r="G53" t="n">
         <v>0</v>
       </c>
       <c r="H53" t="n">
-        <v>0.3524</v>
+        <v>0.4501</v>
       </c>
       <c r="I53" t="n">
-        <v>0.3804</v>
+        <v>0.5112</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
       </c>
       <c r="K53" t="n">
-        <v>152</v>
+        <v>187</v>
       </c>
       <c r="L53" t="n">
         <v>0</v>
       </c>
       <c r="M53" t="n">
-        <v>0.3804</v>
+        <v>0.5112</v>
       </c>
       <c r="N53" t="n">
-        <v>152</v>
+        <v>187</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>JDC</t>
+          <t>Brollan</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>0.2319</v>
+        <v>0.2665</v>
       </c>
       <c r="C54" t="n">
-        <v>0.1508</v>
+        <v>0.1733</v>
       </c>
       <c r="D54" t="n">
-        <v>-0.5185999999999999</v>
+        <v>-0.4948</v>
       </c>
       <c r="E54" t="n">
-        <v>0.2319</v>
+        <v>0.2665</v>
       </c>
       <c r="F54" t="n">
-        <v>0.2319</v>
+        <v>0.1928</v>
       </c>
       <c r="G54" t="n">
         <v>0</v>
       </c>
       <c r="H54" t="n">
-        <v>0.2319</v>
+        <v>0.1928</v>
       </c>
       <c r="I54" t="n">
-        <v>0.2379</v>
+        <v>0.1928</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
       </c>
       <c r="K54" t="n">
-        <v>108</v>
+        <v>86</v>
       </c>
       <c r="L54" t="n">
         <v>0</v>
       </c>
       <c r="M54" t="n">
-        <v>0.2379</v>
+        <v>0.1928</v>
       </c>
       <c r="N54" t="n">
-        <v>108</v>
+        <v>86</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>yuurih</t>
+          <t>jks</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>0.2197</v>
+        <v>0.2656</v>
       </c>
       <c r="C55" t="n">
-        <v>0.1429</v>
+        <v>0.1727</v>
       </c>
       <c r="D55" t="n">
-        <v>-0.5242</v>
+        <v>-0.4952</v>
       </c>
       <c r="E55" t="n">
-        <v>0.2197</v>
+        <v>0.2656</v>
       </c>
       <c r="F55" t="n">
-        <v>0.2197</v>
+        <v>0.3525</v>
       </c>
       <c r="G55" t="n">
         <v>0</v>
       </c>
       <c r="H55" t="n">
-        <v>0.2197</v>
+        <v>0.3525</v>
       </c>
       <c r="I55" t="n">
-        <v>0.2254</v>
+        <v>0.3805</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
       </c>
       <c r="K55" t="n">
-        <v>102</v>
+        <v>152</v>
       </c>
       <c r="L55" t="n">
         <v>0</v>
       </c>
       <c r="M55" t="n">
-        <v>0.2254</v>
+        <v>0.3805</v>
       </c>
       <c r="N55" t="n">
-        <v>102</v>
+        <v>152</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Magisk</t>
+          <t>Aleksib</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>0.1951</v>
+        <v>0.0915</v>
       </c>
       <c r="C56" t="n">
-        <v>0.1269</v>
+        <v>0.0595</v>
       </c>
       <c r="D56" t="n">
-        <v>-0.5354</v>
+        <v>-0.5729</v>
       </c>
       <c r="E56" t="n">
-        <v>0.1951</v>
+        <v>0.0915</v>
       </c>
       <c r="F56" t="n">
-        <v>0.1951</v>
+        <v>1.0052</v>
       </c>
       <c r="G56" t="n">
-        <v>0</v>
+        <v>-0.5197000000000001</v>
       </c>
       <c r="H56" t="n">
-        <v>0.1951</v>
+        <v>1.0052</v>
       </c>
       <c r="I56" t="n">
-        <v>0.2001</v>
+        <v>0.5427999999999999</v>
       </c>
       <c r="J56" t="n">
-        <v>0</v>
+        <v>-0.5197000000000001</v>
       </c>
       <c r="K56" t="n">
-        <v>104</v>
+        <v>147</v>
       </c>
       <c r="L56" t="n">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="M56" t="n">
-        <v>0.2001</v>
+        <v>0.0230999999999999</v>
       </c>
       <c r="N56" t="n">
-        <v>104</v>
+        <v>198</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Brollan</t>
+          <t>Magisk</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>0.1928</v>
+        <v>0.0505</v>
       </c>
       <c r="C57" t="n">
-        <v>0.1254</v>
+        <v>0.0328</v>
       </c>
       <c r="D57" t="n">
-        <v>-0.5364</v>
+        <v>-0.5913</v>
       </c>
       <c r="E57" t="n">
-        <v>0.1928</v>
+        <v>0.0505</v>
       </c>
       <c r="F57" t="n">
-        <v>0.1928</v>
+        <v>0.195</v>
       </c>
       <c r="G57" t="n">
         <v>0</v>
       </c>
       <c r="H57" t="n">
-        <v>0.1928</v>
+        <v>0.195</v>
       </c>
       <c r="I57" t="n">
-        <v>0.1928</v>
+        <v>0.2</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
       </c>
       <c r="K57" t="n">
-        <v>86</v>
+        <v>104</v>
       </c>
       <c r="L57" t="n">
         <v>0</v>
       </c>
       <c r="M57" t="n">
-        <v>0.1928</v>
+        <v>0.2</v>
       </c>
       <c r="N57" t="n">
-        <v>86</v>
+        <v>104</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>degster</t>
+          <t>yuurih</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>0.1792</v>
+        <v>0.0289</v>
       </c>
       <c r="C58" t="n">
-        <v>0.1165</v>
+        <v>0.0188</v>
       </c>
       <c r="D58" t="n">
-        <v>-0.5426</v>
+        <v>-0.6009</v>
       </c>
       <c r="E58" t="n">
-        <v>0.1792</v>
+        <v>0.0289</v>
       </c>
       <c r="F58" t="n">
-        <v>0.1792</v>
+        <v>0.2197</v>
       </c>
       <c r="G58" t="n">
         <v>0</v>
       </c>
       <c r="H58" t="n">
-        <v>0.1792</v>
+        <v>0.2197</v>
       </c>
       <c r="I58" t="n">
-        <v>0.1838</v>
+        <v>0.2254</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
       </c>
       <c r="K58" t="n">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="L58" t="n">
         <v>0</v>
       </c>
       <c r="M58" t="n">
-        <v>0.1838</v>
+        <v>0.2254</v>
       </c>
       <c r="N58" t="n">
-        <v>104</v>
+        <v>102</v>
       </c>
     </row>
     <row r="59">
@@ -3118,16 +3118,16 @@
         </is>
       </c>
       <c r="B59" t="n">
-        <v>0.0648</v>
+        <v>0.0277</v>
       </c>
       <c r="C59" t="n">
-        <v>0.0421</v>
+        <v>0.018</v>
       </c>
       <c r="D59" t="n">
-        <v>-0.5947</v>
+        <v>-0.6014</v>
       </c>
       <c r="E59" t="n">
-        <v>0.0648</v>
+        <v>0.0277</v>
       </c>
       <c r="F59" t="n">
         <v>0.0648</v>
@@ -3160,262 +3160,262 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>mir</t>
+          <t>TeSeS</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>-0.0801</v>
+        <v>-0.2433</v>
       </c>
       <c r="C60" t="n">
-        <v>-0.0521</v>
+        <v>-0.1582</v>
       </c>
       <c r="D60" t="n">
-        <v>-0.6607</v>
+        <v>-0.7225</v>
       </c>
       <c r="E60" t="n">
-        <v>-0.0801</v>
+        <v>-0.2433</v>
       </c>
       <c r="F60" t="n">
+        <v>-0.1477</v>
+      </c>
+      <c r="G60" t="n">
         <v>0</v>
       </c>
-      <c r="G60" t="n">
-        <v>-0.0801</v>
-      </c>
       <c r="H60" t="n">
+        <v>-0.1477</v>
+      </c>
+      <c r="I60" t="n">
+        <v>-0.1515</v>
+      </c>
+      <c r="J60" t="n">
         <v>0</v>
       </c>
-      <c r="I60" t="n">
+      <c r="K60" t="n">
+        <v>104</v>
+      </c>
+      <c r="L60" t="n">
         <v>0</v>
       </c>
-      <c r="J60" t="n">
-        <v>-0.0801</v>
-      </c>
-      <c r="K60" t="n">
-        <v>0</v>
-      </c>
-      <c r="L60" t="n">
-        <v>37</v>
-      </c>
       <c r="M60" t="n">
-        <v>-0.0801</v>
+        <v>-0.1515</v>
       </c>
       <c r="N60" t="n">
-        <v>37</v>
+        <v>104</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>TeSeS</t>
+          <t>kyuubii</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>-0.1476</v>
+        <v>-0.3794</v>
       </c>
       <c r="C61" t="n">
-        <v>-0.096</v>
+        <v>-0.2467</v>
       </c>
       <c r="D61" t="n">
-        <v>-0.6914</v>
+        <v>-0.7833</v>
       </c>
       <c r="E61" t="n">
-        <v>-0.1476</v>
+        <v>-0.3794</v>
       </c>
       <c r="F61" t="n">
-        <v>-0.1476</v>
+        <v>-0.1625</v>
       </c>
       <c r="G61" t="n">
         <v>0</v>
       </c>
       <c r="H61" t="n">
-        <v>-0.1476</v>
+        <v>-0.1625</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.1514</v>
+        <v>-0.1667</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
       </c>
       <c r="K61" t="n">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="L61" t="n">
         <v>0</v>
       </c>
       <c r="M61" t="n">
-        <v>-0.1514</v>
+        <v>-0.1667</v>
       </c>
       <c r="N61" t="n">
-        <v>104</v>
+        <v>108</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>kyuubii</t>
+          <t>karrigan</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>-0.1626</v>
+        <v>-0.3869</v>
       </c>
       <c r="C62" t="n">
-        <v>-0.1057</v>
+        <v>-0.2516</v>
       </c>
       <c r="D62" t="n">
-        <v>-0.6982</v>
+        <v>-0.7866</v>
       </c>
       <c r="E62" t="n">
-        <v>-0.1626</v>
+        <v>-0.3869</v>
       </c>
       <c r="F62" t="n">
-        <v>-0.1626</v>
+        <v>-0.2658</v>
       </c>
       <c r="G62" t="n">
         <v>0</v>
       </c>
       <c r="H62" t="n">
-        <v>-0.1626</v>
+        <v>-0.2658</v>
       </c>
       <c r="I62" t="n">
-        <v>-0.1668</v>
+        <v>-0.3019</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
       </c>
       <c r="K62" t="n">
-        <v>108</v>
+        <v>276</v>
       </c>
       <c r="L62" t="n">
         <v>0</v>
       </c>
       <c r="M62" t="n">
-        <v>-0.1668</v>
+        <v>-0.3019</v>
       </c>
       <c r="N62" t="n">
-        <v>108</v>
+        <v>276</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>karrigan</t>
+          <t>hyped</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>-0.2654</v>
+        <v>-0.397</v>
       </c>
       <c r="C63" t="n">
-        <v>-0.1726</v>
+        <v>-0.2581</v>
       </c>
       <c r="D63" t="n">
-        <v>-0.745</v>
+        <v>-0.7912</v>
       </c>
       <c r="E63" t="n">
-        <v>-0.2654</v>
+        <v>-0.397</v>
       </c>
       <c r="F63" t="n">
-        <v>-0.2654</v>
+        <v>-0.5226</v>
       </c>
       <c r="G63" t="n">
         <v>0</v>
       </c>
       <c r="H63" t="n">
-        <v>-0.2654</v>
+        <v>-0.5226</v>
       </c>
       <c r="I63" t="n">
-        <v>-0.3014</v>
+        <v>-0.5361</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
       </c>
       <c r="K63" t="n">
-        <v>276</v>
+        <v>108</v>
       </c>
       <c r="L63" t="n">
         <v>0</v>
       </c>
       <c r="M63" t="n">
-        <v>-0.3014</v>
+        <v>-0.5361</v>
       </c>
       <c r="N63" t="n">
-        <v>276</v>
+        <v>108</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Senzu</t>
+          <t>mir</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>-0.3157</v>
+        <v>-0.4167</v>
       </c>
       <c r="C64" t="n">
-        <v>-0.2053</v>
+        <v>-0.271</v>
       </c>
       <c r="D64" t="n">
-        <v>-0.7679</v>
+        <v>-0.8</v>
       </c>
       <c r="E64" t="n">
-        <v>-0.3157</v>
+        <v>-0.4167</v>
       </c>
       <c r="F64" t="n">
-        <v>-0.4496</v>
+        <v>0</v>
       </c>
       <c r="G64" t="n">
-        <v>0.1339</v>
+        <v>-0.07140000000000001</v>
       </c>
       <c r="H64" t="n">
-        <v>-0.4496</v>
+        <v>0</v>
       </c>
       <c r="I64" t="n">
-        <v>-0.4978</v>
+        <v>0</v>
       </c>
       <c r="J64" t="n">
-        <v>0.1339</v>
+        <v>-0.07140000000000001</v>
       </c>
       <c r="K64" t="n">
-        <v>147</v>
+        <v>0</v>
       </c>
       <c r="L64" t="n">
-        <v>102</v>
+        <v>37</v>
       </c>
       <c r="M64" t="n">
-        <v>-0.3639</v>
+        <v>-0.07140000000000001</v>
       </c>
       <c r="N64" t="n">
-        <v>249</v>
+        <v>37</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Staehr</t>
+          <t>jabbi</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>-0.3486</v>
+        <v>-0.4682</v>
       </c>
       <c r="C65" t="n">
-        <v>-0.2267</v>
+        <v>-0.3044</v>
       </c>
       <c r="D65" t="n">
-        <v>-0.7829</v>
+        <v>-0.823</v>
       </c>
       <c r="E65" t="n">
-        <v>-0.3486</v>
+        <v>-0.4682</v>
       </c>
       <c r="F65" t="n">
-        <v>-0.3486</v>
+        <v>-0.4611</v>
       </c>
       <c r="G65" t="n">
         <v>0</v>
       </c>
       <c r="H65" t="n">
-        <v>-0.3486</v>
+        <v>-0.4611</v>
       </c>
       <c r="I65" t="n">
-        <v>-0.3668</v>
+        <v>-0.4852</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -3427,7 +3427,7 @@
         <v>0</v>
       </c>
       <c r="M65" t="n">
-        <v>-0.3668</v>
+        <v>-0.4852</v>
       </c>
       <c r="N65" t="n">
         <v>143</v>
@@ -3436,32 +3436,32 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>jabbi</t>
+          <t>Staehr</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>-0.4611</v>
+        <v>-0.4965</v>
       </c>
       <c r="C66" t="n">
-        <v>-0.2998</v>
+        <v>-0.3228</v>
       </c>
       <c r="D66" t="n">
-        <v>-0.8341</v>
+        <v>-0.8356</v>
       </c>
       <c r="E66" t="n">
-        <v>-0.4611</v>
+        <v>-0.4965</v>
       </c>
       <c r="F66" t="n">
-        <v>-0.4611</v>
+        <v>-0.3486</v>
       </c>
       <c r="G66" t="n">
         <v>0</v>
       </c>
       <c r="H66" t="n">
-        <v>-0.4611</v>
+        <v>-0.3486</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.4852</v>
+        <v>-0.3668</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -3473,7 +3473,7 @@
         <v>0</v>
       </c>
       <c r="M66" t="n">
-        <v>-0.4852</v>
+        <v>-0.3668</v>
       </c>
       <c r="N66" t="n">
         <v>143</v>
@@ -3482,93 +3482,93 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>ultimate</t>
+          <t>xertioN</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>-0.4623</v>
+        <v>-0.5245</v>
       </c>
       <c r="C67" t="n">
-        <v>-0.3006</v>
+        <v>-0.3411</v>
       </c>
       <c r="D67" t="n">
-        <v>-0.8347</v>
+        <v>-0.8481</v>
       </c>
       <c r="E67" t="n">
-        <v>-0.4623</v>
+        <v>-0.5245</v>
       </c>
       <c r="F67" t="n">
-        <v>-0.4623</v>
+        <v>-0.4967</v>
       </c>
       <c r="G67" t="n">
         <v>0</v>
       </c>
       <c r="H67" t="n">
-        <v>-0.4623</v>
+        <v>-0.4967</v>
       </c>
       <c r="I67" t="n">
-        <v>-0.499</v>
+        <v>-0.4967</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
       </c>
       <c r="K67" t="n">
-        <v>152</v>
+        <v>86</v>
       </c>
       <c r="L67" t="n">
         <v>0</v>
       </c>
       <c r="M67" t="n">
-        <v>-0.499</v>
+        <v>-0.4967</v>
       </c>
       <c r="N67" t="n">
-        <v>152</v>
+        <v>86</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>chopper</t>
+          <t>Senzu</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>-0.4766</v>
+        <v>-0.5508</v>
       </c>
       <c r="C68" t="n">
-        <v>-0.3099</v>
+        <v>-0.3582</v>
       </c>
       <c r="D68" t="n">
-        <v>-0.8411999999999999</v>
+        <v>-0.8599</v>
       </c>
       <c r="E68" t="n">
-        <v>-0.4766</v>
+        <v>-0.5508</v>
       </c>
       <c r="F68" t="n">
-        <v>0.4476</v>
+        <v>-0.4501</v>
       </c>
       <c r="G68" t="n">
-        <v>-0.9242</v>
+        <v>0.1341</v>
       </c>
       <c r="H68" t="n">
-        <v>0.4476</v>
+        <v>-0.4501</v>
       </c>
       <c r="I68" t="n">
-        <v>0.5348000000000001</v>
+        <v>-0.4983</v>
       </c>
       <c r="J68" t="n">
-        <v>-0.9242</v>
+        <v>0.1341</v>
       </c>
       <c r="K68" t="n">
-        <v>214</v>
+        <v>147</v>
       </c>
       <c r="L68" t="n">
-        <v>149</v>
+        <v>102</v>
       </c>
       <c r="M68" t="n">
-        <v>-0.3894</v>
+        <v>-0.3642</v>
       </c>
       <c r="N68" t="n">
-        <v>363</v>
+        <v>249</v>
       </c>
     </row>
     <row r="69">
@@ -3578,28 +3578,28 @@
         </is>
       </c>
       <c r="B69" t="n">
-        <v>-0.4771</v>
+        <v>-0.6152</v>
       </c>
       <c r="C69" t="n">
-        <v>-0.3102</v>
+        <v>-0.4</v>
       </c>
       <c r="D69" t="n">
-        <v>-0.8414</v>
+        <v>-0.8885999999999999</v>
       </c>
       <c r="E69" t="n">
-        <v>-0.4771</v>
+        <v>-0.6152</v>
       </c>
       <c r="F69" t="n">
-        <v>-0.4771</v>
+        <v>-0.4773</v>
       </c>
       <c r="G69" t="n">
         <v>0</v>
       </c>
       <c r="H69" t="n">
-        <v>-0.4771</v>
+        <v>-0.4773</v>
       </c>
       <c r="I69" t="n">
-        <v>-0.5149</v>
+        <v>-0.5152</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -3611,7 +3611,7 @@
         <v>0</v>
       </c>
       <c r="M69" t="n">
-        <v>-0.5149</v>
+        <v>-0.5152</v>
       </c>
       <c r="N69" t="n">
         <v>191</v>
@@ -3620,185 +3620,185 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>xertioN</t>
+          <t>chopper</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>-0.4967</v>
+        <v>-0.6456</v>
       </c>
       <c r="C70" t="n">
-        <v>-0.323</v>
+        <v>-0.4198</v>
       </c>
       <c r="D70" t="n">
-        <v>-0.8502999999999999</v>
+        <v>-0.9022</v>
       </c>
       <c r="E70" t="n">
-        <v>-0.4967</v>
+        <v>-0.6456</v>
       </c>
       <c r="F70" t="n">
-        <v>-0.4967</v>
+        <v>0.4474</v>
       </c>
       <c r="G70" t="n">
-        <v>0</v>
+        <v>-0.9237</v>
       </c>
       <c r="H70" t="n">
-        <v>-0.4967</v>
+        <v>0.4474</v>
       </c>
       <c r="I70" t="n">
-        <v>-0.4967</v>
+        <v>0.5346</v>
       </c>
       <c r="J70" t="n">
-        <v>0</v>
+        <v>-0.9237</v>
       </c>
       <c r="K70" t="n">
-        <v>86</v>
+        <v>214</v>
       </c>
       <c r="L70" t="n">
-        <v>0</v>
+        <v>149</v>
       </c>
       <c r="M70" t="n">
-        <v>-0.4967</v>
+        <v>-0.3891</v>
       </c>
       <c r="N70" t="n">
-        <v>86</v>
+        <v>363</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>hyped</t>
+          <t>NAF</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>-0.512</v>
+        <v>-0.7284</v>
       </c>
       <c r="C71" t="n">
-        <v>-0.3329</v>
+        <v>-0.4736</v>
       </c>
       <c r="D71" t="n">
-        <v>-0.8573</v>
+        <v>-0.9392</v>
       </c>
       <c r="E71" t="n">
-        <v>-0.512</v>
+        <v>-0.7284</v>
       </c>
       <c r="F71" t="n">
-        <v>-0.512</v>
+        <v>-0.7211</v>
       </c>
       <c r="G71" t="n">
         <v>0</v>
       </c>
       <c r="H71" t="n">
-        <v>-0.512</v>
+        <v>-0.7211</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.5252</v>
+        <v>-0.7783</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
       </c>
       <c r="K71" t="n">
-        <v>108</v>
+        <v>152</v>
       </c>
       <c r="L71" t="n">
         <v>0</v>
       </c>
       <c r="M71" t="n">
-        <v>-0.5252</v>
+        <v>-0.7783</v>
       </c>
       <c r="N71" t="n">
-        <v>108</v>
+        <v>152</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>ztr</t>
+          <t>xelex</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>-0.6107</v>
+        <v>-0.7798</v>
       </c>
       <c r="C72" t="n">
-        <v>-0.3971</v>
+        <v>-0.5071</v>
       </c>
       <c r="D72" t="n">
-        <v>-0.9022</v>
+        <v>-0.9621</v>
       </c>
       <c r="E72" t="n">
-        <v>-0.6107</v>
+        <v>-0.7798</v>
       </c>
       <c r="F72" t="n">
-        <v>-0.6107</v>
+        <v>-0.6868</v>
       </c>
       <c r="G72" t="n">
         <v>0</v>
       </c>
       <c r="H72" t="n">
-        <v>-0.6107</v>
+        <v>-0.6868</v>
       </c>
       <c r="I72" t="n">
-        <v>-0.6936</v>
+        <v>-0.6868</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
       </c>
       <c r="K72" t="n">
-        <v>187</v>
+        <v>86</v>
       </c>
       <c r="L72" t="n">
         <v>0</v>
       </c>
       <c r="M72" t="n">
-        <v>-0.6936</v>
+        <v>-0.6868</v>
       </c>
       <c r="N72" t="n">
-        <v>187</v>
+        <v>86</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>xelex</t>
+          <t>ultimate</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>-0.6868</v>
+        <v>-0.7867</v>
       </c>
       <c r="C73" t="n">
-        <v>-0.4466</v>
+        <v>-0.5115</v>
       </c>
       <c r="D73" t="n">
-        <v>-0.9368</v>
+        <v>-0.9651999999999999</v>
       </c>
       <c r="E73" t="n">
-        <v>-0.6868</v>
+        <v>-0.7867</v>
       </c>
       <c r="F73" t="n">
-        <v>-0.6868</v>
+        <v>-0.4625</v>
       </c>
       <c r="G73" t="n">
         <v>0</v>
       </c>
       <c r="H73" t="n">
-        <v>-0.6868</v>
+        <v>-0.4625</v>
       </c>
       <c r="I73" t="n">
-        <v>-0.6868</v>
+        <v>-0.4992</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
       </c>
       <c r="K73" t="n">
-        <v>86</v>
+        <v>152</v>
       </c>
       <c r="L73" t="n">
         <v>0</v>
       </c>
       <c r="M73" t="n">
-        <v>-0.6868</v>
+        <v>-0.4992</v>
       </c>
       <c r="N73" t="n">
-        <v>86</v>
+        <v>152</v>
       </c>
     </row>
     <row r="74">
@@ -3808,16 +3808,16 @@
         </is>
       </c>
       <c r="B74" t="n">
-        <v>-0.707</v>
+        <v>-0.9425</v>
       </c>
       <c r="C74" t="n">
-        <v>-0.4597</v>
+        <v>-0.6129</v>
       </c>
       <c r="D74" t="n">
-        <v>-0.946</v>
+        <v>-1.0348</v>
       </c>
       <c r="E74" t="n">
-        <v>-0.707</v>
+        <v>-0.9425</v>
       </c>
       <c r="F74" t="n">
         <v>-0.707</v>
@@ -3850,277 +3850,277 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>NAF</t>
+          <t>ztr</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>-0.7207</v>
+        <v>-0.9669</v>
       </c>
       <c r="C75" t="n">
-        <v>-0.4686</v>
+        <v>-0.6287</v>
       </c>
       <c r="D75" t="n">
-        <v>-0.9523</v>
+        <v>-1.0457</v>
       </c>
       <c r="E75" t="n">
-        <v>-0.7207</v>
+        <v>-0.9669</v>
       </c>
       <c r="F75" t="n">
-        <v>-0.7207</v>
+        <v>-0.6104000000000001</v>
       </c>
       <c r="G75" t="n">
         <v>0</v>
       </c>
       <c r="H75" t="n">
-        <v>-0.7207</v>
+        <v>-0.6104000000000001</v>
       </c>
       <c r="I75" t="n">
-        <v>-0.7779</v>
+        <v>-0.6932</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
       </c>
       <c r="K75" t="n">
-        <v>152</v>
+        <v>187</v>
       </c>
       <c r="L75" t="n">
         <v>0</v>
       </c>
       <c r="M75" t="n">
-        <v>-0.7779</v>
+        <v>-0.6932</v>
       </c>
       <c r="N75" t="n">
-        <v>152</v>
+        <v>187</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>kyxsan</t>
+          <t>FalleN</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>-0.9466</v>
+        <v>-1.1352</v>
       </c>
       <c r="C76" t="n">
-        <v>-0.6155</v>
+        <v>-0.7382</v>
       </c>
       <c r="D76" t="n">
-        <v>-1.0551</v>
+        <v>-1.1209</v>
       </c>
       <c r="E76" t="n">
-        <v>-0.9466</v>
+        <v>-1.1352</v>
       </c>
       <c r="F76" t="n">
-        <v>-0.9466</v>
+        <v>-1.0119</v>
       </c>
       <c r="G76" t="n">
         <v>0</v>
       </c>
       <c r="H76" t="n">
-        <v>-0.9466</v>
+        <v>-1.0119</v>
       </c>
       <c r="I76" t="n">
-        <v>-0.971</v>
+        <v>-1.038</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
       </c>
       <c r="K76" t="n">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="L76" t="n">
         <v>0</v>
       </c>
       <c r="M76" t="n">
-        <v>-0.971</v>
+        <v>-1.038</v>
       </c>
       <c r="N76" t="n">
-        <v>104</v>
+        <v>102</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>FalleN</t>
+          <t>Tauson</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>-1.0119</v>
+        <v>-1.1955</v>
       </c>
       <c r="C77" t="n">
-        <v>-0.658</v>
+        <v>-0.7774</v>
       </c>
       <c r="D77" t="n">
-        <v>-1.0848</v>
+        <v>-1.1478</v>
       </c>
       <c r="E77" t="n">
-        <v>-1.0119</v>
+        <v>-1.1955</v>
       </c>
       <c r="F77" t="n">
-        <v>-1.0119</v>
+        <v>-1.1228</v>
       </c>
       <c r="G77" t="n">
         <v>0</v>
       </c>
       <c r="H77" t="n">
-        <v>-1.0119</v>
+        <v>-1.1228</v>
       </c>
       <c r="I77" t="n">
-        <v>-1.038</v>
+        <v>-1.2751</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
       </c>
       <c r="K77" t="n">
-        <v>102</v>
+        <v>187</v>
       </c>
       <c r="L77" t="n">
         <v>0</v>
       </c>
       <c r="M77" t="n">
-        <v>-1.038</v>
+        <v>-1.2751</v>
       </c>
       <c r="N77" t="n">
-        <v>102</v>
+        <v>187</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Djoko</t>
+          <t>kyxsan</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>-1.1095</v>
+        <v>-1.3677</v>
       </c>
       <c r="C78" t="n">
-        <v>-0.7214</v>
+        <v>-0.8893</v>
       </c>
       <c r="D78" t="n">
-        <v>-1.1293</v>
+        <v>-1.2247</v>
       </c>
       <c r="E78" t="n">
-        <v>-1.1095</v>
+        <v>-1.3677</v>
       </c>
       <c r="F78" t="n">
-        <v>-1.1095</v>
+        <v>-0.9377</v>
       </c>
       <c r="G78" t="n">
         <v>0</v>
       </c>
       <c r="H78" t="n">
-        <v>-1.1095</v>
+        <v>-0.9377</v>
       </c>
       <c r="I78" t="n">
-        <v>-1.1975</v>
+        <v>-0.9619</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
       </c>
       <c r="K78" t="n">
-        <v>169</v>
+        <v>104</v>
       </c>
       <c r="L78" t="n">
         <v>0</v>
       </c>
       <c r="M78" t="n">
-        <v>-1.1975</v>
+        <v>-0.9619</v>
       </c>
       <c r="N78" t="n">
-        <v>169</v>
+        <v>104</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Tauson</t>
+          <t>chelo</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>-1.1235</v>
+        <v>-1.373</v>
       </c>
       <c r="C79" t="n">
-        <v>-0.7305</v>
+        <v>-0.8928</v>
       </c>
       <c r="D79" t="n">
-        <v>-1.1356</v>
+        <v>-1.2271</v>
       </c>
       <c r="E79" t="n">
-        <v>-1.1235</v>
+        <v>-1.373</v>
       </c>
       <c r="F79" t="n">
-        <v>-1.1235</v>
+        <v>-1.2106</v>
       </c>
       <c r="G79" t="n">
         <v>0</v>
       </c>
       <c r="H79" t="n">
-        <v>-1.1235</v>
+        <v>-1.2106</v>
       </c>
       <c r="I79" t="n">
-        <v>-1.2759</v>
+        <v>-1.2418</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
       </c>
       <c r="K79" t="n">
-        <v>187</v>
+        <v>102</v>
       </c>
       <c r="L79" t="n">
         <v>0</v>
       </c>
       <c r="M79" t="n">
-        <v>-1.2759</v>
+        <v>-1.2418</v>
       </c>
       <c r="N79" t="n">
-        <v>187</v>
+        <v>102</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>chelo</t>
+          <t>Djoko</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>-1.2106</v>
+        <v>-1.3748</v>
       </c>
       <c r="C80" t="n">
-        <v>-0.7872</v>
+        <v>-0.894</v>
       </c>
       <c r="D80" t="n">
-        <v>-1.1753</v>
+        <v>-1.2279</v>
       </c>
       <c r="E80" t="n">
-        <v>-1.2106</v>
+        <v>-1.3748</v>
       </c>
       <c r="F80" t="n">
-        <v>-1.2106</v>
+        <v>-1.0985</v>
       </c>
       <c r="G80" t="n">
         <v>0</v>
       </c>
       <c r="H80" t="n">
-        <v>-1.2106</v>
+        <v>-1.0985</v>
       </c>
       <c r="I80" t="n">
-        <v>-1.2418</v>
+        <v>-1.1856</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
       </c>
       <c r="K80" t="n">
-        <v>102</v>
+        <v>169</v>
       </c>
       <c r="L80" t="n">
         <v>0</v>
       </c>
       <c r="M80" t="n">
-        <v>-1.2418</v>
+        <v>-1.1856</v>
       </c>
       <c r="N80" t="n">
-        <v>102</v>
+        <v>169</v>
       </c>
     </row>
     <row r="81">
@@ -4130,16 +4130,16 @@
         </is>
       </c>
       <c r="B81" t="n">
-        <v>-1.6138</v>
+        <v>-1.6723</v>
       </c>
       <c r="C81" t="n">
-        <v>-1.0494</v>
+        <v>-1.0874</v>
       </c>
       <c r="D81" t="n">
-        <v>-1.3588</v>
+        <v>-1.3608</v>
       </c>
       <c r="E81" t="n">
-        <v>-1.6138</v>
+        <v>-1.6723</v>
       </c>
       <c r="F81" t="n">
         <v>-1.6138</v>
@@ -4176,31 +4176,31 @@
         </is>
       </c>
       <c r="B82" t="n">
-        <v>-2.5173</v>
+        <v>-2.8544</v>
       </c>
       <c r="C82" t="n">
-        <v>-1.6368</v>
+        <v>-1.856</v>
       </c>
       <c r="D82" t="n">
-        <v>-1.7701</v>
+        <v>-1.8888</v>
       </c>
       <c r="E82" t="n">
-        <v>-2.5173</v>
+        <v>-2.8544</v>
       </c>
       <c r="F82" t="n">
-        <v>-1.5987</v>
+        <v>-1.5985</v>
       </c>
       <c r="G82" t="n">
-        <v>-0.9186</v>
+        <v>-0.9188</v>
       </c>
       <c r="H82" t="n">
-        <v>-1.5987</v>
+        <v>-1.5985</v>
       </c>
       <c r="I82" t="n">
-        <v>-1.77</v>
+        <v>-1.7697</v>
       </c>
       <c r="J82" t="n">
-        <v>-0.9186</v>
+        <v>-0.9188</v>
       </c>
       <c r="K82" t="n">
         <v>165</v>
@@ -4209,7 +4209,7 @@
         <v>37</v>
       </c>
       <c r="M82" t="n">
-        <v>-2.6886</v>
+        <v>-2.6885</v>
       </c>
       <c r="N82" t="n">
         <v>202</v>
@@ -4355,10 +4355,10 @@
         <v>1.3</v>
       </c>
       <c r="I3" t="n">
-        <v>0.736</v>
+        <v>0.7355</v>
       </c>
       <c r="J3" t="n">
-        <v>13.984</v>
+        <v>13.9745</v>
       </c>
     </row>
     <row r="4">
@@ -4395,10 +4395,10 @@
         <v>1.21</v>
       </c>
       <c r="I4" t="n">
-        <v>0.5497</v>
+        <v>0.5491</v>
       </c>
       <c r="J4" t="n">
-        <v>10.4443</v>
+        <v>10.4329</v>
       </c>
     </row>
     <row r="5">
@@ -4432,13 +4432,13 @@
         <v>19</v>
       </c>
       <c r="H5" t="n">
-        <v>0.95</v>
+        <v>0.96</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.2592</v>
+        <v>-0.228</v>
       </c>
       <c r="J5" t="n">
-        <v>-4.9248</v>
+        <v>-4.332</v>
       </c>
     </row>
     <row r="6">
@@ -4472,13 +4472,13 @@
         <v>19</v>
       </c>
       <c r="H6" t="n">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.4017</v>
+        <v>-0.3754</v>
       </c>
       <c r="J6" t="n">
-        <v>-7.6323</v>
+        <v>-7.1326</v>
       </c>
     </row>
     <row r="7">
@@ -4755,10 +4755,10 @@
         <v>1.31</v>
       </c>
       <c r="I13" t="n">
-        <v>0.755</v>
+        <v>0.7552</v>
       </c>
       <c r="J13" t="n">
-        <v>13.59</v>
+        <v>13.5936</v>
       </c>
     </row>
     <row r="14">
@@ -4792,13 +4792,13 @@
         <v>18</v>
       </c>
       <c r="H14" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="I14" t="n">
-        <v>0.5921999999999999</v>
+        <v>0.5711000000000001</v>
       </c>
       <c r="J14" t="n">
-        <v>10.6596</v>
+        <v>10.2798</v>
       </c>
     </row>
     <row r="15">
@@ -4835,10 +4835,10 @@
         <v>0.95</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.2598</v>
+        <v>-0.2595</v>
       </c>
       <c r="J15" t="n">
-        <v>-4.6764</v>
+        <v>-4.671</v>
       </c>
     </row>
     <row r="16">
@@ -4875,10 +4875,10 @@
         <v>0.93</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.3195</v>
+        <v>-0.3192</v>
       </c>
       <c r="J16" t="n">
-        <v>-5.751</v>
+        <v>-5.7456</v>
       </c>
     </row>
     <row r="17">
@@ -5115,10 +5115,10 @@
         <v>1.31</v>
       </c>
       <c r="I22" t="n">
-        <v>0.7772</v>
+        <v>0.7768</v>
       </c>
       <c r="J22" t="n">
-        <v>18.6528</v>
+        <v>18.6432</v>
       </c>
     </row>
     <row r="23">
@@ -5155,10 +5155,10 @@
         <v>1.26</v>
       </c>
       <c r="I23" t="n">
-        <v>0.6746</v>
+        <v>0.6742</v>
       </c>
       <c r="J23" t="n">
-        <v>16.1904</v>
+        <v>16.1808</v>
       </c>
     </row>
     <row r="24">
@@ -5195,10 +5195,10 @@
         <v>1.25</v>
       </c>
       <c r="I24" t="n">
-        <v>0.6536999999999999</v>
+        <v>0.6533</v>
       </c>
       <c r="J24" t="n">
-        <v>15.6888</v>
+        <v>15.6792</v>
       </c>
     </row>
     <row r="25">
@@ -5232,13 +5232,13 @@
         <v>24</v>
       </c>
       <c r="H25" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="I25" t="n">
-        <v>0.4594</v>
+        <v>0.4817</v>
       </c>
       <c r="J25" t="n">
-        <v>11.0256</v>
+        <v>11.5608</v>
       </c>
     </row>
     <row r="26">
@@ -5275,10 +5275,10 @@
         <v>0.92</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.322</v>
+        <v>-0.3223</v>
       </c>
       <c r="J26" t="n">
-        <v>-7.728</v>
+        <v>-7.7352</v>
       </c>
     </row>
     <row r="27">
@@ -5915,10 +5915,10 @@
         <v>1.27</v>
       </c>
       <c r="I42" t="n">
-        <v>0.5202</v>
+        <v>0.5198</v>
       </c>
       <c r="J42" t="n">
-        <v>15.606</v>
+        <v>15.594</v>
       </c>
     </row>
     <row r="43">
@@ -5955,10 +5955,10 @@
         <v>1.12</v>
       </c>
       <c r="I43" t="n">
-        <v>0.2905</v>
+        <v>0.2901</v>
       </c>
       <c r="J43" t="n">
-        <v>8.715</v>
+        <v>8.702999999999999</v>
       </c>
     </row>
     <row r="44">
@@ -5995,10 +5995,10 @@
         <v>1.1</v>
       </c>
       <c r="I44" t="n">
-        <v>0.2521</v>
+        <v>0.2518</v>
       </c>
       <c r="J44" t="n">
-        <v>7.563</v>
+        <v>7.554</v>
       </c>
     </row>
     <row r="45">
@@ -6035,10 +6035,10 @@
         <v>0.85</v>
       </c>
       <c r="I45" t="n">
-        <v>-0.2017</v>
+        <v>-0.2018</v>
       </c>
       <c r="J45" t="n">
-        <v>-6.051</v>
+        <v>-6.054</v>
       </c>
     </row>
     <row r="46">
@@ -6072,13 +6072,13 @@
         <v>30</v>
       </c>
       <c r="H46" t="n">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.3752</v>
+        <v>-0.3663</v>
       </c>
       <c r="J46" t="n">
-        <v>-11.256</v>
+        <v>-10.989</v>
       </c>
     </row>
     <row r="47">
@@ -6512,13 +6512,13 @@
         <v>20</v>
       </c>
       <c r="H57" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="I57" t="n">
-        <v>0.465</v>
+        <v>0.4519</v>
       </c>
       <c r="J57" t="n">
-        <v>9.300000000000001</v>
+        <v>9.038</v>
       </c>
     </row>
     <row r="58">
@@ -6555,10 +6555,10 @@
         <v>0.95</v>
       </c>
       <c r="I58" t="n">
-        <v>-0.0805</v>
+        <v>-0.0803</v>
       </c>
       <c r="J58" t="n">
-        <v>-1.61</v>
+        <v>-1.606</v>
       </c>
     </row>
     <row r="59">
@@ -6595,10 +6595,10 @@
         <v>0.93</v>
       </c>
       <c r="I59" t="n">
-        <v>-0.1058</v>
+        <v>-0.1057</v>
       </c>
       <c r="J59" t="n">
-        <v>-2.116</v>
+        <v>-2.114</v>
       </c>
     </row>
     <row r="60">
@@ -6635,10 +6635,10 @@
         <v>0.92</v>
       </c>
       <c r="I60" t="n">
-        <v>-0.1176</v>
+        <v>-0.1175</v>
       </c>
       <c r="J60" t="n">
-        <v>-2.352</v>
+        <v>-2.35</v>
       </c>
     </row>
     <row r="61">
@@ -6675,10 +6675,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.4647</v>
+        <v>-0.4645</v>
       </c>
       <c r="J61" t="n">
-        <v>-9.294</v>
+        <v>-9.289999999999999</v>
       </c>
     </row>
     <row r="62">
@@ -7115,10 +7115,10 @@
         <v>1.4</v>
       </c>
       <c r="I72" t="n">
-        <v>0.7664</v>
+        <v>0.7653</v>
       </c>
       <c r="J72" t="n">
-        <v>11.496</v>
+        <v>11.4795</v>
       </c>
     </row>
     <row r="73">
@@ -7155,10 +7155,10 @@
         <v>0.74</v>
       </c>
       <c r="I73" t="n">
-        <v>-0.2851</v>
+        <v>-0.2852</v>
       </c>
       <c r="J73" t="n">
-        <v>-4.2765</v>
+        <v>-4.278</v>
       </c>
     </row>
     <row r="74">
@@ -7192,13 +7192,13 @@
         <v>15</v>
       </c>
       <c r="H74" t="n">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="I74" t="n">
-        <v>-0.4017</v>
+        <v>-0.393</v>
       </c>
       <c r="J74" t="n">
-        <v>-6.0255</v>
+        <v>-5.895</v>
       </c>
     </row>
     <row r="75">
@@ -7235,10 +7235,10 @@
         <v>0.5</v>
       </c>
       <c r="I75" t="n">
-        <v>-0.4987</v>
+        <v>-0.4989</v>
       </c>
       <c r="J75" t="n">
-        <v>-7.4805</v>
+        <v>-7.4835</v>
       </c>
     </row>
     <row r="76">
@@ -7275,10 +7275,10 @@
         <v>0.44</v>
       </c>
       <c r="I76" t="n">
-        <v>-0.5507</v>
+        <v>-0.551</v>
       </c>
       <c r="J76" t="n">
-        <v>-8.2605</v>
+        <v>-8.265000000000001</v>
       </c>
     </row>
     <row r="77">
@@ -7315,10 +7315,10 @@
         <v>1.85</v>
       </c>
       <c r="I77" t="n">
-        <v>1.3414</v>
+        <v>1.3421</v>
       </c>
       <c r="J77" t="n">
-        <v>20.121</v>
+        <v>20.1315</v>
       </c>
     </row>
     <row r="78">
@@ -7355,10 +7355,10 @@
         <v>1.79</v>
       </c>
       <c r="I78" t="n">
-        <v>1.27</v>
+        <v>1.2706</v>
       </c>
       <c r="J78" t="n">
-        <v>19.05</v>
+        <v>19.059</v>
       </c>
     </row>
     <row r="79">
@@ -7392,13 +7392,13 @@
         <v>15</v>
       </c>
       <c r="H79" t="n">
-        <v>1.66</v>
+        <v>1.64</v>
       </c>
       <c r="I79" t="n">
-        <v>1.1126</v>
+        <v>1.0885</v>
       </c>
       <c r="J79" t="n">
-        <v>16.689</v>
+        <v>16.3275</v>
       </c>
     </row>
     <row r="80">
@@ -7435,10 +7435,10 @@
         <v>1.2</v>
       </c>
       <c r="I80" t="n">
-        <v>0.4839</v>
+        <v>0.4843</v>
       </c>
       <c r="J80" t="n">
-        <v>7.2585</v>
+        <v>7.2645</v>
       </c>
     </row>
     <row r="81">
@@ -7475,10 +7475,10 @@
         <v>1.11</v>
       </c>
       <c r="I81" t="n">
-        <v>0.2866</v>
+        <v>0.2872</v>
       </c>
       <c r="J81" t="n">
-        <v>4.299</v>
+        <v>4.308</v>
       </c>
     </row>
     <row r="82">
@@ -7712,13 +7712,13 @@
         <v>22</v>
       </c>
       <c r="H87" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="I87" t="n">
-        <v>1.4181</v>
+        <v>1.4061</v>
       </c>
       <c r="J87" t="n">
-        <v>31.1982</v>
+        <v>30.9342</v>
       </c>
     </row>
     <row r="88">
@@ -7755,10 +7755,10 @@
         <v>1.25</v>
       </c>
       <c r="I88" t="n">
-        <v>0.5919</v>
+        <v>0.592</v>
       </c>
       <c r="J88" t="n">
-        <v>13.0218</v>
+        <v>13.024</v>
       </c>
     </row>
     <row r="89">
@@ -7795,10 +7795,10 @@
         <v>1.24</v>
       </c>
       <c r="I89" t="n">
-        <v>0.5768</v>
+        <v>0.5769</v>
       </c>
       <c r="J89" t="n">
-        <v>12.6896</v>
+        <v>12.6918</v>
       </c>
     </row>
     <row r="90">
@@ -7835,10 +7835,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I90" t="n">
-        <v>-0.2737</v>
+        <v>-0.2733</v>
       </c>
       <c r="J90" t="n">
-        <v>-6.0214</v>
+        <v>-6.0126</v>
       </c>
     </row>
     <row r="91">
@@ -7875,10 +7875,10 @@
         <v>0.88</v>
       </c>
       <c r="I91" t="n">
-        <v>-0.4381</v>
+        <v>-0.4378</v>
       </c>
       <c r="J91" t="n">
-        <v>-9.638199999999999</v>
+        <v>-9.631600000000001</v>
       </c>
     </row>
     <row r="92">
@@ -8712,13 +8712,13 @@
         <v>24</v>
       </c>
       <c r="H112" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="I112" t="n">
-        <v>0.7679</v>
+        <v>0.7584</v>
       </c>
       <c r="J112" t="n">
-        <v>18.4296</v>
+        <v>18.2016</v>
       </c>
     </row>
     <row r="113">
@@ -8755,10 +8755,10 @@
         <v>1.17</v>
       </c>
       <c r="I113" t="n">
-        <v>0.2668</v>
+        <v>0.2669</v>
       </c>
       <c r="J113" t="n">
-        <v>6.4032</v>
+        <v>6.4056</v>
       </c>
     </row>
     <row r="114">
@@ -8795,10 +8795,10 @@
         <v>1.03</v>
       </c>
       <c r="I114" t="n">
-        <v>0.0631</v>
+        <v>0.0633</v>
       </c>
       <c r="J114" t="n">
-        <v>1.5144</v>
+        <v>1.5192</v>
       </c>
     </row>
     <row r="115">
@@ -8835,10 +8835,10 @@
         <v>0.97</v>
       </c>
       <c r="I115" t="n">
-        <v>-0.0689</v>
+        <v>-0.0687</v>
       </c>
       <c r="J115" t="n">
-        <v>-1.6536</v>
+        <v>-1.6488</v>
       </c>
     </row>
     <row r="116">
@@ -8875,10 +8875,10 @@
         <v>0.89</v>
       </c>
       <c r="I116" t="n">
-        <v>-0.1699</v>
+        <v>-0.1697</v>
       </c>
       <c r="J116" t="n">
-        <v>-4.0776</v>
+        <v>-4.0728</v>
       </c>
     </row>
     <row r="117">
@@ -8912,13 +8912,13 @@
         <v>24</v>
       </c>
       <c r="H117" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="I117" t="n">
-        <v>0.5449000000000001</v>
+        <v>0.5567</v>
       </c>
       <c r="J117" t="n">
-        <v>13.0776</v>
+        <v>13.3608</v>
       </c>
     </row>
     <row r="118">
@@ -8955,10 +8955,10 @@
         <v>1.05</v>
       </c>
       <c r="I118" t="n">
-        <v>0.1313</v>
+        <v>0.1309</v>
       </c>
       <c r="J118" t="n">
-        <v>3.1512</v>
+        <v>3.1416</v>
       </c>
     </row>
     <row r="119">
@@ -8995,10 +8995,10 @@
         <v>0.77</v>
       </c>
       <c r="I119" t="n">
-        <v>-0.272</v>
+        <v>-0.2722</v>
       </c>
       <c r="J119" t="n">
-        <v>-6.528</v>
+        <v>-6.5328</v>
       </c>
     </row>
     <row r="120">
@@ -9035,10 +9035,10 @@
         <v>0.72</v>
       </c>
       <c r="I120" t="n">
-        <v>-0.3194</v>
+        <v>-0.3196</v>
       </c>
       <c r="J120" t="n">
-        <v>-7.6656</v>
+        <v>-7.6704</v>
       </c>
     </row>
     <row r="121">
@@ -9075,10 +9075,10 @@
         <v>0.61</v>
       </c>
       <c r="I121" t="n">
-        <v>-0.4193</v>
+        <v>-0.4195</v>
       </c>
       <c r="J121" t="n">
-        <v>-10.0632</v>
+        <v>-10.068</v>
       </c>
     </row>
     <row r="122">
@@ -9115,10 +9115,10 @@
         <v>1.02</v>
       </c>
       <c r="I122" t="n">
-        <v>0.1086</v>
+        <v>0.1092</v>
       </c>
       <c r="J122" t="n">
-        <v>2.0634</v>
+        <v>2.0748</v>
       </c>
     </row>
     <row r="123">
@@ -9155,10 +9155,10 @@
         <v>1.01</v>
       </c>
       <c r="I123" t="n">
-        <v>0.0771</v>
+        <v>0.07770000000000001</v>
       </c>
       <c r="J123" t="n">
-        <v>1.4649</v>
+        <v>1.4763</v>
       </c>
     </row>
     <row r="124">
@@ -9195,10 +9195,10 @@
         <v>0.96</v>
       </c>
       <c r="I124" t="n">
-        <v>-0.0568</v>
+        <v>-0.0565</v>
       </c>
       <c r="J124" t="n">
-        <v>-1.0792</v>
+        <v>-1.0735</v>
       </c>
     </row>
     <row r="125">
@@ -9232,13 +9232,13 @@
         <v>19</v>
       </c>
       <c r="H125" t="n">
-        <v>0.68</v>
+        <v>0.67</v>
       </c>
       <c r="I125" t="n">
-        <v>-0.3492</v>
+        <v>-0.3581</v>
       </c>
       <c r="J125" t="n">
-        <v>-6.6348</v>
+        <v>-6.8039</v>
       </c>
     </row>
     <row r="126">
@@ -9275,10 +9275,10 @@
         <v>0.48</v>
       </c>
       <c r="I126" t="n">
-        <v>-0.5258</v>
+        <v>-0.5256</v>
       </c>
       <c r="J126" t="n">
-        <v>-9.9902</v>
+        <v>-9.9864</v>
       </c>
     </row>
     <row r="127">
@@ -9315,10 +9315,10 @@
         <v>1.53</v>
       </c>
       <c r="I127" t="n">
-        <v>1.1241</v>
+        <v>1.1238</v>
       </c>
       <c r="J127" t="n">
-        <v>21.3579</v>
+        <v>21.3522</v>
       </c>
     </row>
     <row r="128">
@@ -9352,13 +9352,13 @@
         <v>19</v>
       </c>
       <c r="H128" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="I128" t="n">
-        <v>0.8337</v>
+        <v>0.8524</v>
       </c>
       <c r="J128" t="n">
-        <v>15.8403</v>
+        <v>16.1956</v>
       </c>
     </row>
     <row r="129">
@@ -9395,10 +9395,10 @@
         <v>1.33</v>
       </c>
       <c r="I129" t="n">
-        <v>0.7955</v>
+        <v>0.7953</v>
       </c>
       <c r="J129" t="n">
-        <v>15.1145</v>
+        <v>15.1107</v>
       </c>
     </row>
     <row r="130">
@@ -9435,10 +9435,10 @@
         <v>1.28</v>
       </c>
       <c r="I130" t="n">
-        <v>0.6991000000000001</v>
+        <v>0.6989</v>
       </c>
       <c r="J130" t="n">
-        <v>13.2829</v>
+        <v>13.2791</v>
       </c>
     </row>
     <row r="131">
@@ -9475,10 +9475,10 @@
         <v>1.05</v>
       </c>
       <c r="I131" t="n">
-        <v>0.1514</v>
+        <v>0.1511</v>
       </c>
       <c r="J131" t="n">
-        <v>2.8766</v>
+        <v>2.8709</v>
       </c>
     </row>
     <row r="132">
@@ -9715,10 +9715,10 @@
         <v>1.56</v>
       </c>
       <c r="I137" t="n">
-        <v>1.1617</v>
+        <v>1.1613</v>
       </c>
       <c r="J137" t="n">
-        <v>19.7489</v>
+        <v>19.7421</v>
       </c>
     </row>
     <row r="138">
@@ -9755,10 +9755,10 @@
         <v>1.49</v>
       </c>
       <c r="I138" t="n">
-        <v>1.0686</v>
+        <v>1.0683</v>
       </c>
       <c r="J138" t="n">
-        <v>18.1662</v>
+        <v>18.1611</v>
       </c>
     </row>
     <row r="139">
@@ -9795,10 +9795,10 @@
         <v>1.36</v>
       </c>
       <c r="I139" t="n">
-        <v>0.8511</v>
+        <v>0.8508</v>
       </c>
       <c r="J139" t="n">
-        <v>14.4687</v>
+        <v>14.4636</v>
       </c>
     </row>
     <row r="140">
@@ -9832,13 +9832,13 @@
         <v>17</v>
       </c>
       <c r="H140" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="I140" t="n">
-        <v>0.4152</v>
+        <v>0.4384</v>
       </c>
       <c r="J140" t="n">
-        <v>7.0584</v>
+        <v>7.4528</v>
       </c>
     </row>
     <row r="141">
@@ -9875,10 +9875,10 @@
         <v>1.04</v>
       </c>
       <c r="I141" t="n">
-        <v>0.1177</v>
+        <v>0.1174</v>
       </c>
       <c r="J141" t="n">
-        <v>2.0009</v>
+        <v>1.9958</v>
       </c>
     </row>
     <row r="142">
@@ -10115,10 +10115,10 @@
         <v>1.63</v>
       </c>
       <c r="I147" t="n">
-        <v>1.2197</v>
+        <v>1.2201</v>
       </c>
       <c r="J147" t="n">
-        <v>19.5152</v>
+        <v>19.5216</v>
       </c>
     </row>
     <row r="148">
@@ -10155,10 +10155,10 @@
         <v>1.6</v>
       </c>
       <c r="I148" t="n">
-        <v>1.183</v>
+        <v>1.1833</v>
       </c>
       <c r="J148" t="n">
-        <v>18.928</v>
+        <v>18.9328</v>
       </c>
     </row>
     <row r="149">
@@ -10192,13 +10192,13 @@
         <v>16</v>
       </c>
       <c r="H149" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="I149" t="n">
-        <v>1.1221</v>
+        <v>1.11</v>
       </c>
       <c r="J149" t="n">
-        <v>17.9536</v>
+        <v>17.76</v>
       </c>
     </row>
     <row r="150">
@@ -10232,13 +10232,13 @@
         <v>16</v>
       </c>
       <c r="H150" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="I150" t="n">
-        <v>1.0973</v>
+        <v>1.085</v>
       </c>
       <c r="J150" t="n">
-        <v>17.5568</v>
+        <v>17.36</v>
       </c>
     </row>
     <row r="151">
@@ -10275,10 +10275,10 @@
         <v>1.47</v>
       </c>
       <c r="I151" t="n">
-        <v>1.0166</v>
+        <v>1.0169</v>
       </c>
       <c r="J151" t="n">
-        <v>16.2656</v>
+        <v>16.2704</v>
       </c>
     </row>
     <row r="152">
@@ -10515,10 +10515,10 @@
         <v>1.44</v>
       </c>
       <c r="I157" t="n">
-        <v>1.0067</v>
+        <v>1.0071</v>
       </c>
       <c r="J157" t="n">
-        <v>22.1474</v>
+        <v>22.1562</v>
       </c>
     </row>
     <row r="158">
@@ -10552,13 +10552,13 @@
         <v>22</v>
       </c>
       <c r="H158" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="I158" t="n">
-        <v>0.956</v>
+        <v>0.9384</v>
       </c>
       <c r="J158" t="n">
-        <v>21.032</v>
+        <v>20.6448</v>
       </c>
     </row>
     <row r="159">
@@ -10595,10 +10595,10 @@
         <v>1.27</v>
       </c>
       <c r="I159" t="n">
-        <v>0.6846</v>
+        <v>0.6848</v>
       </c>
       <c r="J159" t="n">
-        <v>15.0612</v>
+        <v>15.0656</v>
       </c>
     </row>
     <row r="160">
@@ -10635,10 +10635,10 @@
         <v>1.15</v>
       </c>
       <c r="I160" t="n">
-        <v>0.4261</v>
+        <v>0.4264</v>
       </c>
       <c r="J160" t="n">
-        <v>9.3742</v>
+        <v>9.380800000000001</v>
       </c>
     </row>
     <row r="161">
@@ -10675,10 +10675,10 @@
         <v>0.98</v>
       </c>
       <c r="I161" t="n">
-        <v>-0.1435</v>
+        <v>-0.1432</v>
       </c>
       <c r="J161" t="n">
-        <v>-3.157</v>
+        <v>-3.1504</v>
       </c>
     </row>
     <row r="162">
@@ -12115,10 +12115,10 @@
         <v>1.54</v>
       </c>
       <c r="I197" t="n">
-        <v>1.1446</v>
+        <v>1.145</v>
       </c>
       <c r="J197" t="n">
-        <v>20.6028</v>
+        <v>20.61</v>
       </c>
     </row>
     <row r="198">
@@ -12152,13 +12152,13 @@
         <v>18</v>
       </c>
       <c r="H198" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="I198" t="n">
-        <v>1.0772</v>
+        <v>1.0636</v>
       </c>
       <c r="J198" t="n">
-        <v>19.3896</v>
+        <v>19.1448</v>
       </c>
     </row>
     <row r="199">
@@ -12195,10 +12195,10 @@
         <v>1.34</v>
       </c>
       <c r="I199" t="n">
-        <v>0.8203</v>
+        <v>0.8206</v>
       </c>
       <c r="J199" t="n">
-        <v>14.7654</v>
+        <v>14.7708</v>
       </c>
     </row>
     <row r="200">
@@ -12235,10 +12235,10 @@
         <v>1.05</v>
       </c>
       <c r="I200" t="n">
-        <v>0.158</v>
+        <v>0.1583</v>
       </c>
       <c r="J200" t="n">
-        <v>2.844</v>
+        <v>2.8494</v>
       </c>
     </row>
     <row r="201">
@@ -12275,10 +12275,10 @@
         <v>0.92</v>
       </c>
       <c r="I201" t="n">
-        <v>-0.3371</v>
+        <v>-0.3368</v>
       </c>
       <c r="J201" t="n">
-        <v>-6.0678</v>
+        <v>-6.0624</v>
       </c>
     </row>
     <row r="202">
@@ -12715,10 +12715,10 @@
         <v>1.08</v>
       </c>
       <c r="I212" t="n">
-        <v>0.2211</v>
+        <v>0.2206</v>
       </c>
       <c r="J212" t="n">
-        <v>4.6431</v>
+        <v>4.6326</v>
       </c>
     </row>
     <row r="213">
@@ -12755,10 +12755,10 @@
         <v>1.01</v>
       </c>
       <c r="I213" t="n">
-        <v>0.0493</v>
+        <v>0.049</v>
       </c>
       <c r="J213" t="n">
-        <v>1.0353</v>
+        <v>1.029</v>
       </c>
     </row>
     <row r="214">
@@ -12792,13 +12792,13 @@
         <v>21</v>
       </c>
       <c r="H214" t="n">
-        <v>0.99</v>
+        <v>1</v>
       </c>
       <c r="I214" t="n">
-        <v>-0.0226</v>
+        <v>0.0049</v>
       </c>
       <c r="J214" t="n">
-        <v>-0.4746</v>
+        <v>0.1029</v>
       </c>
     </row>
     <row r="215">
@@ -12835,10 +12835,10 @@
         <v>0.97</v>
       </c>
       <c r="I215" t="n">
-        <v>-0.0557</v>
+        <v>-0.0558</v>
       </c>
       <c r="J215" t="n">
-        <v>-1.1697</v>
+        <v>-1.1718</v>
       </c>
     </row>
     <row r="216">
@@ -12875,10 +12875,10 @@
         <v>0.72</v>
       </c>
       <c r="I216" t="n">
-        <v>-0.3249</v>
+        <v>-0.3251</v>
       </c>
       <c r="J216" t="n">
-        <v>-6.8229</v>
+        <v>-6.8271</v>
       </c>
     </row>
     <row r="217">
@@ -12915,10 +12915,10 @@
         <v>1.84</v>
       </c>
       <c r="I217" t="n">
-        <v>1.5541</v>
+        <v>1.5547</v>
       </c>
       <c r="J217" t="n">
-        <v>32.6361</v>
+        <v>32.6487</v>
       </c>
     </row>
     <row r="218">
@@ -12952,13 +12952,13 @@
         <v>21</v>
       </c>
       <c r="H218" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="I218" t="n">
-        <v>1.2287</v>
+        <v>1.2158</v>
       </c>
       <c r="J218" t="n">
-        <v>25.8027</v>
+        <v>25.5318</v>
       </c>
     </row>
     <row r="219">
@@ -12995,10 +12995,10 @@
         <v>0.93</v>
       </c>
       <c r="I219" t="n">
-        <v>-0.2954</v>
+        <v>-0.295</v>
       </c>
       <c r="J219" t="n">
-        <v>-6.2034</v>
+        <v>-6.195</v>
       </c>
     </row>
     <row r="220">
@@ -13035,10 +13035,10 @@
         <v>0.89</v>
       </c>
       <c r="I220" t="n">
-        <v>-0.4047</v>
+        <v>-0.4044</v>
       </c>
       <c r="J220" t="n">
-        <v>-8.498699999999999</v>
+        <v>-8.4924</v>
       </c>
     </row>
     <row r="221">
@@ -13075,10 +13075,10 @@
         <v>0.7</v>
       </c>
       <c r="I221" t="n">
-        <v>-0.8434</v>
+        <v>-0.8431</v>
       </c>
       <c r="J221" t="n">
-        <v>-17.7114</v>
+        <v>-17.7051</v>
       </c>
     </row>
     <row r="222">
@@ -14915,10 +14915,10 @@
         <v>1.76</v>
       </c>
       <c r="I267" t="n">
-        <v>1.4425</v>
+        <v>1.4419</v>
       </c>
       <c r="J267" t="n">
-        <v>30.2925</v>
+        <v>30.2799</v>
       </c>
     </row>
     <row r="268">
@@ -14955,10 +14955,10 @@
         <v>1.2</v>
       </c>
       <c r="I268" t="n">
-        <v>0.5432</v>
+        <v>0.543</v>
       </c>
       <c r="J268" t="n">
-        <v>11.4072</v>
+        <v>11.403</v>
       </c>
     </row>
     <row r="269">
@@ -14995,10 +14995,10 @@
         <v>1.11</v>
       </c>
       <c r="I269" t="n">
-        <v>0.3325</v>
+        <v>0.3321</v>
       </c>
       <c r="J269" t="n">
-        <v>6.9825</v>
+        <v>6.9741</v>
       </c>
     </row>
     <row r="270">
@@ -15032,13 +15032,13 @@
         <v>21</v>
       </c>
       <c r="H270" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="I270" t="n">
-        <v>0.0638</v>
+        <v>0.1</v>
       </c>
       <c r="J270" t="n">
-        <v>1.3398</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="271">
@@ -15075,10 +15075,10 @@
         <v>1.02</v>
       </c>
       <c r="I271" t="n">
-        <v>0.0638</v>
+        <v>0.0635</v>
       </c>
       <c r="J271" t="n">
-        <v>1.3398</v>
+        <v>1.3335</v>
       </c>
     </row>
     <row r="272">
@@ -15115,10 +15115,10 @@
         <v>1.26</v>
       </c>
       <c r="I272" t="n">
-        <v>0.4616</v>
+        <v>0.4609</v>
       </c>
       <c r="J272" t="n">
-        <v>7.8472</v>
+        <v>7.8353</v>
       </c>
     </row>
     <row r="273">
@@ -15155,10 +15155,10 @@
         <v>0.84</v>
       </c>
       <c r="I273" t="n">
-        <v>-0.1981</v>
+        <v>-0.1982</v>
       </c>
       <c r="J273" t="n">
-        <v>-3.3677</v>
+        <v>-3.3694</v>
       </c>
     </row>
     <row r="274">
@@ -15192,13 +15192,13 @@
         <v>17</v>
       </c>
       <c r="H274" t="n">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="I274" t="n">
-        <v>-0.2468</v>
+        <v>-0.2373</v>
       </c>
       <c r="J274" t="n">
-        <v>-4.1956</v>
+        <v>-4.0341</v>
       </c>
     </row>
     <row r="275">
@@ -15235,10 +15235,10 @@
         <v>0.68</v>
       </c>
       <c r="I275" t="n">
-        <v>-0.3501</v>
+        <v>-0.3503</v>
       </c>
       <c r="J275" t="n">
-        <v>-5.9517</v>
+        <v>-5.9551</v>
       </c>
     </row>
     <row r="276">
@@ -15275,10 +15275,10 @@
         <v>0.62</v>
       </c>
       <c r="I276" t="n">
-        <v>-0.4043</v>
+        <v>-0.4045</v>
       </c>
       <c r="J276" t="n">
-        <v>-6.8731</v>
+        <v>-6.8765</v>
       </c>
     </row>
     <row r="277">
@@ -15915,10 +15915,10 @@
         <v>1.3</v>
       </c>
       <c r="I292" t="n">
-        <v>0.7679</v>
+        <v>0.7684</v>
       </c>
       <c r="J292" t="n">
-        <v>17.6617</v>
+        <v>17.6732</v>
       </c>
     </row>
     <row r="293">
@@ -15955,10 +15955,10 @@
         <v>1.18</v>
       </c>
       <c r="I293" t="n">
-        <v>0.5098</v>
+        <v>0.5102</v>
       </c>
       <c r="J293" t="n">
-        <v>11.7254</v>
+        <v>11.7346</v>
       </c>
     </row>
     <row r="294">
@@ -15995,10 +15995,10 @@
         <v>1.08</v>
       </c>
       <c r="I294" t="n">
-        <v>0.2677</v>
+        <v>0.268</v>
       </c>
       <c r="J294" t="n">
-        <v>6.1571</v>
+        <v>6.164</v>
       </c>
     </row>
     <row r="295">
@@ -16035,10 +16035,10 @@
         <v>1.06</v>
       </c>
       <c r="I295" t="n">
-        <v>0.2111</v>
+        <v>0.2114</v>
       </c>
       <c r="J295" t="n">
-        <v>4.8553</v>
+        <v>4.8622</v>
       </c>
     </row>
     <row r="296">
@@ -16072,13 +16072,13 @@
         <v>23</v>
       </c>
       <c r="H296" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="I296" t="n">
-        <v>0.1495</v>
+        <v>0.1164</v>
       </c>
       <c r="J296" t="n">
-        <v>3.4385</v>
+        <v>2.6772</v>
       </c>
     </row>
     <row r="297">
@@ -20715,10 +20715,10 @@
         <v>1.55</v>
       </c>
       <c r="I412" t="n">
-        <v>0.7472</v>
+        <v>0.7467</v>
       </c>
       <c r="J412" t="n">
-        <v>17.1856</v>
+        <v>17.1741</v>
       </c>
     </row>
     <row r="413">
@@ -20755,10 +20755,10 @@
         <v>1.02</v>
       </c>
       <c r="I413" t="n">
-        <v>0.0545</v>
+        <v>0.0543</v>
       </c>
       <c r="J413" t="n">
-        <v>1.2535</v>
+        <v>1.2489</v>
       </c>
     </row>
     <row r="414">
@@ -20795,10 +20795,10 @@
         <v>0.97</v>
       </c>
       <c r="I414" t="n">
-        <v>-0.0614</v>
+        <v>-0.0616</v>
       </c>
       <c r="J414" t="n">
-        <v>-1.4122</v>
+        <v>-1.4168</v>
       </c>
     </row>
     <row r="415">
@@ -20832,13 +20832,13 @@
         <v>23</v>
       </c>
       <c r="H415" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.95</v>
       </c>
       <c r="I415" t="n">
-        <v>-0.1026</v>
+        <v>-0.0897</v>
       </c>
       <c r="J415" t="n">
-        <v>-2.3598</v>
+        <v>-2.0631</v>
       </c>
     </row>
     <row r="416">
@@ -20875,10 +20875,10 @@
         <v>0.74</v>
       </c>
       <c r="I416" t="n">
-        <v>-0.3143</v>
+        <v>-0.3144</v>
       </c>
       <c r="J416" t="n">
-        <v>-7.2289</v>
+        <v>-7.2312</v>
       </c>
     </row>
     <row r="417">
@@ -21552,13 +21552,13 @@
         <v>24</v>
       </c>
       <c r="H433" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="I433" t="n">
-        <v>0.5003</v>
+        <v>0.4778</v>
       </c>
       <c r="J433" t="n">
-        <v>12.0072</v>
+        <v>11.4672</v>
       </c>
     </row>
     <row r="434">
@@ -21632,13 +21632,13 @@
         <v>24</v>
       </c>
       <c r="H435" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="I435" t="n">
-        <v>0.2543</v>
+        <v>0.2815</v>
       </c>
       <c r="J435" t="n">
-        <v>6.1032</v>
+        <v>6.756</v>
       </c>
     </row>
     <row r="436">
@@ -23712,13 +23712,13 @@
         <v>22</v>
       </c>
       <c r="H487" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="I487" t="n">
-        <v>0.739</v>
+        <v>0.7591</v>
       </c>
       <c r="J487" t="n">
-        <v>16.258</v>
+        <v>16.7002</v>
       </c>
     </row>
     <row r="488">
@@ -23755,10 +23755,10 @@
         <v>1.26</v>
       </c>
       <c r="I488" t="n">
-        <v>0.6768</v>
+        <v>0.6765</v>
       </c>
       <c r="J488" t="n">
-        <v>14.8896</v>
+        <v>14.883</v>
       </c>
     </row>
     <row r="489">
@@ -23795,10 +23795,10 @@
         <v>1.15</v>
       </c>
       <c r="I489" t="n">
-        <v>0.4378</v>
+        <v>0.4375</v>
       </c>
       <c r="J489" t="n">
-        <v>9.631600000000001</v>
+        <v>9.625</v>
       </c>
     </row>
     <row r="490">
@@ -23835,10 +23835,10 @@
         <v>1.07</v>
       </c>
       <c r="I490" t="n">
-        <v>0.234</v>
+        <v>0.2337</v>
       </c>
       <c r="J490" t="n">
-        <v>5.148</v>
+        <v>5.1414</v>
       </c>
     </row>
     <row r="491">
@@ -23875,10 +23875,10 @@
         <v>1.07</v>
       </c>
       <c r="I491" t="n">
-        <v>0.234</v>
+        <v>0.2337</v>
       </c>
       <c r="J491" t="n">
-        <v>5.148</v>
+        <v>5.1414</v>
       </c>
     </row>
     <row r="492">
@@ -25312,13 +25312,13 @@
         <v>21</v>
       </c>
       <c r="H527" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="I527" t="n">
-        <v>0.4275</v>
+        <v>0.4105</v>
       </c>
       <c r="J527" t="n">
-        <v>8.977499999999999</v>
+        <v>8.6205</v>
       </c>
     </row>
     <row r="528">
@@ -25355,10 +25355,10 @@
         <v>1.02</v>
       </c>
       <c r="I528" t="n">
-        <v>0.0795</v>
+        <v>0.0799</v>
       </c>
       <c r="J528" t="n">
-        <v>1.6695</v>
+        <v>1.6779</v>
       </c>
     </row>
     <row r="529">
@@ -25395,10 +25395,10 @@
         <v>0.99</v>
       </c>
       <c r="I529" t="n">
-        <v>-0.0227</v>
+        <v>-0.0226</v>
       </c>
       <c r="J529" t="n">
-        <v>-0.4767</v>
+        <v>-0.4746</v>
       </c>
     </row>
     <row r="530">
@@ -25435,10 +25435,10 @@
         <v>0.83</v>
       </c>
       <c r="I530" t="n">
-        <v>-0.2182</v>
+        <v>-0.218</v>
       </c>
       <c r="J530" t="n">
-        <v>-4.5822</v>
+        <v>-4.578</v>
       </c>
     </row>
     <row r="531">
@@ -25475,10 +25475,10 @@
         <v>0.75</v>
       </c>
       <c r="I531" t="n">
-        <v>-0.2969</v>
+        <v>-0.2967</v>
       </c>
       <c r="J531" t="n">
-        <v>-6.2349</v>
+        <v>-6.2307</v>
       </c>
     </row>
     <row r="532">
@@ -25512,13 +25512,13 @@
         <v>24</v>
       </c>
       <c r="H532" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="I532" t="n">
-        <v>0.7421</v>
+        <v>0.7631</v>
       </c>
       <c r="J532" t="n">
-        <v>17.8104</v>
+        <v>18.3144</v>
       </c>
     </row>
     <row r="533">
@@ -25555,10 +25555,10 @@
         <v>1.1</v>
       </c>
       <c r="I533" t="n">
-        <v>0.3405</v>
+        <v>0.34</v>
       </c>
       <c r="J533" t="n">
-        <v>8.172000000000001</v>
+        <v>8.16</v>
       </c>
     </row>
     <row r="534">
@@ -25595,10 +25595,10 @@
         <v>1.01</v>
       </c>
       <c r="I534" t="n">
-        <v>0.058</v>
+        <v>0.0578</v>
       </c>
       <c r="J534" t="n">
-        <v>1.392</v>
+        <v>1.3872</v>
       </c>
     </row>
     <row r="535">
@@ -25635,10 +25635,10 @@
         <v>0.91</v>
       </c>
       <c r="I535" t="n">
-        <v>-0.3163</v>
+        <v>-0.3167</v>
       </c>
       <c r="J535" t="n">
-        <v>-7.5912</v>
+        <v>-7.6008</v>
       </c>
     </row>
     <row r="536">
@@ -25675,10 +25675,10 @@
         <v>0.74</v>
       </c>
       <c r="I536" t="n">
-        <v>-0.7236</v>
+        <v>-0.7241</v>
       </c>
       <c r="J536" t="n">
-        <v>-17.3664</v>
+        <v>-17.3784</v>
       </c>
     </row>
     <row r="537">
@@ -26312,13 +26312,13 @@
         <v>17</v>
       </c>
       <c r="H552" t="n">
-        <v>2.16</v>
+        <v>2.15</v>
       </c>
       <c r="I552" t="n">
-        <v>1.8652</v>
+        <v>1.8542</v>
       </c>
       <c r="J552" t="n">
-        <v>31.7084</v>
+        <v>31.5214</v>
       </c>
     </row>
     <row r="553">
@@ -26355,10 +26355,10 @@
         <v>1.66</v>
       </c>
       <c r="I553" t="n">
-        <v>1.27</v>
+        <v>1.2703</v>
       </c>
       <c r="J553" t="n">
-        <v>21.59</v>
+        <v>21.5951</v>
       </c>
     </row>
     <row r="554">
@@ -26395,10 +26395,10 @@
         <v>1.64</v>
       </c>
       <c r="I554" t="n">
-        <v>1.245</v>
+        <v>1.2453</v>
       </c>
       <c r="J554" t="n">
-        <v>21.165</v>
+        <v>21.1701</v>
       </c>
     </row>
     <row r="555">
@@ -26435,10 +26435,10 @@
         <v>0.93</v>
       </c>
       <c r="I555" t="n">
-        <v>-0.3352</v>
+        <v>-0.3349</v>
       </c>
       <c r="J555" t="n">
-        <v>-5.6984</v>
+        <v>-5.6933</v>
       </c>
     </row>
     <row r="556">
@@ -26475,10 +26475,10 @@
         <v>0.83</v>
       </c>
       <c r="I556" t="n">
-        <v>-0.5915</v>
+        <v>-0.5911999999999999</v>
       </c>
       <c r="J556" t="n">
-        <v>-10.0555</v>
+        <v>-10.0504</v>
       </c>
     </row>
     <row r="557">
@@ -28715,10 +28715,10 @@
         <v>1.21</v>
       </c>
       <c r="I612" t="n">
-        <v>0.3545</v>
+        <v>0.3541</v>
       </c>
       <c r="J612" t="n">
-        <v>7.799</v>
+        <v>7.7902</v>
       </c>
     </row>
     <row r="613">
@@ -28755,10 +28755,10 @@
         <v>1.09</v>
       </c>
       <c r="I613" t="n">
-        <v>0.1834</v>
+        <v>0.1831</v>
       </c>
       <c r="J613" t="n">
-        <v>4.0348</v>
+        <v>4.0282</v>
       </c>
     </row>
     <row r="614">
@@ -28792,13 +28792,13 @@
         <v>22</v>
       </c>
       <c r="H614" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="I614" t="n">
-        <v>0.1674</v>
+        <v>0.1831</v>
       </c>
       <c r="J614" t="n">
-        <v>3.6828</v>
+        <v>4.0282</v>
       </c>
     </row>
     <row r="615">
@@ -28835,10 +28835,10 @@
         <v>0.91</v>
       </c>
       <c r="I615" t="n">
-        <v>-0.1347</v>
+        <v>-0.1349</v>
       </c>
       <c r="J615" t="n">
-        <v>-2.9634</v>
+        <v>-2.9678</v>
       </c>
     </row>
     <row r="616">
@@ -28875,10 +28875,10 @@
         <v>0.67</v>
       </c>
       <c r="I616" t="n">
-        <v>-0.3743</v>
+        <v>-0.3745</v>
       </c>
       <c r="J616" t="n">
-        <v>-8.2346</v>
+        <v>-8.239000000000001</v>
       </c>
     </row>
     <row r="617">
@@ -28915,10 +28915,10 @@
         <v>1.33</v>
       </c>
       <c r="I617" t="n">
-        <v>0.4521</v>
+        <v>0.4524</v>
       </c>
       <c r="J617" t="n">
-        <v>9.946199999999999</v>
+        <v>9.9528</v>
       </c>
     </row>
     <row r="618">
@@ -28952,13 +28952,13 @@
         <v>22</v>
       </c>
       <c r="H618" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="I618" t="n">
-        <v>0.441</v>
+        <v>0.4301</v>
       </c>
       <c r="J618" t="n">
-        <v>9.702</v>
+        <v>9.462199999999999</v>
       </c>
     </row>
     <row r="619">
@@ -28995,10 +28995,10 @@
         <v>1.28</v>
       </c>
       <c r="I619" t="n">
-        <v>0.396</v>
+        <v>0.3962</v>
       </c>
       <c r="J619" t="n">
-        <v>8.712</v>
+        <v>8.7164</v>
       </c>
     </row>
     <row r="620">
@@ -29035,10 +29035,10 @@
         <v>1.18</v>
       </c>
       <c r="I620" t="n">
-        <v>0.2781</v>
+        <v>0.2782</v>
       </c>
       <c r="J620" t="n">
-        <v>6.1182</v>
+        <v>6.1204</v>
       </c>
     </row>
     <row r="621">
@@ -29075,10 +29075,10 @@
         <v>0.65</v>
       </c>
       <c r="I621" t="n">
-        <v>-0.4046</v>
+        <v>-0.4045</v>
       </c>
       <c r="J621" t="n">
-        <v>-8.901199999999999</v>
+        <v>-8.898999999999999</v>
       </c>
     </row>
     <row r="622">
@@ -29715,10 +29715,10 @@
         <v>2.05</v>
       </c>
       <c r="I637" t="n">
-        <v>1.7922</v>
+        <v>1.7929</v>
       </c>
       <c r="J637" t="n">
-        <v>39.4284</v>
+        <v>39.4438</v>
       </c>
     </row>
     <row r="638">
@@ -29755,10 +29755,10 @@
         <v>1.6</v>
       </c>
       <c r="I638" t="n">
-        <v>1.2271</v>
+        <v>1.2275</v>
       </c>
       <c r="J638" t="n">
-        <v>26.9962</v>
+        <v>27.005</v>
       </c>
     </row>
     <row r="639">
@@ -29795,10 +29795,10 @@
         <v>1.03</v>
       </c>
       <c r="I639" t="n">
-        <v>0.0949</v>
+        <v>0.09520000000000001</v>
       </c>
       <c r="J639" t="n">
-        <v>2.0878</v>
+        <v>2.0944</v>
       </c>
     </row>
     <row r="640">
@@ -29832,13 +29832,13 @@
         <v>22</v>
       </c>
       <c r="H640" t="n">
-        <v>0.88</v>
+        <v>0.87</v>
       </c>
       <c r="I640" t="n">
-        <v>-0.4415</v>
+        <v>-0.4665</v>
       </c>
       <c r="J640" t="n">
-        <v>-9.712999999999999</v>
+        <v>-10.263</v>
       </c>
     </row>
     <row r="641">
@@ -29875,10 +29875,10 @@
         <v>0.71</v>
       </c>
       <c r="I641" t="n">
-        <v>-0.8319</v>
+        <v>-0.8316</v>
       </c>
       <c r="J641" t="n">
-        <v>-18.3018</v>
+        <v>-18.2952</v>
       </c>
     </row>
     <row r="642">
@@ -30315,10 +30315,10 @@
         <v>1.28</v>
       </c>
       <c r="I652" t="n">
-        <v>0.7308</v>
+        <v>0.7302999999999999</v>
       </c>
       <c r="J652" t="n">
-        <v>25.578</v>
+        <v>25.5605</v>
       </c>
     </row>
     <row r="653">
@@ -30355,10 +30355,10 @@
         <v>1.28</v>
       </c>
       <c r="I653" t="n">
-        <v>0.7308</v>
+        <v>0.7302999999999999</v>
       </c>
       <c r="J653" t="n">
-        <v>25.578</v>
+        <v>25.5605</v>
       </c>
     </row>
     <row r="654">
@@ -30392,13 +30392,13 @@
         <v>35</v>
       </c>
       <c r="H654" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="I654" t="n">
-        <v>0.0828</v>
+        <v>0.1188</v>
       </c>
       <c r="J654" t="n">
-        <v>2.898</v>
+        <v>4.158</v>
       </c>
     </row>
     <row r="655">
@@ -30435,10 +30435,10 @@
         <v>1.02</v>
       </c>
       <c r="I655" t="n">
-        <v>0.0828</v>
+        <v>0.0824</v>
       </c>
       <c r="J655" t="n">
-        <v>2.898</v>
+        <v>2.884</v>
       </c>
     </row>
     <row r="656">
@@ -30475,10 +30475,10 @@
         <v>0.97</v>
       </c>
       <c r="I656" t="n">
-        <v>-0.1559</v>
+        <v>-0.1563</v>
       </c>
       <c r="J656" t="n">
-        <v>-5.4565</v>
+        <v>-5.4705</v>
       </c>
     </row>
     <row r="657">
@@ -30515,10 +30515,10 @@
         <v>1.39</v>
       </c>
       <c r="I657" t="n">
-        <v>0.7229</v>
+        <v>0.724</v>
       </c>
       <c r="J657" t="n">
-        <v>25.3015</v>
+        <v>25.34</v>
       </c>
     </row>
     <row r="658">
@@ -30555,10 +30555,10 @@
         <v>1.26</v>
       </c>
       <c r="I658" t="n">
-        <v>0.5226</v>
+        <v>0.5235</v>
       </c>
       <c r="J658" t="n">
-        <v>18.291</v>
+        <v>18.3225</v>
       </c>
     </row>
     <row r="659">
@@ -30595,10 +30595,10 @@
         <v>1.03</v>
       </c>
       <c r="I659" t="n">
-        <v>0.0961</v>
+        <v>0.0964</v>
       </c>
       <c r="J659" t="n">
-        <v>3.3635</v>
+        <v>3.374</v>
       </c>
     </row>
     <row r="660">
@@ -30632,13 +30632,13 @@
         <v>35</v>
       </c>
       <c r="H660" t="n">
-        <v>0.99</v>
+        <v>0.98</v>
       </c>
       <c r="I660" t="n">
-        <v>-0.0281</v>
+        <v>-0.0455</v>
       </c>
       <c r="J660" t="n">
-        <v>-0.9835</v>
+        <v>-1.5925</v>
       </c>
     </row>
     <row r="661">
@@ -30672,13 +30672,13 @@
         <v>35</v>
       </c>
       <c r="H661" t="n">
-        <v>0.55</v>
+        <v>0.54</v>
       </c>
       <c r="I661" t="n">
-        <v>-0.4837</v>
+        <v>-0.492</v>
       </c>
       <c r="J661" t="n">
-        <v>-16.9295</v>
+        <v>-17.22</v>
       </c>
     </row>
     <row r="662">
@@ -30715,10 +30715,10 @@
         <v>1.54</v>
       </c>
       <c r="I662" t="n">
-        <v>1.1518</v>
+        <v>1.1523</v>
       </c>
       <c r="J662" t="n">
-        <v>25.3396</v>
+        <v>25.3506</v>
       </c>
     </row>
     <row r="663">
@@ -30752,13 +30752,13 @@
         <v>22</v>
       </c>
       <c r="H663" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="I663" t="n">
-        <v>0.6461</v>
+        <v>0.6258</v>
       </c>
       <c r="J663" t="n">
-        <v>14.2142</v>
+        <v>13.7676</v>
       </c>
     </row>
     <row r="664">
@@ -30795,10 +30795,10 @@
         <v>1.24</v>
       </c>
       <c r="I664" t="n">
-        <v>0.6257</v>
+        <v>0.6258</v>
       </c>
       <c r="J664" t="n">
-        <v>13.7654</v>
+        <v>13.7676</v>
       </c>
     </row>
     <row r="665">
@@ -30835,10 +30835,10 @@
         <v>1.09</v>
       </c>
       <c r="I665" t="n">
-        <v>0.2785</v>
+        <v>0.2789</v>
       </c>
       <c r="J665" t="n">
-        <v>6.127</v>
+        <v>6.1358</v>
       </c>
     </row>
     <row r="666">
@@ -30875,10 +30875,10 @@
         <v>1.04</v>
       </c>
       <c r="I666" t="n">
-        <v>0.1323</v>
+        <v>0.1327</v>
       </c>
       <c r="J666" t="n">
-        <v>2.9106</v>
+        <v>2.9194</v>
       </c>
     </row>
     <row r="667">
@@ -30912,13 +30912,13 @@
         <v>22</v>
       </c>
       <c r="H667" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="I667" t="n">
-        <v>0.2818</v>
+        <v>0.302</v>
       </c>
       <c r="J667" t="n">
-        <v>6.1996</v>
+        <v>6.644</v>
       </c>
     </row>
     <row r="668">
@@ -31032,13 +31032,13 @@
         <v>22</v>
       </c>
       <c r="H670" t="n">
-        <v>0.75</v>
+        <v>0.74</v>
       </c>
       <c r="I670" t="n">
-        <v>-0.2889</v>
+        <v>-0.2984</v>
       </c>
       <c r="J670" t="n">
-        <v>-6.3558</v>
+        <v>-6.5648</v>
       </c>
     </row>
     <row r="671">
@@ -31115,10 +31115,10 @@
         <v>1.72</v>
       </c>
       <c r="I672" t="n">
-        <v>1.1651</v>
+        <v>1.1643</v>
       </c>
       <c r="J672" t="n">
-        <v>23.302</v>
+        <v>23.286</v>
       </c>
     </row>
     <row r="673">
@@ -31155,10 +31155,10 @@
         <v>0.99</v>
       </c>
       <c r="I673" t="n">
-        <v>-0.0238</v>
+        <v>-0.0239</v>
       </c>
       <c r="J673" t="n">
-        <v>-0.476</v>
+        <v>-0.478</v>
       </c>
     </row>
     <row r="674">
@@ -31195,10 +31195,10 @@
         <v>0.96</v>
       </c>
       <c r="I674" t="n">
-        <v>-0.0706</v>
+        <v>-0.0707</v>
       </c>
       <c r="J674" t="n">
-        <v>-1.412</v>
+        <v>-1.414</v>
       </c>
     </row>
     <row r="675">
@@ -31232,13 +31232,13 @@
         <v>20</v>
       </c>
       <c r="H675" t="n">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="I675" t="n">
-        <v>-0.3357</v>
+        <v>-0.3266</v>
       </c>
       <c r="J675" t="n">
-        <v>-6.714</v>
+        <v>-6.532</v>
       </c>
     </row>
     <row r="676">
@@ -31275,10 +31275,10 @@
         <v>0.47</v>
       </c>
       <c r="I676" t="n">
-        <v>-0.546</v>
+        <v>-0.5461</v>
       </c>
       <c r="J676" t="n">
-        <v>-10.92</v>
+        <v>-10.922</v>
       </c>
     </row>
     <row r="677">
@@ -31312,13 +31312,13 @@
         <v>20</v>
       </c>
       <c r="H677" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="I677" t="n">
-        <v>1.0827</v>
+        <v>1.0964</v>
       </c>
       <c r="J677" t="n">
-        <v>21.654</v>
+        <v>21.928</v>
       </c>
     </row>
     <row r="678">
@@ -31432,13 +31432,13 @@
         <v>20</v>
       </c>
       <c r="H680" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="I680" t="n">
-        <v>0.5412</v>
+        <v>0.5193</v>
       </c>
       <c r="J680" t="n">
-        <v>10.824</v>
+        <v>10.386</v>
       </c>
     </row>
     <row r="681">
